--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808CCA45-4C1E-BF44-9C2E-7F419BDB1150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22027C6-7E5E-9242-A46A-D029CF700D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2427,6 +2427,30 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2434,15 +2458,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2454,13 +2469,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2468,18 +2480,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12662,7 +12662,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -13754,18 +13754,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="253" t="s">
+      <c r="B2" s="261" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="254"/>
-      <c r="E2" s="253" t="s">
+      <c r="C2" s="262"/>
+      <c r="E2" s="261" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="254"/>
-      <c r="H2" s="253" t="s">
+      <c r="F2" s="262"/>
+      <c r="H2" s="261" t="s">
         <v>379</v>
       </c>
-      <c r="I2" s="254"/>
+      <c r="I2" s="262"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="I3" s="232">
         <f>'AVG target price'!C5</f>
-        <v>6.0867686783178394</v>
+        <v>6.0868928055205176</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="I7" s="233">
         <f>'AVG target price'!C9</f>
-        <v>13.047072100701815</v>
+        <v>13.047103132502485</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-5.1122029039868011E-2</v>
+        <v>-5.1119772181637428E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -14033,10 +14033,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="255" t="s">
+      <c r="B17" s="263" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="255"/>
+      <c r="C17" s="263"/>
       <c r="E17" s="205" t="s">
         <v>343</v>
       </c>
@@ -14109,14 +14109,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="255" t="s">
+      <c r="B25" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="255"/>
-      <c r="E25" s="253" t="s">
+      <c r="C25" s="263"/>
+      <c r="E25" s="261" t="s">
         <v>399</v>
       </c>
-      <c r="F25" s="254"/>
+      <c r="F25" s="262"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -14165,15 +14165,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="256" t="s">
+      <c r="B33" s="253" t="s">
         <v>389</v>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14192,24 +14192,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="256"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
+      <c r="B39" s="253"/>
+      <c r="C39" s="253"/>
+      <c r="D39" s="253"/>
+      <c r="E39" s="253"/>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="253"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="256" t="s">
+      <c r="B42" s="253" t="s">
         <v>392</v>
       </c>
-      <c r="C42" s="256"/>
-      <c r="D42" s="256"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
-      <c r="G42" s="256"/>
-      <c r="H42" s="256"/>
+      <c r="C42" s="253"/>
+      <c r="D42" s="253"/>
+      <c r="E42" s="253"/>
+      <c r="F42" s="253"/>
+      <c r="G42" s="253"/>
+      <c r="H42" s="253"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14240,24 +14240,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="256"/>
-      <c r="C49" s="256"/>
-      <c r="D49" s="256"/>
-      <c r="E49" s="256"/>
-      <c r="F49" s="256"/>
-      <c r="G49" s="256"/>
-      <c r="H49" s="256"/>
+      <c r="B49" s="253"/>
+      <c r="C49" s="253"/>
+      <c r="D49" s="253"/>
+      <c r="E49" s="253"/>
+      <c r="F49" s="253"/>
+      <c r="G49" s="253"/>
+      <c r="H49" s="253"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="256" t="s">
+      <c r="B52" s="253" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="256"/>
-      <c r="D52" s="256"/>
-      <c r="E52" s="256"/>
-      <c r="F52" s="256"/>
-      <c r="G52" s="256"/>
-      <c r="H52" s="256"/>
+      <c r="C52" s="253"/>
+      <c r="D52" s="253"/>
+      <c r="E52" s="253"/>
+      <c r="F52" s="253"/>
+      <c r="G52" s="253"/>
+      <c r="H52" s="253"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14272,28 +14272,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="256"/>
-      <c r="C59" s="256"/>
-      <c r="D59" s="256"/>
-      <c r="E59" s="256"/>
-      <c r="F59" s="256"/>
-      <c r="G59" s="256"/>
-      <c r="H59" s="256"/>
+      <c r="B59" s="253"/>
+      <c r="C59" s="253"/>
+      <c r="D59" s="253"/>
+      <c r="E59" s="253"/>
+      <c r="F59" s="253"/>
+      <c r="G59" s="253"/>
+      <c r="H59" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14363,36 +14363,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="256" t="s">
+      <c r="S2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256" t="s">
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14403,32 +14403,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="257" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="265" t="s">
+      <c r="S4" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
-      <c r="AA4" s="266"/>
-      <c r="AB4" s="266"/>
-      <c r="AC4" s="266"/>
+      <c r="T4" s="270"/>
+      <c r="U4" s="270"/>
+      <c r="V4" s="270"/>
+      <c r="W4" s="270"/>
+      <c r="X4" s="270"/>
+      <c r="Y4" s="270"/>
+      <c r="Z4" s="270"/>
+      <c r="AA4" s="270"/>
+      <c r="AB4" s="270"/>
+      <c r="AC4" s="270"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="H6" s="64">
         <f>H9*H29</f>
-        <v>628183.5</v>
+        <v>626739.39999999991</v>
       </c>
       <c r="I6" s="64">
         <f t="shared" ref="I6:L6" si="1">I9*I29</f>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="H7" s="64">
         <f>H9-H6-H8</f>
-        <v>1094834.1000000001</v>
+        <v>1092317.24</v>
       </c>
       <c r="I7" s="64">
         <f t="shared" ref="I7:L7" si="2">I9-I6-I8</f>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="H8" s="64">
         <f>H9*H28</f>
-        <v>71792.400000000009</v>
+        <v>71627.360000000001</v>
       </c>
       <c r="I8" s="64">
         <f t="shared" ref="I8:L8" si="5">I9*I28</f>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="H9" s="96">
         <f>H21*H27</f>
-        <v>1794810</v>
+        <v>1790684</v>
       </c>
       <c r="I9" s="96">
         <f t="shared" ref="I9:L9" si="6">I21*I27</f>
@@ -14924,33 +14924,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="257" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="257"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="265" t="s">
+      <c r="S11" s="269" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="266"/>
-      <c r="U11" s="266"/>
-      <c r="V11" s="266"/>
-      <c r="W11" s="266"/>
-      <c r="X11" s="266"/>
-      <c r="Y11" s="266"/>
-      <c r="Z11" s="266"/>
-      <c r="AA11" s="266"/>
-      <c r="AB11" s="266"/>
-      <c r="AC11" s="266"/>
+      <c r="T11" s="270"/>
+      <c r="U11" s="270"/>
+      <c r="V11" s="270"/>
+      <c r="W11" s="270"/>
+      <c r="X11" s="270"/>
+      <c r="Y11" s="270"/>
+      <c r="Z11" s="270"/>
+      <c r="AA11" s="270"/>
+      <c r="AB11" s="270"/>
+      <c r="AC11" s="270"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15070,11 +15070,11 @@
       </c>
       <c r="H13" s="97">
         <f t="shared" si="9"/>
-        <v>3.5932908307140243E-2</v>
+        <v>3.355145334551457E-2</v>
       </c>
       <c r="I13" s="97">
         <f t="shared" si="9"/>
-        <v>2.3522986515882582E-2</v>
+        <v>2.5881334411080648E-2</v>
       </c>
       <c r="J13" s="97">
         <f t="shared" si="9"/>
@@ -15154,11 +15154,11 @@
       </c>
       <c r="H14" s="97">
         <f t="shared" si="11"/>
-        <v>0.14705732593517684</v>
+        <v>0.14442041254222238</v>
       </c>
       <c r="I14" s="97">
         <f t="shared" si="11"/>
-        <v>0.13360382436023865</v>
+        <v>0.13621581473894895</v>
       </c>
       <c r="J14" s="97">
         <f t="shared" si="11"/>
@@ -15238,11 +15238,11 @@
       </c>
       <c r="H15" s="97">
         <f t="shared" si="12"/>
-        <v>0.44434072345390918</v>
+        <v>0.44102039995171616</v>
       </c>
       <c r="I15" s="97">
         <f t="shared" si="12"/>
-        <v>-0.1044173867986028</v>
+        <v>-0.1023538323903046</v>
       </c>
       <c r="J15" s="97">
         <f t="shared" si="12"/>
@@ -15322,11 +15322,11 @@
       </c>
       <c r="H16" s="107">
         <f t="shared" si="13"/>
-        <v>0.11439289892038351</v>
+        <v>0.1118310761642447</v>
       </c>
       <c r="I16" s="107">
         <f t="shared" si="13"/>
-        <v>8.5554682668360416E-2</v>
+        <v>8.8055960739024774E-2</v>
       </c>
       <c r="J16" s="107">
         <f t="shared" si="13"/>
@@ -15391,33 +15391,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="264" t="s">
+      <c r="C19" s="257" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="264"/>
-      <c r="E19" s="264"/>
-      <c r="F19" s="264"/>
-      <c r="G19" s="264"/>
-      <c r="H19" s="264"/>
-      <c r="I19" s="264"/>
-      <c r="J19" s="264"/>
-      <c r="K19" s="264"/>
-      <c r="L19" s="264"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="257"/>
+      <c r="J19" s="257"/>
+      <c r="K19" s="257"/>
+      <c r="L19" s="257"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="265" t="s">
+      <c r="S19" s="269" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="266"/>
-      <c r="U19" s="266"/>
-      <c r="V19" s="266"/>
-      <c r="W19" s="266"/>
-      <c r="X19" s="266"/>
-      <c r="Y19" s="266"/>
-      <c r="Z19" s="266"/>
-      <c r="AA19" s="266"/>
-      <c r="AB19" s="266"/>
-      <c r="AC19" s="266"/>
+      <c r="T19" s="270"/>
+      <c r="U19" s="270"/>
+      <c r="V19" s="270"/>
+      <c r="W19" s="270"/>
+      <c r="X19" s="270"/>
+      <c r="Y19" s="270"/>
+      <c r="Z19" s="270"/>
+      <c r="AA19" s="270"/>
+      <c r="AB19" s="270"/>
+      <c r="AC19" s="270"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16004,7 +16004,7 @@
         <v>0.86937314547867905</v>
       </c>
       <c r="H27" s="114">
-        <v>0.87</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="I27" s="114">
         <v>0.86</v>
@@ -16235,32 +16235,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="264" t="s">
+      <c r="C32" s="257" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="264"/>
-      <c r="E32" s="264"/>
-      <c r="F32" s="264"/>
-      <c r="G32" s="264"/>
-      <c r="H32" s="264"/>
-      <c r="I32" s="264"/>
-      <c r="J32" s="264"/>
-      <c r="K32" s="264"/>
-      <c r="L32" s="264"/>
+      <c r="D32" s="257"/>
+      <c r="E32" s="257"/>
+      <c r="F32" s="257"/>
+      <c r="G32" s="257"/>
+      <c r="H32" s="257"/>
+      <c r="I32" s="257"/>
+      <c r="J32" s="257"/>
+      <c r="K32" s="257"/>
+      <c r="L32" s="257"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="265" t="s">
+      <c r="S32" s="269" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="266"/>
-      <c r="U32" s="266"/>
-      <c r="V32" s="266"/>
-      <c r="W32" s="266"/>
-      <c r="X32" s="266"/>
-      <c r="Y32" s="266"/>
-      <c r="Z32" s="266"/>
-      <c r="AA32" s="266"/>
-      <c r="AB32" s="266"/>
-      <c r="AC32" s="266"/>
+      <c r="T32" s="270"/>
+      <c r="U32" s="270"/>
+      <c r="V32" s="270"/>
+      <c r="W32" s="270"/>
+      <c r="X32" s="270"/>
+      <c r="Y32" s="270"/>
+      <c r="Z32" s="270"/>
+      <c r="AA32" s="270"/>
+      <c r="AB32" s="270"/>
+      <c r="AC32" s="270"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16517,18 +16517,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16565,35 +16565,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="P2" s="256" t="s">
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="P2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256" t="s">
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16602,31 +16602,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="257" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="P4" s="266" t="s">
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="P4" s="270" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
+      <c r="Q4" s="270"/>
+      <c r="R4" s="270"/>
+      <c r="S4" s="270"/>
+      <c r="T4" s="270"/>
+      <c r="U4" s="270"/>
+      <c r="V4" s="270"/>
+      <c r="W4" s="270"/>
+      <c r="X4" s="270"/>
+      <c r="Y4" s="270"/>
+      <c r="Z4" s="270"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16749,7 +16749,7 @@
       </c>
       <c r="H6" s="94">
         <f>Revenue!H9</f>
-        <v>1794810</v>
+        <v>1790684</v>
       </c>
       <c r="I6" s="94">
         <f>Revenue!I9</f>
@@ -16821,32 +16821,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="257" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="257"/>
+      <c r="K9" s="257"/>
+      <c r="L9" s="257"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="266" t="s">
+      <c r="P9" s="270" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="266"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
-      <c r="V9" s="266"/>
-      <c r="W9" s="266"/>
-      <c r="X9" s="266"/>
-      <c r="Y9" s="266"/>
-      <c r="Z9" s="266"/>
+      <c r="Q9" s="270"/>
+      <c r="R9" s="270"/>
+      <c r="S9" s="270"/>
+      <c r="T9" s="270"/>
+      <c r="U9" s="270"/>
+      <c r="V9" s="270"/>
+      <c r="W9" s="270"/>
+      <c r="X9" s="270"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="H11" s="25">
         <f>H6*H23</f>
-        <v>5384.43</v>
+        <v>5372.0519999999997</v>
       </c>
       <c r="I11" s="25">
         <f t="shared" ref="I11:L11" si="3">I6*I23</f>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="H12" s="25">
         <f>H6*H24</f>
-        <v>179481</v>
+        <v>179068.40000000002</v>
       </c>
       <c r="I12" s="25">
         <f t="shared" ref="I12:L12" si="4">I6*I24</f>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="H13" s="25">
         <f>H6*H25</f>
-        <v>125636.70000000001</v>
+        <v>125347.88</v>
       </c>
       <c r="I13" s="25">
         <f t="shared" ref="I13:L13" si="6">I6*I25</f>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H14" s="127">
         <f>SUM(H11:H13)</f>
-        <v>310502.13</v>
+        <v>309788.33200000005</v>
       </c>
       <c r="I14" s="127">
         <f t="shared" ref="I14:L14" si="7">SUM(I11:I13)</f>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="H15" s="24">
         <f>H6*H27</f>
-        <v>717924</v>
+        <v>716273.60000000009</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" ref="I15:L15" si="8">I6*I27</f>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="H16" s="24">
         <f>H6*H28</f>
-        <v>448702.5</v>
+        <v>447671</v>
       </c>
       <c r="I16" s="24">
         <f t="shared" ref="I16:L16" si="10">I6*I28</f>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="H17" s="24">
         <f>H6*H29</f>
-        <v>215377.19999999998</v>
+        <v>214882.08</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" ref="I17:L17" si="11">I6*I29</f>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="H18" s="127">
         <f>SUM(H15:H17)</f>
-        <v>1382003.7</v>
+        <v>1378826.6800000002</v>
       </c>
       <c r="I18" s="127">
         <f>SUM(I15:I17)</f>
@@ -17695,31 +17695,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="264" t="s">
+      <c r="C21" s="257" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="E21" s="264"/>
-      <c r="F21" s="264"/>
-      <c r="G21" s="264"/>
-      <c r="H21" s="264"/>
-      <c r="I21" s="264"/>
-      <c r="J21" s="264"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="P21" s="266" t="s">
+      <c r="D21" s="257"/>
+      <c r="E21" s="257"/>
+      <c r="F21" s="257"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="257"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="257"/>
+      <c r="L21" s="257"/>
+      <c r="P21" s="270" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="266"/>
-      <c r="R21" s="266"/>
-      <c r="S21" s="266"/>
-      <c r="T21" s="266"/>
-      <c r="U21" s="266"/>
-      <c r="V21" s="266"/>
-      <c r="W21" s="266"/>
-      <c r="X21" s="266"/>
-      <c r="Y21" s="266"/>
-      <c r="Z21" s="266"/>
+      <c r="Q21" s="270"/>
+      <c r="R21" s="270"/>
+      <c r="S21" s="270"/>
+      <c r="T21" s="270"/>
+      <c r="U21" s="270"/>
+      <c r="V21" s="270"/>
+      <c r="W21" s="270"/>
+      <c r="X21" s="270"/>
+      <c r="Y21" s="270"/>
+      <c r="Z21" s="270"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="H26" s="107">
         <f t="shared" si="21"/>
-        <v>0.17300000000000001</v>
+        <v>0.17300000000000004</v>
       </c>
       <c r="I26" s="107">
         <f t="shared" si="21"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="H30" s="107">
         <f t="shared" si="29"/>
-        <v>0.77</v>
+        <v>0.77000000000000013</v>
       </c>
       <c r="I30" s="107">
         <f t="shared" si="29"/>
@@ -18534,60 +18534,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="262"/>
-      <c r="H3" s="263" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="P3" s="267"/>
-      <c r="Q3" s="267"/>
-      <c r="R3" s="267"/>
-      <c r="S3" s="267"/>
-      <c r="T3" s="267"/>
-      <c r="U3" s="267"/>
-      <c r="V3" s="267"/>
-      <c r="W3" s="267"/>
-      <c r="X3" s="267"/>
-      <c r="Y3" s="267"/>
-      <c r="Z3" s="267"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="257" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="267"/>
-      <c r="Q5" s="267"/>
-      <c r="R5" s="267"/>
-      <c r="S5" s="267"/>
-      <c r="T5" s="267"/>
-      <c r="U5" s="267"/>
-      <c r="V5" s="267"/>
-      <c r="W5" s="267"/>
-      <c r="X5" s="267"/>
-      <c r="Y5" s="267"/>
-      <c r="Z5" s="267"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="H7" s="94">
         <f>Revenue!H9</f>
-        <v>1794810</v>
+        <v>1790684</v>
       </c>
       <c r="I7" s="94">
         <f>Revenue!I9</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="H8" s="133">
         <f>'COGS &amp; OpEx'!H14</f>
-        <v>310502.13</v>
+        <v>309788.33200000005</v>
       </c>
       <c r="I8" s="133">
         <f>'COGS &amp; OpEx'!I14</f>
@@ -18773,30 +18773,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="257" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="257"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="267"/>
-      <c r="Q11" s="267"/>
-      <c r="R11" s="267"/>
-      <c r="S11" s="267"/>
-      <c r="T11" s="267"/>
-      <c r="U11" s="267"/>
-      <c r="V11" s="267"/>
-      <c r="W11" s="267"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="256"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="256"/>
+      <c r="W11" s="256"/>
+      <c r="X11" s="256"/>
+      <c r="Y11" s="256"/>
+      <c r="Z11" s="256"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="H13" s="25">
         <f>H20*H7/365</f>
-        <v>639247.39726027392</v>
+        <v>637777.8630136986</v>
       </c>
       <c r="I13" s="25">
         <f>I20*I7/365</f>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H15" s="24">
         <f>H22*H8/365</f>
-        <v>19565.887643835616</v>
+        <v>19520.908591780826</v>
       </c>
       <c r="I15" s="24">
         <f>I22*I8/365</f>
@@ -19038,18 +19038,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="257" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19262,23 +19262,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="267"/>
-      <c r="C25" s="267"/>
+      <c r="B25" s="256"/>
+      <c r="C25" s="256"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="257" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
-      <c r="F26" s="264"/>
-      <c r="G26" s="264"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="264"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
+      <c r="D26" s="257"/>
+      <c r="E26" s="257"/>
+      <c r="F26" s="257"/>
+      <c r="G26" s="257"/>
+      <c r="H26" s="257"/>
+      <c r="I26" s="257"/>
+      <c r="J26" s="257"/>
+      <c r="K26" s="257"/>
+      <c r="L26" s="257"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19351,11 +19351,11 @@
       </c>
       <c r="H28" s="147">
         <f>-(H13-G13)</f>
-        <v>-58542.397260273923</v>
+        <v>-57072.863013698603</v>
       </c>
       <c r="I28" s="147">
         <f t="shared" ref="I28:L29" si="7">-(I13-H13)</f>
-        <v>-54690.608219178161</v>
+        <v>-56160.142465753481</v>
       </c>
       <c r="J28" s="147">
         <f t="shared" si="7"/>
@@ -19441,11 +19441,11 @@
       </c>
       <c r="H30" s="64">
         <f>H15-G15</f>
-        <v>9404.8876438356165</v>
+        <v>9359.9085917808261</v>
       </c>
       <c r="I30" s="64">
         <f t="shared" ref="I30:L30" si="8">I15-H15</f>
-        <v>1060.0850728767109</v>
+        <v>1105.0641249315013</v>
       </c>
       <c r="J30" s="64">
         <f t="shared" si="8"/>
@@ -19470,18 +19470,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="264" t="s">
+      <c r="C33" s="257" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="264"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
+      <c r="D33" s="257"/>
+      <c r="E33" s="257"/>
+      <c r="F33" s="257"/>
+      <c r="G33" s="257"/>
+      <c r="H33" s="257"/>
+      <c r="I33" s="257"/>
+      <c r="J33" s="257"/>
+      <c r="K33" s="257"/>
+      <c r="L33" s="257"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19554,11 +19554,11 @@
       </c>
       <c r="H35" s="147">
         <f>H36+H28+H29+H30</f>
-        <v>-102981.80961643829</v>
+        <v>-101433.47442191777</v>
       </c>
       <c r="I35" s="147">
         <f t="shared" ref="I35:L35" si="10">I36+I28+I29+I30</f>
-        <v>-112081.45514630145</v>
+        <v>-113506.01034082199</v>
       </c>
       <c r="J35" s="147">
         <f t="shared" si="10"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="H36" s="64">
         <f>H7*H37</f>
-        <v>-53844.299999999996</v>
+        <v>-53720.52</v>
       </c>
       <c r="I36" s="64">
         <f>I7*I37</f>
@@ -19665,18 +19665,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="257" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="257"/>
+      <c r="E40" s="257"/>
+      <c r="F40" s="257"/>
+      <c r="G40" s="257"/>
+      <c r="H40" s="257"/>
+      <c r="I40" s="257"/>
+      <c r="J40" s="257"/>
+      <c r="K40" s="257"/>
+      <c r="L40" s="257"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H42" s="25">
         <f>H7*H43</f>
-        <v>17948.100000000002</v>
+        <v>17906.84</v>
       </c>
       <c r="I42" s="25">
         <f>I7*I43</f>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="H45" s="25">
         <f>H7*H46</f>
-        <v>19742.91</v>
+        <v>19697.523999999998</v>
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
@@ -19940,12 +19940,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19953,6 +19947,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19990,60 +19990,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="S2" s="267"/>
-      <c r="T2" s="267"/>
-      <c r="U2" s="267"/>
-      <c r="V2" s="267"/>
-      <c r="W2" s="267"/>
-      <c r="X2" s="267"/>
-      <c r="Y2" s="267"/>
-      <c r="Z2" s="267"/>
-      <c r="AA2" s="267"/>
-      <c r="AB2" s="267"/>
-      <c r="AC2" s="267"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="S4" s="267"/>
-      <c r="T4" s="267"/>
-      <c r="U4" s="267"/>
-      <c r="V4" s="267"/>
-      <c r="W4" s="267"/>
-      <c r="X4" s="267"/>
-      <c r="Y4" s="267"/>
-      <c r="Z4" s="267"/>
-      <c r="AA4" s="267"/>
-      <c r="AB4" s="267"/>
-      <c r="AC4" s="267"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="256"/>
+      <c r="V4" s="256"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="256"/>
+      <c r="Y4" s="256"/>
+      <c r="Z4" s="256"/>
+      <c r="AA4" s="256"/>
+      <c r="AB4" s="256"/>
+      <c r="AC4" s="256"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H6" s="94">
         <f>Revenue!H9</f>
-        <v>1794810</v>
+        <v>1790684</v>
       </c>
       <c r="I6" s="94">
         <f>Revenue!I9</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H7" s="133">
         <f>'COGS &amp; OpEx'!H14</f>
-        <v>310502.13</v>
+        <v>309788.33200000005</v>
       </c>
       <c r="I7" s="133">
         <f>'COGS &amp; OpEx'!I14</f>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H8" s="96">
         <f t="shared" si="1"/>
-        <v>1484307.87</v>
+        <v>1480895.6680000001</v>
       </c>
       <c r="I8" s="96">
         <f t="shared" si="1"/>
@@ -20311,7 +20311,7 @@
       </c>
       <c r="H9" s="133">
         <f>'COGS &amp; OpEx'!H18</f>
-        <v>1382003.7</v>
+        <v>1378826.6800000002</v>
       </c>
       <c r="I9" s="133">
         <f>'COGS &amp; OpEx'!I18</f>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="H10" s="96">
         <f t="shared" si="2"/>
-        <v>102304.17000000016</v>
+        <v>102068.9879999999</v>
       </c>
       <c r="I10" s="96">
         <f t="shared" si="2"/>
@@ -20406,18 +20406,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="257" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
+      <c r="F13" s="257"/>
+      <c r="G13" s="257"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="257"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="257"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20510,18 +20510,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="257" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="H20" s="90">
         <f>'WC &amp; Investments'!H42</f>
-        <v>17948.100000000002</v>
+        <v>17906.84</v>
       </c>
       <c r="I20" s="90">
         <f>'WC &amp; Investments'!I42</f>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="H21" s="90">
         <f>'WC &amp; Investments'!H45</f>
-        <v>19742.91</v>
+        <v>19697.523999999998</v>
       </c>
       <c r="I21" s="90">
         <f>'WC &amp; Investments'!I45</f>
@@ -20690,11 +20690,11 @@
       </c>
       <c r="H22" s="90">
         <f>'WC &amp; Investments'!H35</f>
-        <v>-102981.80961643829</v>
+        <v>-101433.47442191777</v>
       </c>
       <c r="I22" s="90">
         <f>'WC &amp; Investments'!I35</f>
-        <v>-112081.45514630145</v>
+        <v>-113506.01034082199</v>
       </c>
       <c r="J22" s="90">
         <f>'WC &amp; Investments'!J35</f>
@@ -20713,18 +20713,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="264" t="s">
+      <c r="C25" s="257" t="s">
         <v>309</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="E25" s="264"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="264"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="264"/>
-      <c r="J25" s="264"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
+      <c r="D25" s="257"/>
+      <c r="E25" s="257"/>
+      <c r="F25" s="257"/>
+      <c r="G25" s="257"/>
+      <c r="H25" s="257"/>
+      <c r="I25" s="257"/>
+      <c r="J25" s="257"/>
+      <c r="K25" s="257"/>
+      <c r="L25" s="257"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="H27" s="147">
         <f t="shared" si="6"/>
-        <v>80820.294300000125</v>
+        <v>80634.500519999914</v>
       </c>
       <c r="I27" s="147">
         <f t="shared" si="6"/>
@@ -20842,11 +20842,11 @@
       </c>
       <c r="H28" s="96">
         <f t="shared" si="7"/>
-        <v>-23956.32531643816</v>
+        <v>-22589.657901917861</v>
       </c>
       <c r="I28" s="96">
         <f t="shared" si="7"/>
-        <v>-18598.931234301272</v>
+        <v>-20023.486428821809</v>
       </c>
       <c r="J28" s="96">
         <f t="shared" si="7"/>
@@ -20862,18 +20862,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="264" t="s">
+      <c r="C31" s="257" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="E31" s="264"/>
-      <c r="F31" s="264"/>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
+      <c r="D31" s="257"/>
+      <c r="E31" s="257"/>
+      <c r="F31" s="257"/>
+      <c r="G31" s="257"/>
+      <c r="H31" s="257"/>
+      <c r="I31" s="257"/>
+      <c r="J31" s="257"/>
+      <c r="K31" s="257"/>
+      <c r="L31" s="257"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="H34" s="237">
         <f>H10/H6</f>
-        <v>5.7000000000000085E-2</v>
+        <v>5.699999999999994E-2</v>
       </c>
       <c r="I34" s="237">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
@@ -21012,16 +21012,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21084,10 +21084,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="253" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="253"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C11" s="156">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21172,10 +21172,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="253" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="256"/>
+      <c r="C15" s="253"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3668000000000001E-2</v>
+        <v>9.2649599999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.3668000000000001E-2</v>
+        <v>9.2649599999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21264,60 +21264,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="262"/>
-      <c r="H3" s="263" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="P3" s="267"/>
-      <c r="Q3" s="267"/>
-      <c r="R3" s="267"/>
-      <c r="S3" s="267"/>
-      <c r="T3" s="267"/>
-      <c r="U3" s="267"/>
-      <c r="V3" s="267"/>
-      <c r="W3" s="267"/>
-      <c r="X3" s="267"/>
-      <c r="Y3" s="267"/>
-      <c r="Z3" s="267"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="257" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="267"/>
-      <c r="Q5" s="267"/>
-      <c r="R5" s="267"/>
-      <c r="S5" s="267"/>
-      <c r="T5" s="267"/>
-      <c r="U5" s="267"/>
-      <c r="V5" s="267"/>
-      <c r="W5" s="267"/>
-      <c r="X5" s="267"/>
-      <c r="Y5" s="267"/>
-      <c r="Z5" s="267"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21404,11 +21404,11 @@
       </c>
       <c r="H7" s="133">
         <f>'FCF &amp; Other'!H28</f>
-        <v>-23956.32531643816</v>
+        <v>-22589.657901917861</v>
       </c>
       <c r="I7" s="133">
         <f>'FCF &amp; Other'!I28</f>
-        <v>-18598.931234301272</v>
+        <v>-20023.486428821809</v>
       </c>
       <c r="J7" s="133">
         <f>'FCF &amp; Other'!J28</f>
@@ -21524,11 +21524,11 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f>H7/(1+$C$15)^H9</f>
-        <v>-21778.477560398325</v>
+        <v>-20536.052638107143</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>-15371.017549009313</v>
+        <v>-16548.335891588267</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" si="0"/>
@@ -21563,10 +21563,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="256" t="s">
+      <c r="B13" s="253" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="256"/>
+      <c r="C13" s="253"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21586,10 +21586,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="256" t="s">
+      <c r="B18" s="253" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="256"/>
+      <c r="C18" s="253"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="C19" s="64">
         <f>SUM(H10:L10)</f>
-        <v>206294.91578958137</v>
+        <v>206360.02236929361</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C21" s="96">
         <f>C19+C20</f>
-        <v>1787576.4733078817</v>
+        <v>1787641.5798875941</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C24" s="96">
         <f>C21+C22-C23</f>
-        <v>3192601.4733078815</v>
+        <v>3192666.5798875941</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C26" s="163">
         <f>C24/C25</f>
-        <v>6.0867686783178394</v>
+        <v>6.0868928055205176</v>
       </c>
     </row>
   </sheetData>
@@ -21703,37 +21703,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="257" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="H6" s="94">
         <f>Revenue!H9</f>
-        <v>1794810</v>
+        <v>1790684</v>
       </c>
       <c r="I6" s="94">
         <f>Revenue!I9</f>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="H7" s="94">
         <f>'FCF &amp; Other'!H10</f>
-        <v>102304.17000000016</v>
+        <v>102068.9879999999</v>
       </c>
       <c r="I7" s="94">
         <f>'FCF &amp; Other'!I10</f>
@@ -21898,11 +21898,11 @@
       </c>
       <c r="H8" s="94">
         <f>'FCF &amp; Other'!H28</f>
-        <v>-23956.32531643816</v>
+        <v>-22589.657901917861</v>
       </c>
       <c r="I8" s="94">
         <f>'FCF &amp; Other'!I28</f>
-        <v>-18598.931234301272</v>
+        <v>-20023.486428821809</v>
       </c>
       <c r="J8" s="94">
         <f>'FCF &amp; Other'!J28</f>
@@ -21922,18 +21922,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="264" t="s">
+      <c r="C10" s="257" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="264"/>
-      <c r="E10" s="264"/>
-      <c r="F10" s="264"/>
-      <c r="G10" s="264"/>
-      <c r="H10" s="264"/>
-      <c r="I10" s="264"/>
-      <c r="J10" s="264"/>
-      <c r="K10" s="264"/>
-      <c r="L10" s="264"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="257"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="257"/>
+      <c r="H10" s="257"/>
+      <c r="I10" s="257"/>
+      <c r="J10" s="257"/>
+      <c r="K10" s="257"/>
+      <c r="L10" s="257"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22005,11 +22005,11 @@
       </c>
       <c r="H12" s="97">
         <f t="shared" si="1"/>
-        <v>0.11439289892038357</v>
+        <v>0.11183107616424476</v>
       </c>
       <c r="I12" s="97">
         <f t="shared" si="1"/>
-        <v>8.5554682668360388E-2</v>
+        <v>8.8055960739024816E-2</v>
       </c>
       <c r="J12" s="97">
         <f t="shared" si="1"/>
@@ -22054,11 +22054,11 @@
       </c>
       <c r="H13" s="97">
         <f t="shared" si="2"/>
-        <v>0.80239904862579559</v>
+        <v>0.79825560253699601</v>
       </c>
       <c r="I13" s="97">
         <f t="shared" si="2"/>
-        <v>0.18077877763926953</v>
+        <v>0.18349946606701284</v>
       </c>
       <c r="J13" s="97">
         <f t="shared" si="2"/>
@@ -22103,15 +22103,15 @@
       </c>
       <c r="H14" s="97">
         <f t="shared" si="3"/>
-        <v>0.74656364051754898</v>
+        <v>0.7610217516670772</v>
       </c>
       <c r="I14" s="97">
         <f t="shared" si="3"/>
-        <v>0.2236317136026198</v>
+        <v>0.11359939509655807</v>
       </c>
       <c r="J14" s="97">
         <f t="shared" si="3"/>
-        <v>4.4213688093055454</v>
+        <v>4.1779582161007971</v>
       </c>
       <c r="K14" s="97">
         <f t="shared" si="3"/>
@@ -22127,18 +22127,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="264" t="s">
+      <c r="C16" s="257" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="264"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="264"/>
-      <c r="G16" s="264"/>
-      <c r="H16" s="264"/>
-      <c r="I16" s="264"/>
-      <c r="J16" s="264"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="264"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="257"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22272,18 +22272,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="264" t="s">
+      <c r="C21" s="257" t="s">
         <v>238</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="E21" s="264"/>
-      <c r="F21" s="264"/>
-      <c r="G21" s="264"/>
-      <c r="H21" s="264"/>
-      <c r="I21" s="264"/>
-      <c r="J21" s="264"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
+      <c r="D21" s="257"/>
+      <c r="E21" s="257"/>
+      <c r="F21" s="257"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="257"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="257"/>
+      <c r="L21" s="257"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22367,18 +22367,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="257" t="s">
         <v>239</v>
       </c>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
-      <c r="F26" s="264"/>
-      <c r="G26" s="264"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="264"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
+      <c r="D26" s="257"/>
+      <c r="E26" s="257"/>
+      <c r="F26" s="257"/>
+      <c r="G26" s="257"/>
+      <c r="H26" s="257"/>
+      <c r="I26" s="257"/>
+      <c r="J26" s="257"/>
+      <c r="K26" s="257"/>
+      <c r="L26" s="257"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22648,10 +22648,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="253" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="256"/>
+      <c r="C37" s="253"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22744,10 +22744,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="256" t="s">
+      <c r="B49" s="253" t="s">
         <v>249</v>
       </c>
-      <c r="C49" s="256"/>
+      <c r="C49" s="253"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22803,10 +22803,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="256" t="s">
+      <c r="B57" s="253" t="s">
         <v>373</v>
       </c>
-      <c r="C57" s="256"/>
+      <c r="C57" s="253"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22946,10 +22946,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="253" t="s">
         <v>254</v>
       </c>
-      <c r="C4" s="256"/>
+      <c r="C4" s="253"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="C5" s="154">
         <f>DCF!C26</f>
-        <v>6.0867686783178394</v>
+        <v>6.0868928055205176</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="C9" s="163">
         <f>AVERAGE(C5:C8)</f>
-        <v>13.047072100701815</v>
+        <v>13.047103132502485</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-5.1122029039868011E-2</v>
+        <v>-5.1119772181637428E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23068,37 +23068,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="256" t="s">
+      <c r="C2" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="257" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23211,18 +23211,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="257" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="257"/>
+      <c r="K9" s="257"/>
+      <c r="L9" s="257"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23343,18 +23343,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="264" t="s">
+      <c r="C14" s="257" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="264"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="264"/>
-      <c r="G14" s="264"/>
-      <c r="H14" s="264"/>
-      <c r="I14" s="264"/>
-      <c r="J14" s="264"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="257"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="257"/>
+      <c r="J14" s="257"/>
+      <c r="K14" s="257"/>
+      <c r="L14" s="257"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23444,10 +23444,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="256" t="s">
+      <c r="B20" s="253" t="s">
         <v>422</v>
       </c>
-      <c r="C20" s="256"/>
+      <c r="C20" s="253"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23548,60 +23548,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="256" t="s">
+      <c r="C3" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="262"/>
-      <c r="H3" s="263" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="P3" s="267"/>
-      <c r="Q3" s="267"/>
-      <c r="R3" s="267"/>
-      <c r="S3" s="267"/>
-      <c r="T3" s="267"/>
-      <c r="U3" s="267"/>
-      <c r="V3" s="267"/>
-      <c r="W3" s="267"/>
-      <c r="X3" s="267"/>
-      <c r="Y3" s="267"/>
-      <c r="Z3" s="267"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="257" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="267"/>
-      <c r="Q5" s="267"/>
-      <c r="R5" s="267"/>
-      <c r="S5" s="267"/>
-      <c r="T5" s="267"/>
-      <c r="U5" s="267"/>
-      <c r="V5" s="267"/>
-      <c r="W5" s="267"/>
-      <c r="X5" s="267"/>
-      <c r="Y5" s="267"/>
-      <c r="Z5" s="267"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23687,23 +23687,23 @@
       </c>
       <c r="H7" s="147">
         <f>G7*(1+$C$17)</f>
-        <v>17600</v>
+        <v>19200</v>
       </c>
       <c r="I7" s="147">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>38720</v>
+        <v>46080</v>
       </c>
       <c r="J7" s="147">
         <f t="shared" si="0"/>
-        <v>85184</v>
+        <v>110592</v>
       </c>
       <c r="K7" s="147">
         <f t="shared" si="0"/>
-        <v>187404.80000000002</v>
+        <v>265420.79999999999</v>
       </c>
       <c r="L7" s="147">
         <f t="shared" si="0"/>
-        <v>412290.56000000006</v>
+        <v>637009.91999999993</v>
       </c>
       <c r="N7" s="93"/>
       <c r="O7" s="16"/>
@@ -23735,7 +23735,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>5256704.6400000006</v>
+        <v>8121876.4799999986</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -23789,23 +23789,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f>H7/(1+$C$21)^H9</f>
-        <v>15999.999999999998</v>
+        <v>17454.545454545452</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>31999.999999999996</v>
+        <v>38082.644628099166</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" si="1"/>
-        <v>63999.999999999978</v>
+        <v>83089.40646130727</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" si="1"/>
-        <v>127999.99999999997</v>
+        <v>181285.9777337613</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" si="1"/>
-        <v>255999.99999999994</v>
+        <v>395533.04232820641</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -23824,15 +23824,15 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f>L8/(1+C21)^L9</f>
-        <v>3263999.9999999991</v>
+        <v>5043046.2896846319</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="268" t="s">
+      <c r="B14" s="258" t="s">
         <v>262</v>
       </c>
-      <c r="C14" s="269"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="176" t="s">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="C16" s="177">
         <f>C36</f>
-        <v>9.910708118106669</v>
+        <v>13.745436887017615</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23857,22 +23857,22 @@
         <v>375</v>
       </c>
       <c r="C17" s="179">
-        <v>1.2</v>
-      </c>
-      <c r="E17" s="270" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E17" s="260" t="s">
         <v>265</v>
       </c>
-      <c r="F17" s="270"/>
-      <c r="G17" s="270"/>
-      <c r="H17" s="270"/>
-      <c r="I17" s="270"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="260"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="268" t="s">
+      <c r="B19" s="258" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="269"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="180" t="s">
@@ -23938,10 +23938,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="268" t="s">
+      <c r="B28" s="258" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="269"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="C29" s="182">
         <f>SUM(H10:L10)</f>
-        <v>495999.99999999988</v>
+        <v>715445.61660591955</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="C30" s="182">
         <f>L11</f>
-        <v>3263999.9999999991</v>
+        <v>5043046.2896846319</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="C31" s="185">
         <f>C29+C30</f>
-        <v>3759999.9999999991</v>
+        <v>5758491.9062905516</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="C34" s="185">
         <f>C31+C32-C33</f>
-        <v>5165024.9999999991</v>
+        <v>7163516.9062905516</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24012,22 +24012,22 @@
       </c>
       <c r="C36" s="188">
         <f>C34/C35</f>
-        <v>9.910708118106669</v>
+        <v>13.745436887017615</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="264" t="s">
+      <c r="C39" s="257" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="E39" s="264"/>
-      <c r="F39" s="264"/>
-      <c r="G39" s="264"/>
-      <c r="H39" s="264"/>
-      <c r="I39" s="264"/>
-      <c r="J39" s="264"/>
-      <c r="K39" s="264"/>
-      <c r="L39" s="264"/>
+      <c r="D39" s="257"/>
+      <c r="E39" s="257"/>
+      <c r="F39" s="257"/>
+      <c r="G39" s="257"/>
+      <c r="H39" s="257"/>
+      <c r="I39" s="257"/>
+      <c r="J39" s="257"/>
+      <c r="K39" s="257"/>
+      <c r="L39" s="257"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24097,23 +24097,23 @@
       </c>
       <c r="H41" s="164">
         <f t="shared" si="2"/>
-        <v>17600</v>
+        <v>19200</v>
       </c>
       <c r="I41" s="164">
         <f t="shared" si="2"/>
-        <v>38720</v>
+        <v>46080</v>
       </c>
       <c r="J41" s="164">
         <f t="shared" si="2"/>
-        <v>85184</v>
+        <v>110592</v>
       </c>
       <c r="K41" s="164">
         <f t="shared" si="2"/>
-        <v>187404.80000000002</v>
+        <v>265420.79999999999</v>
       </c>
       <c r="L41" s="164">
         <f t="shared" si="2"/>
-        <v>412290.56000000006</v>
+        <v>637009.91999999993</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -24142,23 +24142,23 @@
       </c>
       <c r="H42" s="164">
         <f>H41/H43</f>
-        <v>15999.999999999998</v>
+        <v>17454.545454545452</v>
       </c>
       <c r="I42" s="164">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>35200</v>
+        <v>41890.909090909088</v>
       </c>
       <c r="J42" s="164">
         <f t="shared" si="3"/>
-        <v>77440</v>
+        <v>100538.18181818181</v>
       </c>
       <c r="K42" s="164">
         <f t="shared" si="3"/>
-        <v>170368</v>
+        <v>241291.63636363632</v>
       </c>
       <c r="L42" s="164">
         <f t="shared" si="3"/>
-        <v>374809.60000000003</v>
+        <v>579099.92727272713</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -24227,23 +24227,23 @@
       </c>
       <c r="H44" s="164">
         <f>H41/H45</f>
-        <v>1760000</v>
+        <v>1920000</v>
       </c>
       <c r="I44" s="164">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>1936000</v>
+        <v>2304000</v>
       </c>
       <c r="J44" s="164">
         <f t="shared" si="5"/>
-        <v>2028190.476190476</v>
+        <v>2633142.8571428568</v>
       </c>
       <c r="K44" s="164">
         <f t="shared" si="5"/>
-        <v>2677211.4285714286</v>
+        <v>3791725.7142857136</v>
       </c>
       <c r="L44" s="164">
         <f t="shared" si="5"/>
-        <v>2748603.7333333339</v>
+        <v>4246732.7999999998</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -24309,23 +24309,23 @@
       </c>
       <c r="H46" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="I46" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="J46" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="K46" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="L46" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
@@ -24351,23 +24351,23 @@
       </c>
       <c r="H47" s="190">
         <f t="shared" si="7"/>
-        <v>-0.71811134601832283</v>
+        <v>-0.69248510474726122</v>
       </c>
       <c r="I47" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000004</v>
       </c>
       <c r="J47" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="K47" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
       <c r="L47" s="190">
         <f t="shared" si="7"/>
-        <v>1.2000000000000002</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
@@ -24393,23 +24393,23 @@
       </c>
       <c r="H48" s="190">
         <f t="shared" si="8"/>
-        <v>9.2779459719900759E-2</v>
+        <v>0.19212304696716442</v>
       </c>
       <c r="I48" s="190">
         <f t="shared" si="8"/>
-        <v>0.10000000000000009</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="J48" s="190">
         <f t="shared" si="8"/>
-        <v>4.761904761904745E-2</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="K48" s="190">
         <f t="shared" si="8"/>
-        <v>0.32000000000000006</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="L48" s="190">
         <f t="shared" si="8"/>
-        <v>2.6666666666666838E-2</v>
+        <v>0.12000000000000011</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -24450,26 +24450,26 @@
       </c>
       <c r="K49" s="190">
         <f t="shared" si="9"/>
-        <v>6.363636363636363E-2</v>
+        <v>6.3636363636363644E-2</v>
       </c>
       <c r="L49" s="190">
         <f t="shared" si="9"/>
-        <v>0.13636363636363635</v>
+        <v>0.13636363636363633</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24813,7 +24813,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="22">
-        <f t="shared" ref="T7:Z7" si="2">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="2">T5-T6</f>
         <v>290890</v>
       </c>
       <c r="U7" s="22">
@@ -25091,19 +25091,19 @@
         <v>1282828</v>
       </c>
       <c r="T11" s="24">
-        <f t="shared" ref="T11:U11" si="5">SUM(T8:T10)</f>
+        <f t="shared" ref="T11" si="5">SUM(T8:T10)</f>
         <v>334254</v>
       </c>
       <c r="U11" s="24">
-        <f t="shared" ref="U11:V11" si="6">SUM(U8:U10)</f>
+        <f t="shared" ref="U11" si="6">SUM(U8:U10)</f>
         <v>325503</v>
       </c>
       <c r="V11" s="24">
-        <f t="shared" ref="V11:W11" si="7">SUM(V8:V10)</f>
+        <f t="shared" ref="V11" si="7">SUM(V8:V10)</f>
         <v>309179</v>
       </c>
       <c r="W11" s="24">
-        <f t="shared" ref="W11:X11" si="8">SUM(W8:W10)</f>
+        <f t="shared" ref="W11" si="8">SUM(W8:W10)</f>
         <v>317533</v>
       </c>
       <c r="X11" s="24">
@@ -25119,7 +25119,7 @@
         <v>313467</v>
       </c>
       <c r="AA11" s="24">
-        <f t="shared" ref="Z11:AA11" si="10">SUM(AA8:AA10)</f>
+        <f t="shared" ref="AA11" si="10">SUM(AA8:AA10)</f>
         <v>298065</v>
       </c>
       <c r="AC11" s="24">
@@ -25704,7 +25704,7 @@
         <v>523584</v>
       </c>
       <c r="AA20" s="25">
-        <f t="shared" ref="T20:AA20" si="13">AA19*AA$85</f>
+        <f t="shared" ref="AA20" si="13">AA19*AA$85</f>
         <v>519654</v>
       </c>
       <c r="AC20" s="25">
@@ -25863,7 +25863,7 @@
         <v>527818</v>
       </c>
       <c r="AA22" s="25">
-        <f t="shared" ref="T22:AA22" si="16">AA21*AA$85</f>
+        <f t="shared" ref="AA22" si="16">AA21*AA$85</f>
         <v>523013</v>
       </c>
       <c r="AC22" s="25">
@@ -25992,7 +25992,7 @@
         <v>0.04</v>
       </c>
       <c r="AA24" s="65">
-        <f t="shared" ref="T24:AA24" si="18">AA23/AA$85</f>
+        <f t="shared" ref="AA24" si="18">AA23/AA$85</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AC24" s="65">
@@ -26124,7 +26124,7 @@
         <v>0.04</v>
       </c>
       <c r="AA26" s="66">
-        <f t="shared" ref="T26:AA26" si="20">AA25/AA$85</f>
+        <f t="shared" ref="AA26" si="20">AA25/AA$85</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AB26" s="1"/>
@@ -26636,7 +26636,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="35">
-        <f t="shared" ref="T36:Z36" si="23">T37-T32</f>
+        <f t="shared" ref="T36:Y36" si="23">T37-T32</f>
         <v>486813</v>
       </c>
       <c r="U36" s="35">
@@ -27015,7 +27015,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="35">
-        <f t="shared" ref="T42:Z42" si="26">T43-T40</f>
+        <f t="shared" ref="T42:Y42" si="26">T43-T40</f>
         <v>235973</v>
       </c>
       <c r="U42" s="35">
@@ -28473,7 +28473,7 @@
         <v>22525</v>
       </c>
       <c r="AA69" s="64">
-        <f t="shared" ref="T69:AA69" si="32">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
+        <f t="shared" ref="AA69" si="32">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
         <v>36089</v>
       </c>
       <c r="AC69" s="64">
@@ -28549,7 +28549,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="40">
-        <f t="shared" ref="T70:Z70" si="34">T18-T69</f>
+        <f t="shared" ref="T70:Y70" si="34">T18-T69</f>
         <v>0</v>
       </c>
       <c r="U70" s="40">
@@ -28684,7 +28684,7 @@
         <v>0</v>
       </c>
       <c r="AA71" s="42">
-        <f t="shared" ref="T71:AA71" si="38">AA37-(AA43+AA112)</f>
+        <f t="shared" ref="AA71" si="38">AA37-(AA43+AA112)</f>
         <v>0</v>
       </c>
       <c r="AB71" s="16"/>
@@ -28771,7 +28771,7 @@
         <v>534750</v>
       </c>
       <c r="Y74" s="21">
-        <f t="shared" ref="Y74:Z74" si="39">459231+64691</f>
+        <f t="shared" ref="Y74" si="39">459231+64691</f>
         <v>523922</v>
       </c>
       <c r="Z74" s="21">
@@ -28822,19 +28822,19 @@
         <v>523922</v>
       </c>
       <c r="T75" s="25">
-        <f t="shared" ref="T75:U75" si="41">T74*T85</f>
+        <f t="shared" ref="T75" si="41">T74*T85</f>
         <v>549599</v>
       </c>
       <c r="U75" s="25">
-        <f t="shared" ref="U75:V75" si="42">U74*U85</f>
+        <f t="shared" ref="U75" si="42">U74*U85</f>
         <v>551493</v>
       </c>
       <c r="V75" s="25">
-        <f t="shared" ref="V75:W75" si="43">V74*V85</f>
+        <f t="shared" ref="V75" si="43">V74*V85</f>
         <v>535039</v>
       </c>
       <c r="W75" s="25">
-        <f t="shared" ref="W75:X75" si="44">W74*W85</f>
+        <f t="shared" ref="W75" si="44">W74*W85</f>
         <v>531022</v>
       </c>
       <c r="X75" s="25">
@@ -28850,7 +28850,7 @@
         <v>518121</v>
       </c>
       <c r="AA75" s="25">
-        <f t="shared" ref="Z75:AA75" si="46">AA74*AA85</f>
+        <f t="shared" ref="AA75" si="46">AA74*AA85</f>
         <v>521156</v>
       </c>
       <c r="AC75" s="24">
@@ -28951,7 +28951,7 @@
         <v>6735</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" ref="T77:Z77" si="48">T76*T85</f>
+        <f t="shared" ref="T77:Y77" si="48">T76*T85</f>
         <v>0</v>
       </c>
       <c r="U77" s="25">
@@ -29022,7 +29022,7 @@
         <v>530657</v>
       </c>
       <c r="T78" s="25">
-        <f t="shared" ref="T78:Z78" si="51">T75+T77</f>
+        <f t="shared" ref="T78:Y78" si="51">T75+T77</f>
         <v>549599</v>
       </c>
       <c r="U78" s="25">
@@ -29245,19 +29245,19 @@
         <v>0</v>
       </c>
       <c r="T82" s="45">
-        <f t="shared" ref="T82:U82" si="55">T81/T85</f>
+        <f t="shared" ref="T82" si="55">T81/T85</f>
         <v>0</v>
       </c>
       <c r="U82" s="45">
-        <f t="shared" ref="U82:V82" si="56">U81/U85</f>
+        <f t="shared" ref="U82" si="56">U81/U85</f>
         <v>0</v>
       </c>
       <c r="V82" s="45">
-        <f t="shared" ref="V82:W82" si="57">V81/V85</f>
+        <f t="shared" ref="V82" si="57">V81/V85</f>
         <v>0</v>
       </c>
       <c r="W82" s="45">
-        <f t="shared" ref="W82:X82" si="58">W81/W85</f>
+        <f t="shared" ref="W82" si="58">W81/W85</f>
         <v>0</v>
       </c>
       <c r="X82" s="45">
@@ -29273,7 +29273,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="45">
-        <f t="shared" ref="Z82:AA82" si="60">AA81/AA85</f>
+        <f t="shared" ref="AA82" si="60">AA81/AA85</f>
         <v>0</v>
       </c>
       <c r="AC82" s="72">
@@ -29374,7 +29374,7 @@
         <v>0.45018062878344073</v>
       </c>
       <c r="AA83" s="46">
-        <f t="shared" ref="T83:AA83" si="63">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
+        <f t="shared" ref="AA83" si="63">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
         <v>0.31720745435625769</v>
       </c>
       <c r="AC83" s="46">
@@ -29585,7 +29585,7 @@
         <v>-0.13037640275448081</v>
       </c>
       <c r="AA89" s="48">
-        <f t="shared" ref="T89:AA96" si="72">IF(Z5=0,
+        <f t="shared" ref="AA89:AA96" si="72">IF(Z5=0,
 IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
 (AA5-Z5)/ABS(Z5)
 )</f>
@@ -30186,7 +30186,7 @@
         <v>-0.55680084814522324</v>
       </c>
       <c r="AA97" s="52">
-        <f t="shared" ref="T97:AA97" si="80">IF(Z15=0,
+        <f t="shared" ref="AA97" si="80">IF(Z15=0,
 IF(AA15=0,0,IF(AA15&gt;0,1,-1)),
 (AA15-Z15)/ABS(Z15)
 )</f>
@@ -30299,7 +30299,7 @@
         <v>-0.78437135034749483</v>
       </c>
       <c r="AA98" s="52">
-        <f t="shared" ref="T98:AA98" si="88">IF(Z18=0,
+        <f t="shared" ref="AA98" si="88">IF(Z18=0,
 IF(AA18=0,0,IF(AA18&gt;0,1,-1)),
 (AA18-Z18)/ABS(Z18)
 )</f>
@@ -30387,7 +30387,7 @@
         <v>0.81612975701631518</v>
       </c>
       <c r="AA101" s="50">
-        <f t="shared" ref="T101:AA101" si="90">AA7/AA5</f>
+        <f t="shared" ref="AA101" si="90">AA7/AA5</f>
         <v>0.80356899106899105</v>
       </c>
       <c r="AC101" s="50">
@@ -30458,7 +30458,7 @@
         <v>6.689341319655244E-2</v>
       </c>
       <c r="AA102" s="50">
-        <f t="shared" ref="T102:AA102" si="92">AA12/AA5</f>
+        <f t="shared" ref="AA102" si="92">AA12/AA5</f>
         <v>7.703482703482703E-2</v>
       </c>
       <c r="AC102" s="50">
@@ -30532,7 +30532,7 @@
         <v>5.3838358246769698E-2</v>
       </c>
       <c r="AA103" s="55">
-        <f t="shared" ref="T103:AA103" si="94">AA111/AA5</f>
+        <f t="shared" ref="AA103" si="94">AA111/AA5</f>
         <v>8.7967025467025464E-2</v>
       </c>
       <c r="AB103" s="1"/>
@@ -30650,7 +30650,7 @@
         <v>0.45018062878344073</v>
       </c>
       <c r="AA106" s="81">
-        <f t="shared" ref="T106:AA106" si="97">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
+        <f t="shared" ref="AA106" si="97">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
         <v>0.31720745435625769</v>
       </c>
       <c r="AC106" s="81">
@@ -30721,7 +30721,7 @@
         <v>1415746</v>
       </c>
       <c r="AA107" s="25">
-        <f t="shared" ref="T107:AA107" si="100">AA29+AA34</f>
+        <f t="shared" ref="AA107" si="100">AA29+AA34</f>
         <v>1405025</v>
       </c>
       <c r="AC107" s="25">
@@ -30812,7 +30812,7 @@
         <v>0</v>
       </c>
       <c r="AA108" s="25">
-        <f t="shared" ref="T108:AA108" si="102">AA39+AA41</f>
+        <f t="shared" ref="AA108" si="102">AA39+AA41</f>
         <v>0</v>
       </c>
       <c r="AC108" s="25">
@@ -30930,7 +30930,7 @@
         <v>-2684</v>
       </c>
       <c r="AA110" s="147">
-        <f t="shared" ref="T110:AA110" si="104">AA60+AA61</f>
+        <f t="shared" ref="AA110" si="104">AA60+AA61</f>
         <v>-1389</v>
       </c>
       <c r="AC110" s="147">
@@ -31001,7 +31001,7 @@
         <v>22525</v>
       </c>
       <c r="AA111" s="147">
-        <f t="shared" ref="T111:AA111" si="106">AA17+AA18</f>
+        <f t="shared" ref="AA111" si="106">AA17+AA18</f>
         <v>36089</v>
       </c>
       <c r="AC111" s="147">
@@ -31072,7 +31072,7 @@
         <v>1902965</v>
       </c>
       <c r="AA112" s="147">
-        <f t="shared" ref="T112:AA112" si="108">AA49+AA48</f>
+        <f t="shared" ref="AA112" si="108">AA49+AA48</f>
         <v>1948551</v>
       </c>
       <c r="AC112" s="147">
@@ -31226,7 +31226,7 @@
         <v>10.3</v>
       </c>
       <c r="AA117" s="65">
-        <f t="shared" ref="T117:AA117" si="110">AA116/AA85</f>
+        <f t="shared" ref="AA117" si="110">AA116/AA85</f>
         <v>12.76</v>
       </c>
       <c r="AC117" s="65">
@@ -31621,7 +31621,7 @@
         <v>410256</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" ref="T131:AA131" si="120">AB5</f>
+        <f t="shared" ref="AA131" si="120">AB5</f>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -31646,7 +31646,7 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="246" t="str">
-        <f t="shared" ref="T132:Z132" si="121">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Y132" si="121">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U132" s="246" t="str">
@@ -31817,7 +31817,7 @@
         <v>1937722</v>
       </c>
       <c r="AA135" s="25">
-        <f t="shared" ref="T135:AA135" si="129">AB213</f>
+        <f t="shared" ref="AA135" si="129">AB213</f>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -31842,7 +31842,7 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="246" t="str">
-        <f t="shared" ref="T136:Z136" si="130">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Y136" si="130">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U136" s="246" t="str">
@@ -32007,7 +32007,7 @@
         <v>64.534109976050601</v>
       </c>
       <c r="AA141" s="139">
-        <f t="shared" ref="T141:AA141" si="133">AA30/AA5*90</f>
+        <f t="shared" ref="AA141" si="133">AA30/AA5*90</f>
         <v>67.372762372762367</v>
       </c>
       <c r="AC141" s="139">
@@ -32068,7 +32068,7 @@
         <v>0</v>
       </c>
       <c r="AA142" s="139">
-        <f t="shared" ref="T142:AA142" si="135">AA31/AA6*365</f>
+        <f t="shared" ref="AA142" si="135">AA31/AA6*365</f>
         <v>0</v>
       </c>
       <c r="AC142" s="139">
@@ -32129,7 +32129,7 @@
         <v>23.046355033277873</v>
       </c>
       <c r="AA143" s="139">
-        <f t="shared" ref="T143:AA143" si="137">AA38/AA6*90</f>
+        <f t="shared" ref="AA143" si="137">AA38/AA6*90</f>
         <v>18.409420874334572</v>
       </c>
       <c r="AC143" s="139">
@@ -32162,19 +32162,19 @@
         <v>117.91746855390694</v>
       </c>
       <c r="T144" s="139">
-        <f t="shared" ref="T144:U144" si="139">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="139">T141+T142-T143</f>
         <v>87.187137429695923</v>
       </c>
       <c r="U144" s="139">
-        <f t="shared" ref="U144:V144" si="140">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="140">U141+U142-U143</f>
         <v>68.419460331074703</v>
       </c>
       <c r="V144" s="139">
-        <f t="shared" ref="V144:W144" si="141">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="141">V141+V142-V143</f>
         <v>69.519655214399876</v>
       </c>
       <c r="W144" s="139">
-        <f t="shared" ref="W144:X144" si="142">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="142">W141+W142-W143</f>
         <v>68.744825768278702</v>
       </c>
       <c r="X144" s="139">
@@ -32190,7 +32190,7 @@
         <v>41.487754942772725</v>
       </c>
       <c r="AA144" s="139">
-        <f t="shared" ref="Z144:AA144" si="144">AA141+AA142-AA143</f>
+        <f t="shared" ref="AA144" si="144">AA141+AA142-AA143</f>
         <v>48.963341498427795</v>
       </c>
       <c r="AC144" s="139">
@@ -32251,7 +32251,7 @@
         <v>0</v>
       </c>
       <c r="AA145" s="139">
-        <f t="shared" ref="T145:AA145" si="147">AA108/AA49</f>
+        <f t="shared" ref="AA145" si="147">AA108/AA49</f>
         <v>0</v>
       </c>
       <c r="AC145" s="139">
@@ -32312,7 +32312,7 @@
         <v>-0.74396849127545694</v>
       </c>
       <c r="AA146" s="200">
-        <f t="shared" ref="T146:AA146" si="149">(AA108-AA107)/AA49</f>
+        <f t="shared" ref="AA146" si="149">(AA108-AA107)/AA49</f>
         <v>-0.72106144514564929</v>
       </c>
       <c r="AC146" s="200">
@@ -32373,7 +32373,7 @@
         <v>2.063021693804965</v>
       </c>
       <c r="AA147" s="139">
-        <f t="shared" ref="T147:AA147" si="151">(AA107+AA30)/AA40</f>
+        <f t="shared" ref="AA147" si="151">(AA107+AA30)/AA40</f>
         <v>2.1209291205537757</v>
       </c>
       <c r="AC147" s="139">
@@ -32434,7 +32434,7 @@
         <v>2.3066495444084523</v>
       </c>
       <c r="AA148" s="139">
-        <f t="shared" ref="T148:AA148" si="153">AA32/AA40</f>
+        <f t="shared" ref="AA148" si="153">AA32/AA40</f>
         <v>2.386634756174606</v>
       </c>
       <c r="AC148" s="139">
@@ -32495,7 +32495,7 @@
         <v>N/A</v>
       </c>
       <c r="AA149" s="202" t="str">
-        <f t="shared" ref="T149:AA149" si="155">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
+        <f t="shared" ref="AA149" si="155">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
         <v>N/A</v>
       </c>
       <c r="AC149" s="202" t="str">
@@ -32752,7 +32752,7 @@
         <v>3964510.5</v>
       </c>
       <c r="AA154" s="164">
-        <f t="shared" ref="T154:AA154" si="157">AA153+AA108-AA107+AA48+AA45</f>
+        <f t="shared" ref="AA154" si="157">AA153+AA108-AA107+AA48+AA45</f>
         <v>5287786.3999999994</v>
       </c>
       <c r="AC154" s="164">
@@ -32887,7 +32887,7 @@
         <v>75934</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" ref="T157:AA157" si="159">AA59-AA54+AA110+AA65</f>
+        <f t="shared" ref="AA157" si="159">AA59-AA54+AA110+AA65</f>
         <v>-15652</v>
       </c>
       <c r="AC157" s="64">
@@ -33466,7 +33466,7 @@
         <v>2.732462108272006</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" ref="T172:AA172" si="166">AA107/AA75</f>
+        <f t="shared" ref="AA172" si="166">AA107/AA75</f>
         <v>2.6959777878408766</v>
       </c>
       <c r="AC172" s="72">
@@ -33527,7 +33527,7 @@
         <v>0.40408404584318719</v>
       </c>
       <c r="AA173" s="175">
-        <f t="shared" ref="T173:AA173" si="168">AA54/AA59</f>
+        <f t="shared" ref="AA173" si="168">AA54/AA59</f>
         <v>1.4646079676862438</v>
       </c>
       <c r="AC173" s="175">
@@ -33588,7 +33588,7 @@
         <v>0.1274194396508454</v>
       </c>
       <c r="AA174" s="175">
-        <f t="shared" ref="T174:AA174" si="170">AA54/AA5</f>
+        <f t="shared" ref="AA174" si="170">AA54/AA5</f>
         <v>0.1095949845949846</v>
       </c>
       <c r="AC174" s="175">
@@ -33649,7 +33649,7 @@
         <v>2.732462108272006</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" ref="T175:AA175" si="172">(AA107-AA108)/AA75</f>
+        <f t="shared" ref="AA175" si="172">(AA107-AA108)/AA75</f>
         <v>2.6959777878408766</v>
       </c>
       <c r="AC175" s="72">
@@ -33747,7 +33747,7 @@
         <v>6.415189946030183E-3</v>
       </c>
       <c r="AA177" s="175">
-        <f t="shared" ref="T177:AA177" si="174">-AA110/AA5</f>
+        <f t="shared" ref="AA177" si="174">-AA110/AA5</f>
         <v>3.3856908856908859E-3</v>
       </c>
       <c r="AC177" s="175">
@@ -33808,7 +33808,7 @@
         <v>2.0344430295312594E-2</v>
       </c>
       <c r="AA178" s="175">
-        <f t="shared" ref="T178:AA178" si="176">-(AA110/AA59)</f>
+        <f t="shared" ref="AA178" si="176">-(AA110/AA59)</f>
         <v>4.524577347796345E-2</v>
       </c>
       <c r="AC178" s="175">
@@ -33869,7 +33869,7 @@
         <v>0.35743774137701423</v>
       </c>
       <c r="AA179" s="175">
-        <f t="shared" ref="T179:AA179" si="178">-AA110/AA53</f>
+        <f t="shared" ref="AA179" si="178">-AA110/AA53</f>
         <v>0.15424764019988896</v>
       </c>
       <c r="AC179" s="175">
@@ -34533,7 +34533,7 @@
         <v>-0.30844727286201273</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" ref="T197:AA199" si="196">IF(Z187=0,
+        <f t="shared" ref="AA197:AA199" si="196">IF(Z187=0,
 IF(AA187=0,0,IF(AA187&gt;0,1,-1)),
 (AA187-Z187)/ABS(Z187)
 )</f>
@@ -35217,15 +35217,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="256" t="s">
+      <c r="B4" s="253" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="E4" s="256" t="s">
+      <c r="C4" s="253"/>
+      <c r="E4" s="253" t="s">
         <v>287</v>
       </c>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35362,14 +35362,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="256" t="s">
+      <c r="B15" s="253" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="256"/>
-      <c r="E15" s="256" t="s">
+      <c r="C15" s="253"/>
+      <c r="E15" s="253" t="s">
         <v>293</v>
       </c>
-      <c r="F15" s="256"/>
+      <c r="F15" s="253"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35420,14 +35420,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="256" t="s">
+      <c r="B21" s="253" t="s">
         <v>292</v>
       </c>
-      <c r="C21" s="256"/>
-      <c r="E21" s="256" t="s">
+      <c r="C21" s="253"/>
+      <c r="E21" s="253" t="s">
         <v>296</v>
       </c>
-      <c r="F21" s="256"/>
+      <c r="F21" s="253"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35496,14 +35496,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="256" t="s">
+      <c r="B29" s="253" t="s">
         <v>297</v>
       </c>
-      <c r="C29" s="256"/>
-      <c r="E29" s="256" t="s">
+      <c r="C29" s="253"/>
+      <c r="E29" s="253" t="s">
         <v>303</v>
       </c>
-      <c r="F29" s="256"/>
+      <c r="F29" s="253"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35579,14 +35579,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="256" t="s">
+      <c r="B37" s="253" t="s">
         <v>315</v>
       </c>
-      <c r="C37" s="256"/>
-      <c r="E37" s="256" t="s">
+      <c r="C37" s="253"/>
+      <c r="E37" s="253" t="s">
         <v>318</v>
       </c>
-      <c r="F37" s="256"/>
+      <c r="F37" s="253"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35655,14 +35655,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="256" t="s">
+      <c r="B45" s="253" t="s">
         <v>326</v>
       </c>
-      <c r="C45" s="256"/>
-      <c r="E45" s="256" t="s">
+      <c r="C45" s="253"/>
+      <c r="E45" s="253" t="s">
         <v>332</v>
       </c>
-      <c r="F45" s="256"/>
+      <c r="F45" s="253"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35699,14 +35699,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="256" t="s">
+      <c r="B51" s="253" t="s">
         <v>329</v>
       </c>
-      <c r="C51" s="256"/>
-      <c r="E51" s="256" t="s">
+      <c r="C51" s="253"/>
+      <c r="E51" s="253" t="s">
         <v>350</v>
       </c>
-      <c r="F51" s="256"/>
+      <c r="F51" s="253"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37688,14 +37688,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="264" t="s">
         <v>363</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="F3" s="261" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>364</v>
       </c>
-      <c r="G3" s="260"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37762,19 +37762,19 @@
       <c r="B7" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C7" s="257">
+      <c r="C7" s="267">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="258"/>
-      <c r="F7" s="257">
+      <c r="D7" s="268"/>
+      <c r="F7" s="267">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="258"/>
+      <c r="G7" s="268"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -37801,19 +37801,19 @@
       <c r="B9" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C9" s="257">
+      <c r="C9" s="267">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="F9" s="257">
+      <c r="D9" s="268"/>
+      <c r="F9" s="267">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="258"/>
+      <c r="G9" s="268"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -37840,19 +37840,19 @@
       <c r="B11" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C11" s="257">
+      <c r="C11" s="267">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="F11" s="257">
+      <c r="D11" s="268"/>
+      <c r="F11" s="267">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="258"/>
+      <c r="G11" s="268"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37879,19 +37879,19 @@
       <c r="B13" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C13" s="257">
+      <c r="C13" s="267">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="F13" s="257">
+      <c r="D13" s="268"/>
+      <c r="F13" s="267">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="258"/>
+      <c r="G13" s="268"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37918,19 +37918,19 @@
       <c r="B15" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="257">
+      <c r="C15" s="267">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="258"/>
-      <c r="F15" s="257">
+      <c r="D15" s="268"/>
+      <c r="F15" s="267">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="258"/>
+      <c r="G15" s="268"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37957,19 +37957,19 @@
       <c r="B17" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C17" s="257">
+      <c r="C17" s="267">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="258"/>
-      <c r="F17" s="257">
+      <c r="D17" s="268"/>
+      <c r="F17" s="267">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="258"/>
+      <c r="G17" s="268"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37996,22 +37996,22 @@
       <c r="B19" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="257">
+      <c r="C19" s="267">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="F19" s="257">
+      <c r="D19" s="268"/>
+      <c r="F19" s="267">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="258"/>
+      <c r="G19" s="268"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -38038,22 +38038,22 @@
       <c r="B21" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C21" s="257">
+      <c r="C21" s="267">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="F21" s="257">
+      <c r="D21" s="268"/>
+      <c r="F21" s="267">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="258"/>
+      <c r="G21" s="268"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38101,22 +38101,22 @@
       <c r="B25" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C25" s="257">
+      <c r="C25" s="267">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="F25" s="257">
+      <c r="D25" s="268"/>
+      <c r="F25" s="267">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="258"/>
+      <c r="G25" s="268"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38143,22 +38143,22 @@
       <c r="B27" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C27" s="257">
+      <c r="C27" s="267">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="258"/>
-      <c r="F27" s="257">
+      <c r="D27" s="268"/>
+      <c r="F27" s="267">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="258"/>
+      <c r="G27" s="268"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38185,22 +38185,22 @@
       <c r="B29" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C29" s="257">
+      <c r="C29" s="267">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="258"/>
-      <c r="F29" s="257">
+      <c r="D29" s="268"/>
+      <c r="F29" s="267">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="258"/>
+      <c r="G29" s="268"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38248,22 +38248,22 @@
       <c r="B33" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C33" s="257">
+      <c r="C33" s="267">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="F33" s="257">
+      <c r="D33" s="268"/>
+      <c r="F33" s="267">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="258"/>
+      <c r="G33" s="268"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38290,43 +38290,25 @@
       <c r="B35" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C35" s="257">
+      <c r="C35" s="267">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="258"/>
-      <c r="F35" s="257">
+      <c r="D35" s="268"/>
+      <c r="F35" s="267">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="258"/>
+      <c r="G35" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38337,6 +38319,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22027C6-7E5E-9242-A46A-D029CF700D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F329942-9A08-A34B-87DD-C5D2260861BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2427,30 +2457,6 @@
     <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2458,6 +2464,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2469,10 +2484,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2480,6 +2498,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12870,7 +12900,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12889,11 +12919,9 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>1.0184</v>
-    <v>-0.12</v>
-    <v>-8.652E-3</v>
-    <v>0.02</v>
-    <v>1.4549999999999999E-3</v>
+    <v>0.97519999999999996</v>
+    <v>-0.29499999999999998</v>
+    <v>-2.1707000000000001E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12901,35 +12929,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>14.465</v>
+    <v>13.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46276.999695485938</v>
+    <v>46287.767096318748</v>
     <v>0</v>
-    <v>13.74</v>
-    <v>7165886750</v>
+    <v>13.19</v>
+    <v>6928761043</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.85</v>
-    <v>20.683900000000001</v>
-    <v>13.87</v>
-    <v>13.75</v>
-    <v>13.77</v>
+    <v>13.91</v>
+    <v>19.825500000000002</v>
+    <v>13.59</v>
+    <v>13.295</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>41791957</v>
-    <v>67565227</v>
+    <v>28804785</v>
+    <v>63112589</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12941,30 +12983,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.48</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12986,8 +13028,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13008,7 +13048,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13018,6 +13057,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13053,7 +13097,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13064,16 +13108,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13167,19 +13208,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13251,9 +13286,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13261,9 +13293,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13754,18 +13783,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="261" t="s">
+      <c r="B2" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="262"/>
-      <c r="E2" s="261" t="s">
+      <c r="C2" s="254"/>
+      <c r="E2" s="253" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="262"/>
-      <c r="H2" s="261" t="s">
+      <c r="F2" s="254"/>
+      <c r="H2" s="253" t="s">
         <v>379</v>
       </c>
-      <c r="I2" s="262"/>
+      <c r="I2" s="254"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13780,7 +13809,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>7212081.25</v>
+        <v>6973426.9249999998</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13804,7 +13833,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>5807056.25</v>
+        <v>5568401.9249999998</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13821,7 +13850,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>290</v>
@@ -13843,16 +13872,16 @@
       <c r="B6" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="229" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>13.77</v>
+      <c r="C6" s="229" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>284</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>20.522388059701488</v>
+        <v>19.843283582089548</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13869,14 +13898,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.12</v>
+        <v>-0.29499999999999998</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>4.2650350508292956</v>
+        <v>4.1239011636927625</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13891,16 +13920,16 @@
       <c r="B8" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.02</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>312</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.7800132243379816E-2</v>
+        <v>1.840931315129541E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13908,7 +13937,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-5.1119772181637428E-2</v>
+        <v>-1.8645871944153035E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13917,30 +13946,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.652E-3</v>
+        <v>-2.1707000000000001E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>335</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.8727272727272737E-2</v>
+        <v>5.0394885295223783E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.4549999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>340</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
       <c r="H10" s="205" t="s">
         <v>427</v>
@@ -13988,7 +14017,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0184</v>
+        <v>0.97519999999999996</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>121</v>
@@ -14004,7 +14033,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>67565227</v>
+        <v>63112589</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>122</v>
@@ -14020,7 +14049,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.19481547022227461</v>
+        <v>0.20148271647659088</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14033,10 +14062,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="263" t="s">
+      <c r="B17" s="255" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="263"/>
+      <c r="C17" s="255"/>
       <c r="E17" s="205" t="s">
         <v>343</v>
       </c>
@@ -14109,14 +14138,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="263" t="s">
+      <c r="B25" s="255" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="263"/>
-      <c r="E25" s="261" t="s">
+      <c r="C25" s="255"/>
+      <c r="E25" s="253" t="s">
         <v>399</v>
       </c>
-      <c r="F25" s="262"/>
+      <c r="F25" s="254"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -14125,12 +14154,12 @@
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="206" t="e" vm="2">
+      <c r="E26" s="206" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14145,7 +14174,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14165,15 +14194,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="253" t="s">
+      <c r="B33" s="256" t="s">
         <v>389</v>
       </c>
-      <c r="C33" s="253"/>
-      <c r="D33" s="253"/>
-      <c r="E33" s="253"/>
-      <c r="F33" s="253"/>
-      <c r="G33" s="253"/>
-      <c r="H33" s="253"/>
+      <c r="C33" s="256"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14192,24 +14221,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="253"/>
-      <c r="C39" s="253"/>
-      <c r="D39" s="253"/>
-      <c r="E39" s="253"/>
-      <c r="F39" s="253"/>
-      <c r="G39" s="253"/>
-      <c r="H39" s="253"/>
+      <c r="B39" s="256"/>
+      <c r="C39" s="256"/>
+      <c r="D39" s="256"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="253" t="s">
+      <c r="B42" s="256" t="s">
         <v>392</v>
       </c>
-      <c r="C42" s="253"/>
-      <c r="D42" s="253"/>
-      <c r="E42" s="253"/>
-      <c r="F42" s="253"/>
-      <c r="G42" s="253"/>
-      <c r="H42" s="253"/>
+      <c r="C42" s="256"/>
+      <c r="D42" s="256"/>
+      <c r="E42" s="256"/>
+      <c r="F42" s="256"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14240,24 +14269,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="253"/>
-      <c r="C49" s="253"/>
-      <c r="D49" s="253"/>
-      <c r="E49" s="253"/>
-      <c r="F49" s="253"/>
-      <c r="G49" s="253"/>
-      <c r="H49" s="253"/>
+      <c r="B49" s="256"/>
+      <c r="C49" s="256"/>
+      <c r="D49" s="256"/>
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="256"/>
+      <c r="H49" s="256"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="253" t="s">
+      <c r="B52" s="256" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="253"/>
-      <c r="D52" s="253"/>
-      <c r="E52" s="253"/>
-      <c r="F52" s="253"/>
-      <c r="G52" s="253"/>
-      <c r="H52" s="253"/>
+      <c r="C52" s="256"/>
+      <c r="D52" s="256"/>
+      <c r="E52" s="256"/>
+      <c r="F52" s="256"/>
+      <c r="G52" s="256"/>
+      <c r="H52" s="256"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14272,28 +14301,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="253"/>
-      <c r="C59" s="253"/>
-      <c r="D59" s="253"/>
-      <c r="E59" s="253"/>
-      <c r="F59" s="253"/>
-      <c r="G59" s="253"/>
-      <c r="H59" s="253"/>
+      <c r="B59" s="256"/>
+      <c r="C59" s="256"/>
+      <c r="D59" s="256"/>
+      <c r="E59" s="256"/>
+      <c r="F59" s="256"/>
+      <c r="G59" s="256"/>
+      <c r="H59" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14363,36 +14392,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="253" t="s">
+      <c r="S2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253" t="s">
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14403,32 +14432,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="269" t="s">
+      <c r="S4" s="265" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="270"/>
-      <c r="U4" s="270"/>
-      <c r="V4" s="270"/>
-      <c r="W4" s="270"/>
-      <c r="X4" s="270"/>
-      <c r="Y4" s="270"/>
-      <c r="Z4" s="270"/>
-      <c r="AA4" s="270"/>
-      <c r="AB4" s="270"/>
-      <c r="AC4" s="270"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
+      <c r="AA4" s="266"/>
+      <c r="AB4" s="266"/>
+      <c r="AC4" s="266"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14924,33 +14953,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="269" t="s">
+      <c r="S11" s="265" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="270"/>
-      <c r="U11" s="270"/>
-      <c r="V11" s="270"/>
-      <c r="W11" s="270"/>
-      <c r="X11" s="270"/>
-      <c r="Y11" s="270"/>
-      <c r="Z11" s="270"/>
-      <c r="AA11" s="270"/>
-      <c r="AB11" s="270"/>
-      <c r="AC11" s="270"/>
+      <c r="T11" s="266"/>
+      <c r="U11" s="266"/>
+      <c r="V11" s="266"/>
+      <c r="W11" s="266"/>
+      <c r="X11" s="266"/>
+      <c r="Y11" s="266"/>
+      <c r="Z11" s="266"/>
+      <c r="AA11" s="266"/>
+      <c r="AB11" s="266"/>
+      <c r="AC11" s="266"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15391,33 +15420,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="257" t="s">
+      <c r="C19" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="E19" s="257"/>
-      <c r="F19" s="257"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
+      <c r="D19" s="264"/>
+      <c r="E19" s="264"/>
+      <c r="F19" s="264"/>
+      <c r="G19" s="264"/>
+      <c r="H19" s="264"/>
+      <c r="I19" s="264"/>
+      <c r="J19" s="264"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="269" t="s">
+      <c r="S19" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="270"/>
-      <c r="U19" s="270"/>
-      <c r="V19" s="270"/>
-      <c r="W19" s="270"/>
-      <c r="X19" s="270"/>
-      <c r="Y19" s="270"/>
-      <c r="Z19" s="270"/>
-      <c r="AA19" s="270"/>
-      <c r="AB19" s="270"/>
-      <c r="AC19" s="270"/>
+      <c r="T19" s="266"/>
+      <c r="U19" s="266"/>
+      <c r="V19" s="266"/>
+      <c r="W19" s="266"/>
+      <c r="X19" s="266"/>
+      <c r="Y19" s="266"/>
+      <c r="Z19" s="266"/>
+      <c r="AA19" s="266"/>
+      <c r="AB19" s="266"/>
+      <c r="AC19" s="266"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16235,32 +16264,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="257" t="s">
+      <c r="C32" s="264" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="257"/>
-      <c r="E32" s="257"/>
-      <c r="F32" s="257"/>
-      <c r="G32" s="257"/>
-      <c r="H32" s="257"/>
-      <c r="I32" s="257"/>
-      <c r="J32" s="257"/>
-      <c r="K32" s="257"/>
-      <c r="L32" s="257"/>
+      <c r="D32" s="264"/>
+      <c r="E32" s="264"/>
+      <c r="F32" s="264"/>
+      <c r="G32" s="264"/>
+      <c r="H32" s="264"/>
+      <c r="I32" s="264"/>
+      <c r="J32" s="264"/>
+      <c r="K32" s="264"/>
+      <c r="L32" s="264"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="269" t="s">
+      <c r="S32" s="265" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="270"/>
-      <c r="U32" s="270"/>
-      <c r="V32" s="270"/>
-      <c r="W32" s="270"/>
-      <c r="X32" s="270"/>
-      <c r="Y32" s="270"/>
-      <c r="Z32" s="270"/>
-      <c r="AA32" s="270"/>
-      <c r="AB32" s="270"/>
-      <c r="AC32" s="270"/>
+      <c r="T32" s="266"/>
+      <c r="U32" s="266"/>
+      <c r="V32" s="266"/>
+      <c r="W32" s="266"/>
+      <c r="X32" s="266"/>
+      <c r="Y32" s="266"/>
+      <c r="Z32" s="266"/>
+      <c r="AA32" s="266"/>
+      <c r="AB32" s="266"/>
+      <c r="AC32" s="266"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16517,18 +16546,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16565,35 +16594,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="P2" s="253" t="s">
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="P2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253" t="s">
+      <c r="Q2" s="256"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16602,31 +16631,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
-      <c r="P4" s="270" t="s">
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="P4" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="270"/>
-      <c r="R4" s="270"/>
-      <c r="S4" s="270"/>
-      <c r="T4" s="270"/>
-      <c r="U4" s="270"/>
-      <c r="V4" s="270"/>
-      <c r="W4" s="270"/>
-      <c r="X4" s="270"/>
-      <c r="Y4" s="270"/>
-      <c r="Z4" s="270"/>
+      <c r="Q4" s="266"/>
+      <c r="R4" s="266"/>
+      <c r="S4" s="266"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16821,32 +16850,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="257" t="s">
+      <c r="C9" s="264" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="270" t="s">
+      <c r="P9" s="266" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="270"/>
-      <c r="R9" s="270"/>
-      <c r="S9" s="270"/>
-      <c r="T9" s="270"/>
-      <c r="U9" s="270"/>
-      <c r="V9" s="270"/>
-      <c r="W9" s="270"/>
-      <c r="X9" s="270"/>
-      <c r="Y9" s="270"/>
-      <c r="Z9" s="270"/>
+      <c r="Q9" s="266"/>
+      <c r="R9" s="266"/>
+      <c r="S9" s="266"/>
+      <c r="T9" s="266"/>
+      <c r="U9" s="266"/>
+      <c r="V9" s="266"/>
+      <c r="W9" s="266"/>
+      <c r="X9" s="266"/>
+      <c r="Y9" s="266"/>
+      <c r="Z9" s="266"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17695,31 +17724,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="E21" s="257"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="257"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="257"/>
-      <c r="L21" s="257"/>
-      <c r="P21" s="270" t="s">
+      <c r="D21" s="264"/>
+      <c r="E21" s="264"/>
+      <c r="F21" s="264"/>
+      <c r="G21" s="264"/>
+      <c r="H21" s="264"/>
+      <c r="I21" s="264"/>
+      <c r="J21" s="264"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="P21" s="266" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="270"/>
-      <c r="R21" s="270"/>
-      <c r="S21" s="270"/>
-      <c r="T21" s="270"/>
-      <c r="U21" s="270"/>
-      <c r="V21" s="270"/>
-      <c r="W21" s="270"/>
-      <c r="X21" s="270"/>
-      <c r="Y21" s="270"/>
-      <c r="Z21" s="270"/>
+      <c r="Q21" s="266"/>
+      <c r="R21" s="266"/>
+      <c r="S21" s="266"/>
+      <c r="T21" s="266"/>
+      <c r="U21" s="266"/>
+      <c r="V21" s="266"/>
+      <c r="W21" s="266"/>
+      <c r="X21" s="266"/>
+      <c r="Y21" s="266"/>
+      <c r="Z21" s="266"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18534,60 +18563,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18773,30 +18802,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="264" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="256"/>
-      <c r="Q11" s="256"/>
-      <c r="R11" s="256"/>
-      <c r="S11" s="256"/>
-      <c r="T11" s="256"/>
-      <c r="U11" s="256"/>
-      <c r="V11" s="256"/>
-      <c r="W11" s="256"/>
-      <c r="X11" s="256"/>
-      <c r="Y11" s="256"/>
-      <c r="Z11" s="256"/>
+      <c r="P11" s="267"/>
+      <c r="Q11" s="267"/>
+      <c r="R11" s="267"/>
+      <c r="S11" s="267"/>
+      <c r="T11" s="267"/>
+      <c r="U11" s="267"/>
+      <c r="V11" s="267"/>
+      <c r="W11" s="267"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19038,18 +19067,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="257" t="s">
+      <c r="C18" s="264" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19262,23 +19291,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="256"/>
-      <c r="C25" s="256"/>
+      <c r="B25" s="267"/>
+      <c r="C25" s="267"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="257" t="s">
+      <c r="C26" s="264" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="257"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="257"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="257"/>
-      <c r="J26" s="257"/>
-      <c r="K26" s="257"/>
-      <c r="L26" s="257"/>
+      <c r="D26" s="264"/>
+      <c r="E26" s="264"/>
+      <c r="F26" s="264"/>
+      <c r="G26" s="264"/>
+      <c r="H26" s="264"/>
+      <c r="I26" s="264"/>
+      <c r="J26" s="264"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19470,18 +19499,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="257" t="s">
+      <c r="C33" s="264" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="E33" s="257"/>
-      <c r="F33" s="257"/>
-      <c r="G33" s="257"/>
-      <c r="H33" s="257"/>
-      <c r="I33" s="257"/>
-      <c r="J33" s="257"/>
-      <c r="K33" s="257"/>
-      <c r="L33" s="257"/>
+      <c r="D33" s="264"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="264"/>
+      <c r="G33" s="264"/>
+      <c r="H33" s="264"/>
+      <c r="I33" s="264"/>
+      <c r="J33" s="264"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19665,18 +19694,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="257" t="s">
+      <c r="C40" s="264" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="257"/>
-      <c r="E40" s="257"/>
-      <c r="F40" s="257"/>
-      <c r="G40" s="257"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="257"/>
-      <c r="J40" s="257"/>
-      <c r="K40" s="257"/>
-      <c r="L40" s="257"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19940,6 +19969,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19947,12 +19982,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19990,60 +20019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256"/>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="S2" s="267"/>
+      <c r="T2" s="267"/>
+      <c r="U2" s="267"/>
+      <c r="V2" s="267"/>
+      <c r="W2" s="267"/>
+      <c r="X2" s="267"/>
+      <c r="Y2" s="267"/>
+      <c r="Z2" s="267"/>
+      <c r="AA2" s="267"/>
+      <c r="AB2" s="267"/>
+      <c r="AC2" s="267"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
-      <c r="S4" s="256"/>
-      <c r="T4" s="256"/>
-      <c r="U4" s="256"/>
-      <c r="V4" s="256"/>
-      <c r="W4" s="256"/>
-      <c r="X4" s="256"/>
-      <c r="Y4" s="256"/>
-      <c r="Z4" s="256"/>
-      <c r="AA4" s="256"/>
-      <c r="AB4" s="256"/>
-      <c r="AC4" s="256"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="S4" s="267"/>
+      <c r="T4" s="267"/>
+      <c r="U4" s="267"/>
+      <c r="V4" s="267"/>
+      <c r="W4" s="267"/>
+      <c r="X4" s="267"/>
+      <c r="Y4" s="267"/>
+      <c r="Z4" s="267"/>
+      <c r="AA4" s="267"/>
+      <c r="AB4" s="267"/>
+      <c r="AC4" s="267"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20406,18 +20435,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="257" t="s">
+      <c r="C13" s="264" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="E13" s="257"/>
-      <c r="F13" s="257"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="257"/>
-      <c r="I13" s="257"/>
-      <c r="J13" s="257"/>
-      <c r="K13" s="257"/>
-      <c r="L13" s="257"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20466,23 +20495,23 @@
         <v>74</v>
       </c>
       <c r="C15" s="150">
-        <f>-Statement!M83</f>
+        <f>Statement!M83</f>
         <v>0</v>
       </c>
       <c r="D15" s="150">
-        <f>-Statement!N83</f>
+        <f>Statement!N83</f>
         <v>0</v>
       </c>
       <c r="E15" s="150">
-        <f>-Statement!O83</f>
+        <f>Statement!O83</f>
         <v>0</v>
       </c>
       <c r="F15" s="150">
-        <f>-Statement!P83</f>
+        <f>Statement!P83</f>
         <v>0</v>
       </c>
       <c r="G15" s="151">
-        <f>-Statement!Q83</f>
+        <f>Statement!Q83</f>
         <v>0</v>
       </c>
       <c r="H15" s="150">
@@ -20510,18 +20539,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="257" t="s">
+      <c r="C18" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20713,18 +20742,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="257" t="s">
+      <c r="C25" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="E25" s="257"/>
-      <c r="F25" s="257"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="257"/>
-      <c r="I25" s="257"/>
-      <c r="J25" s="257"/>
-      <c r="K25" s="257"/>
-      <c r="L25" s="257"/>
+      <c r="D25" s="264"/>
+      <c r="E25" s="264"/>
+      <c r="F25" s="264"/>
+      <c r="G25" s="264"/>
+      <c r="H25" s="264"/>
+      <c r="I25" s="264"/>
+      <c r="J25" s="264"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20862,18 +20891,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="257" t="s">
+      <c r="C31" s="264" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="257"/>
-      <c r="E31" s="257"/>
-      <c r="F31" s="257"/>
-      <c r="G31" s="257"/>
-      <c r="H31" s="257"/>
-      <c r="I31" s="257"/>
-      <c r="J31" s="257"/>
-      <c r="K31" s="257"/>
-      <c r="L31" s="257"/>
+      <c r="D31" s="264"/>
+      <c r="E31" s="264"/>
+      <c r="F31" s="264"/>
+      <c r="G31" s="264"/>
+      <c r="H31" s="264"/>
+      <c r="I31" s="264"/>
+      <c r="J31" s="264"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21012,16 +21041,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21084,10 +21113,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="253" t="s">
+      <c r="B4" s="256" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="253"/>
+      <c r="C4" s="256"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21104,7 +21133,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21113,7 +21142,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>7212081.25</v>
+        <v>6973426.9249999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21131,7 +21160,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21140,7 +21169,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>1.0184</v>
+        <v>0.97519999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21172,10 +21201,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="253" t="s">
+      <c r="B15" s="256" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="253"/>
+      <c r="C15" s="256"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21210,7 +21239,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.2649599999999999E-2</v>
+        <v>9.2538800000000004E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21219,7 +21248,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.2649599999999999E-2</v>
+        <v>9.2538800000000004E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21264,60 +21293,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21563,10 +21592,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="253" t="s">
+      <c r="B13" s="256" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="253"/>
+      <c r="C13" s="256"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21586,10 +21615,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="253" t="s">
+      <c r="B18" s="256" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="253"/>
+      <c r="C18" s="256"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21703,37 +21732,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="264" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21922,18 +21951,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="257" t="s">
+      <c r="C10" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="257"/>
-      <c r="E10" s="257"/>
-      <c r="F10" s="257"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-      <c r="L10" s="257"/>
+      <c r="D10" s="264"/>
+      <c r="E10" s="264"/>
+      <c r="F10" s="264"/>
+      <c r="G10" s="264"/>
+      <c r="H10" s="264"/>
+      <c r="I10" s="264"/>
+      <c r="J10" s="264"/>
+      <c r="K10" s="264"/>
+      <c r="L10" s="264"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22127,18 +22156,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="257" t="s">
+      <c r="C16" s="264" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="257"/>
-      <c r="E16" s="257"/>
-      <c r="F16" s="257"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="257"/>
-      <c r="J16" s="257"/>
-      <c r="K16" s="257"/>
-      <c r="L16" s="257"/>
+      <c r="D16" s="264"/>
+      <c r="E16" s="264"/>
+      <c r="F16" s="264"/>
+      <c r="G16" s="264"/>
+      <c r="H16" s="264"/>
+      <c r="I16" s="264"/>
+      <c r="J16" s="264"/>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22272,18 +22301,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="264" t="s">
         <v>238</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="E21" s="257"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="257"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="257"/>
-      <c r="L21" s="257"/>
+      <c r="D21" s="264"/>
+      <c r="E21" s="264"/>
+      <c r="F21" s="264"/>
+      <c r="G21" s="264"/>
+      <c r="H21" s="264"/>
+      <c r="I21" s="264"/>
+      <c r="J21" s="264"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22367,18 +22396,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="257" t="s">
+      <c r="C26" s="264" t="s">
         <v>239</v>
       </c>
-      <c r="D26" s="257"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="257"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="257"/>
-      <c r="J26" s="257"/>
-      <c r="K26" s="257"/>
-      <c r="L26" s="257"/>
+      <c r="D26" s="264"/>
+      <c r="E26" s="264"/>
+      <c r="F26" s="264"/>
+      <c r="G26" s="264"/>
+      <c r="H26" s="264"/>
+      <c r="I26" s="264"/>
+      <c r="J26" s="264"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22648,10 +22677,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="253" t="s">
+      <c r="B37" s="256" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="253"/>
+      <c r="C37" s="256"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22744,10 +22773,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="253" t="s">
+      <c r="B49" s="256" t="s">
         <v>249</v>
       </c>
-      <c r="C49" s="253"/>
+      <c r="C49" s="256"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22803,10 +22832,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="253" t="s">
+      <c r="B57" s="256" t="s">
         <v>373</v>
       </c>
-      <c r="C57" s="253"/>
+      <c r="C57" s="256"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22946,10 +22975,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="253" t="s">
+      <c r="B4" s="256" t="s">
         <v>254</v>
       </c>
-      <c r="C4" s="253"/>
+      <c r="C4" s="256"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23003,7 +23032,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23012,7 +23041,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-5.1119772181637428E-2</v>
+        <v>-1.8645871944153035E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23068,37 +23097,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="264" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23211,18 +23240,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="257" t="s">
+      <c r="C9" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23343,18 +23372,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="257" t="s">
+      <c r="C14" s="264" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="257"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="257"/>
-      <c r="G14" s="257"/>
-      <c r="H14" s="257"/>
-      <c r="I14" s="257"/>
-      <c r="J14" s="257"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="257"/>
+      <c r="D14" s="264"/>
+      <c r="E14" s="264"/>
+      <c r="F14" s="264"/>
+      <c r="G14" s="264"/>
+      <c r="H14" s="264"/>
+      <c r="I14" s="264"/>
+      <c r="J14" s="264"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23444,10 +23473,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="253" t="s">
+      <c r="B20" s="256" t="s">
         <v>422</v>
       </c>
-      <c r="C20" s="253"/>
+      <c r="C20" s="256"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23548,60 +23577,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="263" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23829,10 +23858,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="269"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="176" t="s">
@@ -23840,7 +23869,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23859,20 +23888,20 @@
       <c r="C17" s="179">
         <v>1.4</v>
       </c>
-      <c r="E17" s="260" t="s">
+      <c r="E17" s="270" t="s">
         <v>265</v>
       </c>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="268" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="269"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="180" t="s">
@@ -23906,7 +23935,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>7165895</v>
+        <v>6928769.0199999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23933,15 +23962,15 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>5760870</v>
+        <v>5523744.0199999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="268" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="269"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
@@ -24016,18 +24045,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="257" t="s">
+      <c r="C39" s="264" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="257"/>
-      <c r="E39" s="257"/>
-      <c r="F39" s="257"/>
-      <c r="G39" s="257"/>
-      <c r="H39" s="257"/>
-      <c r="I39" s="257"/>
-      <c r="J39" s="257"/>
-      <c r="K39" s="257"/>
-      <c r="L39" s="257"/>
+      <c r="D39" s="264"/>
+      <c r="E39" s="264"/>
+      <c r="F39" s="264"/>
+      <c r="G39" s="264"/>
+      <c r="H39" s="264"/>
+      <c r="I39" s="264"/>
+      <c r="J39" s="264"/>
+      <c r="K39" s="264"/>
+      <c r="L39" s="264"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24459,17 +24488,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31160,7 +31189,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31231,7 +31260,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32537,7 +32566,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>20.522388059701488</v>
+        <v>19.843283582089548</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32574,7 +32603,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.2650350508292956</v>
+        <v>4.1239011636927625</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32635,7 +32664,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.6775506517407037</v>
+        <v>3.5558571574467384</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32696,7 +32725,7 @@
       </c>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7212081.25</v>
+        <v>6973426.9249999998</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32757,7 +32786,7 @@
       </c>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5807056.25</v>
+        <v>5568401.9249999998</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32794,7 +32823,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>3.3745121619564196</v>
+        <v>3.2358288278289087</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32831,7 +32860,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>37.967520006799695</v>
+        <v>36.407157497973166</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32966,7 +32995,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>56.179357901788499</v>
+        <v>54.320331876674764</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33003,7 +33032,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-128.68252376625966</v>
+        <v>-123.39401965563853</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33040,7 +33069,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.7800132243379816E-2</v>
+        <v>1.840931315129541E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33077,7 +33106,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.8727272727272737E-2</v>
+        <v>5.0394885295223783E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33151,7 +33180,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -33188,7 +33217,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33691,7 +33720,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.19481547022227461</v>
+        <v>0.20148271647659088</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35217,15 +35246,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="253" t="s">
+      <c r="B4" s="256" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="253"/>
-      <c r="E4" s="253" t="s">
+      <c r="C4" s="256"/>
+      <c r="E4" s="256" t="s">
         <v>287</v>
       </c>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35233,7 +35262,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35249,7 +35278,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>7212081.25</v>
+        <v>6973426.9249999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35269,7 +35298,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>5807056.25</v>
+        <v>5568401.9249999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35289,7 +35318,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>20.522388059701488</v>
+        <v>19.843283582089548</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>290</v>
@@ -35309,7 +35338,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>4.2650350508292956</v>
+        <v>4.1239011636927625</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>291</v>
@@ -35329,7 +35358,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.6775506517407037</v>
+        <v>3.5558571574467384</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35349,7 +35378,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>3.3745121619564196</v>
+        <v>3.2358288278289087</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35358,18 +35387,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>37.967520006799695</v>
+        <v>36.407157497973166</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="253" t="s">
+      <c r="B15" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="253"/>
-      <c r="E15" s="253" t="s">
+      <c r="C15" s="256"/>
+      <c r="E15" s="256" t="s">
         <v>293</v>
       </c>
-      <c r="F15" s="253"/>
+      <c r="F15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35420,14 +35449,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="253" t="s">
+      <c r="B21" s="256" t="s">
         <v>292</v>
       </c>
-      <c r="C21" s="253"/>
-      <c r="E21" s="253" t="s">
+      <c r="C21" s="256"/>
+      <c r="E21" s="256" t="s">
         <v>296</v>
       </c>
-      <c r="F21" s="253"/>
+      <c r="F21" s="256"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35496,14 +35525,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="253" t="s">
+      <c r="B29" s="256" t="s">
         <v>297</v>
       </c>
-      <c r="C29" s="253"/>
-      <c r="E29" s="253" t="s">
+      <c r="C29" s="256"/>
+      <c r="E29" s="256" t="s">
         <v>303</v>
       </c>
-      <c r="F29" s="253"/>
+      <c r="F29" s="256"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35579,14 +35608,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="253" t="s">
+      <c r="B37" s="256" t="s">
         <v>315</v>
       </c>
-      <c r="C37" s="253"/>
-      <c r="E37" s="253" t="s">
+      <c r="C37" s="256"/>
+      <c r="E37" s="256" t="s">
         <v>318</v>
       </c>
-      <c r="F37" s="253"/>
+      <c r="F37" s="256"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35594,7 +35623,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>4.8727272727272737E-2</v>
+        <v>5.0394885295223783E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>317</v>
@@ -35610,7 +35639,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.7800132243379816E-2</v>
+        <v>1.840931315129541E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>319</v>
@@ -35642,7 +35671,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35651,18 +35680,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="253" t="s">
+      <c r="B45" s="256" t="s">
         <v>326</v>
       </c>
-      <c r="C45" s="253"/>
-      <c r="E45" s="253" t="s">
+      <c r="C45" s="256"/>
+      <c r="E45" s="256" t="s">
         <v>332</v>
       </c>
-      <c r="F45" s="253"/>
+      <c r="F45" s="256"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35695,18 +35724,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.19481547022227461</v>
+        <v>0.20148271647659088</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="253" t="s">
+      <c r="B51" s="256" t="s">
         <v>329</v>
       </c>
-      <c r="C51" s="253"/>
-      <c r="E51" s="253" t="s">
+      <c r="C51" s="256"/>
+      <c r="E51" s="256" t="s">
         <v>350</v>
       </c>
-      <c r="F51" s="253"/>
+      <c r="F51" s="256"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35874,7 +35903,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>13.75</v>
+        <v>13.295</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35903,7 +35932,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>7212081.25</v>
+        <v>6973426.9249999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35932,7 +35961,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>5807056.25</v>
+        <v>5568401.9249999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35961,7 +35990,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>20.522388059701488</v>
+        <v>19.843283582089548</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35990,7 +36019,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>4.2650350508292956</v>
+        <v>4.1239011636927625</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36019,7 +36048,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.6775506517407037</v>
+        <v>3.5558571574467384</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36048,7 +36077,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>3.3745121619564196</v>
+        <v>3.2358288278289087</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36077,7 +36106,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>37.967520006799695</v>
+        <v>36.407157497973166</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36850,7 +36879,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>4.8727272727272737E-2</v>
+        <v>5.0394885295223783E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36879,7 +36908,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.7800132243379816E-2</v>
+        <v>1.840931315129541E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36937,7 +36966,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36966,7 +36995,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>3.7235853381435494E-2</v>
+        <v>3.8510190597573372E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37202,7 +37231,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.19481547022227461</v>
+        <v>0.20148271647659088</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37688,14 +37717,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="259" t="s">
         <v>363</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="260"/>
+      <c r="F3" s="261" t="s">
         <v>364</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="260"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37762,19 +37791,19 @@
       <c r="B7" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C7" s="267">
+      <c r="C7" s="257">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="268"/>
-      <c r="F7" s="267">
+      <c r="D7" s="258"/>
+      <c r="F7" s="257">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="268"/>
+      <c r="G7" s="258"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -37801,19 +37830,19 @@
       <c r="B9" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C9" s="267">
+      <c r="C9" s="257">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="268"/>
-      <c r="F9" s="267">
+      <c r="D9" s="258"/>
+      <c r="F9" s="257">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="268"/>
+      <c r="G9" s="258"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -37840,19 +37869,19 @@
       <c r="B11" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C11" s="267">
+      <c r="C11" s="257">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="268"/>
-      <c r="F11" s="267">
+      <c r="D11" s="258"/>
+      <c r="F11" s="257">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="268"/>
+      <c r="G11" s="258"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37879,19 +37908,19 @@
       <c r="B13" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C13" s="267">
+      <c r="C13" s="257">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="268"/>
-      <c r="F13" s="267">
+      <c r="D13" s="258"/>
+      <c r="F13" s="257">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="268"/>
+      <c r="G13" s="258"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37918,19 +37947,19 @@
       <c r="B15" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="267">
+      <c r="C15" s="257">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="268"/>
-      <c r="F15" s="267">
+      <c r="D15" s="258"/>
+      <c r="F15" s="257">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="268"/>
+      <c r="G15" s="258"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37957,19 +37986,19 @@
       <c r="B17" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C17" s="267">
+      <c r="C17" s="257">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="268"/>
-      <c r="F17" s="267">
+      <c r="D17" s="258"/>
+      <c r="F17" s="257">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="268"/>
+      <c r="G17" s="258"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37996,22 +38025,22 @@
       <c r="B19" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="267">
+      <c r="C19" s="257">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="268"/>
-      <c r="F19" s="267">
+      <c r="D19" s="258"/>
+      <c r="F19" s="257">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="268"/>
+      <c r="G19" s="258"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -38038,22 +38067,22 @@
       <c r="B21" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C21" s="267">
+      <c r="C21" s="257">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="268"/>
-      <c r="F21" s="267">
+      <c r="D21" s="258"/>
+      <c r="F21" s="257">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="268"/>
+      <c r="G21" s="258"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38101,22 +38130,22 @@
       <c r="B25" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C25" s="267">
+      <c r="C25" s="257">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="268"/>
-      <c r="F25" s="267">
+      <c r="D25" s="258"/>
+      <c r="F25" s="257">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="268"/>
+      <c r="G25" s="258"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38143,22 +38172,22 @@
       <c r="B27" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C27" s="267">
+      <c r="C27" s="257">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="268"/>
-      <c r="F27" s="267">
+      <c r="D27" s="258"/>
+      <c r="F27" s="257">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="268"/>
+      <c r="G27" s="258"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38185,22 +38214,22 @@
       <c r="B29" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C29" s="267">
+      <c r="C29" s="257">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="268"/>
-      <c r="F29" s="267">
+      <c r="D29" s="258"/>
+      <c r="F29" s="257">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="268"/>
+      <c r="G29" s="258"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38248,22 +38277,22 @@
       <c r="B33" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C33" s="267">
+      <c r="C33" s="257">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="268"/>
-      <c r="F33" s="267">
+      <c r="D33" s="258"/>
+      <c r="F33" s="257">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="268"/>
+      <c r="G33" s="258"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38290,25 +38319,43 @@
       <c r="B35" s="227" t="s">
         <v>365</v>
       </c>
-      <c r="C35" s="267">
+      <c r="C35" s="257">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="268"/>
-      <c r="F35" s="267">
+      <c r="D35" s="258"/>
+      <c r="F35" s="257">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="268"/>
+      <c r="G35" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38319,24 +38366,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEC876A-BA92-8444-AE99-7F40758A5D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F950D8-DD85-1643-8C9B-9A9E9ED6D3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2440,7 +2410,16 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2452,12 +2431,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2467,13 +2440,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12883,7 +12853,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12903,8 +12873,10 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>0.99560000000000004</v>
-    <v>-6.5000000000000002E-2</v>
-    <v>-5.1590000000000004E-3</v>
+    <v>-0.13</v>
+    <v>-1.0317E-2</v>
+    <v>0.03</v>
+    <v>2.4060000000000002E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12915,46 +12887,32 @@
     <v>12.81</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.719503008593</v>
+    <v>46290.839063471874</v>
     <v>0</v>
-    <v>12.515000000000001</v>
-    <v>6532682939</v>
+    <v>12.36</v>
+    <v>6498807838</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>12.54</v>
-    <v>18.6922</v>
+    <v>18.595300000000002</v>
     <v>12.6</v>
-    <v>12.535</v>
+    <v>12.47</v>
+    <v>12.5</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>27075877</v>
+    <v>44748884</v>
     <v>59393997</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12973,7 +12931,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12983,13 +12941,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13011,6 +12969,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13031,6 +12991,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13040,11 +13001,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13080,7 +13036,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13091,13 +13047,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13191,13 +13150,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13269,6 +13234,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13276,6 +13244,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13766,18 +13737,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="E2" s="252" t="s">
+      <c r="C2" s="256"/>
+      <c r="E2" s="255" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="253"/>
-      <c r="H2" s="252" t="s">
+      <c r="F2" s="256"/>
+      <c r="H2" s="255" t="s">
         <v>371</v>
       </c>
-      <c r="I2" s="253"/>
+      <c r="I2" s="256"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="202" t="s">
@@ -13792,7 +13763,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6574795.5250000004</v>
+        <v>6540702.0500000007</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13816,7 +13787,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5169770.5250000004</v>
+        <v>5135677.0500000007</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13824,7 +13795,7 @@
       </c>
       <c r="I4" s="228">
         <f>'AVG target price'!C6</f>
-        <v>18.721026295266533</v>
+        <v>15.500001157758549</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13833,7 +13804,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13855,16 +13826,16 @@
       <c r="B6" s="202" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="225" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="225" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>12.5</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>18.708955223880594</v>
+        <v>18.611940298507459</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13872,7 +13843,7 @@
       </c>
       <c r="I6" s="228">
         <f>'AVG target price'!C8</f>
-        <v>13.150246280287572</v>
+        <v>9.9292211427795856</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13881,14 +13852,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-6.5000000000000002E-2</v>
+        <v>-0.13</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>3.8881610445196526</v>
+        <v>3.867999060643005</v>
       </c>
       <c r="H7" s="201" t="str">
         <f>'AVG target price'!B9</f>
@@ -13896,23 +13867,23 @@
       </c>
       <c r="I7" s="229">
         <f>'AVG target price'!C9</f>
-        <v>13.125592727105769</v>
+        <v>11.515080158351775</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.03</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.9525474140125443E-2</v>
+        <v>1.9627250869805327E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B11</f>
@@ -13920,7 +13891,7 @@
       </c>
       <c r="I8" s="230">
         <f ca="1">'AVG target price'!C11</f>
-        <v>4.7115494783068888E-2</v>
+        <v>-7.6577373027123113E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13929,30 +13900,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.1590000000000004E-3</v>
+        <v>-1.0317E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.3450339050658172E-2</v>
+        <v>5.3728949478749004E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>2.4060000000000002E-3</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
       <c r="H10" s="201" t="s">
         <v>418</v>
@@ -14032,7 +14003,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.21369866099371965</v>
+        <v>0.21481256740627711</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14045,10 +14016,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="257" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="254"/>
+      <c r="C17" s="257"/>
       <c r="E17" s="201" t="s">
         <v>338</v>
       </c>
@@ -14121,14 +14092,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="257" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="254"/>
-      <c r="E25" s="252" t="s">
+      <c r="C25" s="257"/>
+      <c r="E25" s="255" t="s">
         <v>391</v>
       </c>
-      <c r="F25" s="253"/>
+      <c r="F25" s="256"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="201" t="s">
@@ -14137,7 +14108,7 @@
       <c r="C26" s="187">
         <v>0.21</v>
       </c>
-      <c r="E26" s="202" t="e" vm="5">
+      <c r="E26" s="202" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="236" cm="1">
@@ -14177,15 +14148,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="251" t="s">
+      <c r="B33" s="252" t="s">
         <v>381</v>
       </c>
-      <c r="C33" s="251"/>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
+      <c r="C33" s="252"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14204,24 +14175,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="251"/>
-      <c r="C39" s="251"/>
-      <c r="D39" s="251"/>
-      <c r="E39" s="251"/>
-      <c r="F39" s="251"/>
-      <c r="G39" s="251"/>
-      <c r="H39" s="251"/>
+      <c r="B39" s="252"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="252"/>
+      <c r="E39" s="252"/>
+      <c r="F39" s="252"/>
+      <c r="G39" s="252"/>
+      <c r="H39" s="252"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="251" t="s">
+      <c r="B42" s="252" t="s">
         <v>384</v>
       </c>
-      <c r="C42" s="251"/>
-      <c r="D42" s="251"/>
-      <c r="E42" s="251"/>
-      <c r="F42" s="251"/>
-      <c r="G42" s="251"/>
-      <c r="H42" s="251"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14252,24 +14223,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="251"/>
-      <c r="C49" s="251"/>
-      <c r="D49" s="251"/>
-      <c r="E49" s="251"/>
-      <c r="F49" s="251"/>
-      <c r="G49" s="251"/>
-      <c r="H49" s="251"/>
+      <c r="B49" s="252"/>
+      <c r="C49" s="252"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="252"/>
+      <c r="F49" s="252"/>
+      <c r="G49" s="252"/>
+      <c r="H49" s="252"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="251" t="s">
+      <c r="B52" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="251"/>
-      <c r="D52" s="251"/>
-      <c r="E52" s="251"/>
-      <c r="F52" s="251"/>
-      <c r="G52" s="251"/>
-      <c r="H52" s="251"/>
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14284,28 +14255,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="251"/>
-      <c r="C59" s="251"/>
-      <c r="D59" s="251"/>
-      <c r="E59" s="251"/>
-      <c r="F59" s="251"/>
-      <c r="G59" s="251"/>
-      <c r="H59" s="251"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="252"/>
+      <c r="D59" s="252"/>
+      <c r="E59" s="252"/>
+      <c r="F59" s="252"/>
+      <c r="G59" s="252"/>
+      <c r="H59" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14375,36 +14346,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="251" t="s">
+      <c r="S2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="251"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14415,18 +14386,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="251" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
       <c r="S4" s="263" t="s">
         <v>138</v>
@@ -14936,18 +14907,18 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
       <c r="S11" s="263" t="s">
@@ -15403,18 +15374,18 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="262" t="s">
+      <c r="C19" s="251" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="262"/>
-      <c r="E19" s="262"/>
-      <c r="F19" s="262"/>
-      <c r="G19" s="262"/>
-      <c r="H19" s="262"/>
-      <c r="I19" s="262"/>
-      <c r="J19" s="262"/>
-      <c r="K19" s="262"/>
-      <c r="L19" s="262"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="251"/>
+      <c r="J19" s="251"/>
+      <c r="K19" s="251"/>
+      <c r="L19" s="251"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
       <c r="S19" s="263" t="s">
@@ -16247,18 +16218,18 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="262" t="s">
+      <c r="C32" s="251" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="262"/>
-      <c r="E32" s="262"/>
-      <c r="F32" s="262"/>
-      <c r="G32" s="262"/>
-      <c r="H32" s="262"/>
-      <c r="I32" s="262"/>
-      <c r="J32" s="262"/>
-      <c r="K32" s="262"/>
-      <c r="L32" s="262"/>
+      <c r="D32" s="251"/>
+      <c r="E32" s="251"/>
+      <c r="F32" s="251"/>
+      <c r="G32" s="251"/>
+      <c r="H32" s="251"/>
+      <c r="I32" s="251"/>
+      <c r="J32" s="251"/>
+      <c r="K32" s="251"/>
+      <c r="L32" s="251"/>
       <c r="O32" s="5"/>
       <c r="S32" s="263" t="s">
         <v>148</v>
@@ -16529,18 +16500,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16577,35 +16548,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="P2" s="251" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="251"/>
-      <c r="R2" s="251"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16614,18 +16585,18 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="251" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="P4" s="264" t="s">
         <v>138</v>
       </c>
@@ -16833,18 +16804,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="251" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="93"/>
       <c r="P9" s="264" t="s">
         <v>165</v>
@@ -17707,18 +17678,18 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="262" t="s">
+      <c r="C21" s="251" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="262"/>
-      <c r="J21" s="262"/>
-      <c r="K21" s="262"/>
-      <c r="L21" s="262"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
       <c r="P21" s="264" t="s">
         <v>167</v>
       </c>
@@ -18546,20 +18517,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -18577,18 +18548,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="251" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -18785,18 +18756,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="93"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19050,18 +19021,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="251" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19279,18 +19250,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="251" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19482,18 +19453,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="262" t="s">
+      <c r="C33" s="251" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="262"/>
-      <c r="E33" s="262"/>
-      <c r="F33" s="262"/>
-      <c r="G33" s="262"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="262"/>
-      <c r="J33" s="262"/>
-      <c r="K33" s="262"/>
-      <c r="L33" s="262"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19677,18 +19648,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="251" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19952,12 +19923,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19965,6 +19930,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20002,20 +19973,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="S2" s="265"/>
       <c r="T2" s="265"/>
       <c r="U2" s="265"/>
@@ -20033,18 +20004,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -20418,18 +20389,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="251" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20522,18 +20493,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="251" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20725,18 +20696,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="251" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="262"/>
-      <c r="E25" s="262"/>
-      <c r="F25" s="262"/>
-      <c r="G25" s="262"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="262"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="262"/>
-      <c r="L25" s="262"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20874,18 +20845,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="262" t="s">
+      <c r="C31" s="251" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21024,16 +20995,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21096,10 +21067,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="252" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21116,7 +21087,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21125,7 +21096,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6574795.5250000004</v>
+        <v>6540702.0500000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21184,10 +21155,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="252" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="251"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21276,20 +21247,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -21307,18 +21278,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="251" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -21575,10 +21546,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="251" t="s">
+      <c r="B13" s="252" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="251"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21598,10 +21569,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="251" t="s">
+      <c r="B18" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="251"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21715,37 +21686,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="251" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21965,18 +21936,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22170,18 +22141,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="262" t="s">
+      <c r="C17" s="251" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="262"/>
-      <c r="E17" s="262"/>
-      <c r="F17" s="262"/>
-      <c r="G17" s="262"/>
-      <c r="H17" s="262"/>
-      <c r="I17" s="262"/>
-      <c r="J17" s="262"/>
-      <c r="K17" s="262"/>
-      <c r="L17" s="262"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22315,18 +22286,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="262" t="s">
+      <c r="C22" s="251" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="262"/>
-      <c r="E22" s="262"/>
-      <c r="F22" s="262"/>
-      <c r="G22" s="262"/>
-      <c r="H22" s="262"/>
-      <c r="I22" s="262"/>
-      <c r="J22" s="262"/>
-      <c r="K22" s="262"/>
-      <c r="L22" s="262"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22410,18 +22381,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="262" t="s">
+      <c r="C27" s="251" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="262"/>
-      <c r="E27" s="262"/>
-      <c r="F27" s="262"/>
-      <c r="G27" s="262"/>
-      <c r="H27" s="262"/>
-      <c r="I27" s="262"/>
-      <c r="J27" s="262"/>
-      <c r="K27" s="262"/>
-      <c r="L27" s="262"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="251"/>
+      <c r="I27" s="251"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="251"/>
+      <c r="L27" s="251"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22691,10 +22662,10 @@
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="251" t="s">
+      <c r="B38" s="252" t="s">
         <v>244</v>
       </c>
-      <c r="C38" s="251"/>
+      <c r="C38" s="252"/>
       <c r="N38" s="93"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -22737,8 +22708,8 @@
         <v>426</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/(1+C40)^5-G31+G32</f>
-        <v>8332096.1678350428</v>
+        <f>C42/(1+C40)^5</f>
+        <v>6642620.1678350428</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -22747,7 +22718,7 @@
       </c>
       <c r="C44" s="127">
         <f>SUM(H9:K9)+C43</f>
-        <v>8414434.1072617248</v>
+        <v>6724958.1072617248</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22774,7 +22745,7 @@
       </c>
       <c r="C47" s="127">
         <f>C44+C45-C46</f>
-        <v>9819459.1072617248</v>
+        <v>8129983.1072617248</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -22792,14 +22763,14 @@
       </c>
       <c r="C49" s="250">
         <f>C47/C48</f>
-        <v>18.721026295266533</v>
+        <v>15.500001157758549</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="251" t="s">
+      <c r="B51" s="252" t="s">
         <v>249</v>
       </c>
-      <c r="C51" s="251"/>
+      <c r="C51" s="252"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -22855,10 +22826,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="251" t="s">
+      <c r="B59" s="252" t="s">
         <v>368</v>
       </c>
-      <c r="C59" s="251"/>
+      <c r="C59" s="252"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -22900,8 +22871,8 @@
         <v>426</v>
       </c>
       <c r="C64" s="24">
-        <f>C63/(1+C61)^5-G31+G32</f>
-        <v>5410138.4882783536</v>
+        <f>C63/(1+C61)^5</f>
+        <v>3720662.4882783531</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -22910,7 +22881,7 @@
       </c>
       <c r="C65" s="127">
         <f>SUM(H9:K9)+C64</f>
-        <v>5492476.4277050355</v>
+        <v>3803000.4277050351</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -22937,7 +22908,7 @@
       </c>
       <c r="C68" s="127">
         <f>C65+C66-C67</f>
-        <v>6897501.4277050355</v>
+        <v>5208025.4277050346</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -22955,7 +22926,7 @@
       </c>
       <c r="C70" s="250">
         <f>C68/C69</f>
-        <v>13.150246280287572</v>
+        <v>9.9292211427795856</v>
       </c>
     </row>
   </sheetData>
@@ -23007,10 +22978,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="252" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23028,7 +22999,7 @@
       </c>
       <c r="C6" s="154">
         <f>Multiples!C49</f>
-        <v>18.721026295266533</v>
+        <v>15.500001157758549</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23046,7 +23017,7 @@
       </c>
       <c r="C8" s="154">
         <f>Multiples!C70</f>
-        <v>13.150246280287572</v>
+        <v>9.9292211427795856</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23055,7 +23026,7 @@
       </c>
       <c r="C9" s="250">
         <f>AVERAGE(C5:C8)</f>
-        <v>13.125592727105769</v>
+        <v>11.515080158351775</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23064,7 +23035,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23073,7 +23044,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">(C9-C10)/C10</f>
-        <v>4.7115494783068888E-2</v>
+        <v>-7.6577373027123113E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23129,37 +23100,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="251" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23272,18 +23243,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23404,18 +23375,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="262" t="s">
+      <c r="C14" s="251" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="262"/>
-      <c r="E14" s="262"/>
-      <c r="F14" s="262"/>
-      <c r="G14" s="262"/>
-      <c r="H14" s="262"/>
-      <c r="I14" s="262"/>
-      <c r="J14" s="262"/>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23505,10 +23476,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="251" t="s">
+      <c r="B20" s="252" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="251"/>
+      <c r="C20" s="252"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23609,20 +23580,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -23640,18 +23611,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="251" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -23901,7 +23872,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23967,7 +23938,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6532690.46</v>
+        <v>6498815.3200000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23994,7 +23965,7 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5127665.46</v>
+        <v>5093790.32</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24078,16 +24049,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30778,7 +30749,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30849,7 +30820,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32155,7 +32126,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.708955223880594</v>
+        <v>18.611940298507459</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32192,7 +32163,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.8881610445196526</v>
+        <v>3.867999060643005</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32253,7 +32224,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.352588903241434</v>
+        <v>3.3352041183422965</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32314,7 +32285,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6574795.5250000004</v>
+        <v>6540702.0500000007</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32375,7 +32346,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5169770.5250000004</v>
+        <v>5135677.0500000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32412,7 +32383,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.0041819400554841</v>
+        <v>2.9843700351801257</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32449,7 +32420,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>33.800837703010174</v>
+        <v>33.577928773177817</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32584,7 +32555,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>51.215145549012277</v>
+        <v>50.949570402567467</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32621,7 +32592,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-114.56047432800763</v>
+        <v>-113.80497374077605</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32658,7 +32629,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.9525474140125443E-2</v>
+        <v>1.9627250869805327E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32695,7 +32666,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.3450339050658172E-2</v>
+        <v>5.3728949478749004E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32769,7 +32740,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32806,7 +32777,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33309,7 +33280,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.21369866099371965</v>
+        <v>0.21481256740627711</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34835,15 +34806,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="252" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="251"/>
-      <c r="E4" s="251" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34851,7 +34822,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34867,7 +34838,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6574795.5250000004</v>
+        <v>6540702.0500000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34887,7 +34858,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5169770.5250000004</v>
+        <v>5135677.0500000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34907,7 +34878,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.708955223880594</v>
+        <v>18.611940298507459</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -34927,7 +34898,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.8881610445196526</v>
+        <v>3.867999060643005</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -34947,7 +34918,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.352588903241434</v>
+        <v>3.3352041183422965</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34967,7 +34938,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.0041819400554841</v>
+        <v>2.9843700351801257</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34976,18 +34947,18 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.800837703010174</v>
+        <v>33.577928773177817</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="252" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="251"/>
-      <c r="E15" s="251" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="251"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35038,14 +35009,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="251" t="s">
+      <c r="B21" s="252" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="251"/>
-      <c r="E21" s="251" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>291</v>
       </c>
-      <c r="F21" s="251"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35114,14 +35085,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="251" t="s">
+      <c r="B29" s="252" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="251"/>
-      <c r="E29" s="251" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="251"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35197,14 +35168,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="251" t="s">
+      <c r="B37" s="252" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="251"/>
-      <c r="E37" s="251" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="251"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35212,7 +35183,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.3450339050658172E-2</v>
+        <v>5.3728949478749004E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35228,7 +35199,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.9525474140125443E-2</v>
+        <v>1.9627250869805327E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35260,7 +35231,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35269,18 +35240,18 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="251" t="s">
+      <c r="B45" s="252" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="251"/>
-      <c r="E45" s="251" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>327</v>
       </c>
-      <c r="F45" s="251"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35313,18 +35284,18 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.21369866099371965</v>
+        <v>0.21481256740627711</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="251" t="s">
+      <c r="B51" s="252" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="251"/>
-      <c r="E51" s="251" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>345</v>
       </c>
-      <c r="F51" s="251"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35492,7 +35463,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>12.535</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35521,7 +35492,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6574795.5250000004</v>
+        <v>6540702.0500000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35550,7 +35521,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5169770.5250000004</v>
+        <v>5135677.0500000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35579,7 +35550,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.708955223880594</v>
+        <v>18.611940298507459</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35608,7 +35579,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.8881610445196526</v>
+        <v>3.867999060643005</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35637,7 +35608,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.352588903241434</v>
+        <v>3.3352041183422965</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35666,7 +35637,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.0041819400554841</v>
+        <v>2.9843700351801257</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35695,7 +35666,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.800837703010174</v>
+        <v>33.577928773177817</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36468,7 +36439,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.3450339050658172E-2</v>
+        <v>5.3728949478749004E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36497,7 +36468,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.9525474140125443E-2</v>
+        <v>1.9627250869805327E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36555,7 +36526,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36584,7 +36555,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.0845072516532743E-2</v>
+        <v>4.1057977866458532E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36820,7 +36791,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.21369866099371965</v>
+        <v>0.21481256740627711</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37306,14 +37277,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="258" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="259"/>
+      <c r="F3" s="260" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="259"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37380,19 +37351,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="261">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="262"/>
+      <c r="F7" s="261">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="262"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37419,19 +37390,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="261">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="262"/>
+      <c r="F9" s="261">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="262"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37458,19 +37429,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="261">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="262"/>
+      <c r="F11" s="261">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="262"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37497,19 +37468,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="261">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="262"/>
+      <c r="F13" s="261">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="262"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37536,19 +37507,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="261">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="262"/>
+      <c r="F15" s="261">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="262"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37575,19 +37546,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="261">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="262"/>
+      <c r="F17" s="261">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="262"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37614,22 +37585,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="261">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="262"/>
+      <c r="F19" s="261">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="262"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -37656,22 +37627,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="261">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="262"/>
+      <c r="F21" s="261">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="262"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37719,22 +37690,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="261">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="262"/>
+      <c r="F25" s="261">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="262"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37761,22 +37732,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="261">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="262"/>
+      <c r="F27" s="261">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="262"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37803,22 +37774,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="261">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="262"/>
+      <c r="F29" s="261">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="262"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37866,22 +37837,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="261">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="F33" s="255">
+      <c r="D33" s="262"/>
+      <c r="F33" s="261">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="262"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37908,43 +37879,25 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="255">
+      <c r="C35" s="261">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="256"/>
-      <c r="F35" s="255">
+      <c r="D35" s="262"/>
+      <c r="F35" s="261">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="256"/>
+      <c r="G35" s="262"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37955,6 +37908,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F950D8-DD85-1643-8C9B-9A9E9ED6D3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E0709-4AA7-8A42-85BE-096929668063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="433">
   <si>
     <t>Ticker</t>
   </si>
@@ -1457,6 +1457,18 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
   </si>
 </sst>
 </file>
@@ -2431,6 +2443,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2438,12 +2456,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2455,14 +2467,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12872,11 +12884,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.99560000000000004</v>
-    <v>-0.13</v>
-    <v>-1.0317E-2</v>
-    <v>0.03</v>
-    <v>2.4060000000000002E-3</v>
+    <v>0.9829</v>
+    <v>-0.14000000000000001</v>
+    <v>-1.1110999999999999E-2</v>
+    <v>0.02</v>
+    <v>1.6050000000000001E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12887,21 +12899,21 @@
     <v>12.81</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.839063471874</v>
+    <v>46290.999607175778</v>
     <v>0</v>
     <v>12.36</v>
-    <v>6498807838</v>
+    <v>6493596284</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.54</v>
-    <v>18.595300000000002</v>
     <v>12.6</v>
-    <v>12.47</v>
-    <v>12.5</v>
+    <v>18.79</v>
+    <v>12.6</v>
+    <v>12.46</v>
+    <v>12.48</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>44748884</v>
+    <v>45670205</v>
     <v>59393997</v>
     <v>2015</v>
   </rv>
@@ -12924,19 +12936,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13158,9 +13170,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13763,7 +13775,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6540702.0500000007</v>
+        <v>6535456.9000000004</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13787,7 +13799,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5135677.0500000007</v>
+        <v>5130431.9000000004</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13804,7 +13816,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13819,7 +13831,7 @@
       </c>
       <c r="I5" s="228">
         <f>'AVG target price'!C7</f>
-        <v>14.544205527348455</v>
+        <v>11.635364421878764</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13828,14 +13840,14 @@
       </c>
       <c r="C6" s="225" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>18.611940298507459</v>
+        <v>18.597014925373131</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13852,22 +13864,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.13</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>3.867999060643005</v>
+        <v>3.8648972169696747</v>
       </c>
       <c r="H7" s="201" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="229">
-        <f>'AVG target price'!C9</f>
-        <v>11.515080158351775</v>
+        <f>'AVG target price'!C10</f>
+        <v>10.954332680019224</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13876,22 +13888,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.9627250869805327E-2</v>
+        <v>1.9643003077566005E-2</v>
       </c>
       <c r="H8" s="201" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="230">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-7.6577373027123113E-2</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.12084007383473329</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13900,14 +13912,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0317E-2</v>
+        <v>-1.1110999999999999E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.3728949478749004E-2</v>
+        <v>5.377207062600322E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13916,14 +13928,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.4060000000000002E-3</v>
+        <v>1.6050000000000001E-3</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
       <c r="H10" s="201" t="s">
         <v>418</v>
@@ -13971,7 +13983,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.99560000000000004</v>
+        <v>0.9829</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14003,7 +14015,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.21481256740627711</v>
+        <v>0.21498496914576851</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14113,7 +14125,7 @@
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14128,7 +14140,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14265,18 +14277,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16500,18 +16512,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19923,6 +19935,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19930,12 +19948,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20995,16 +21007,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21087,7 +21099,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21096,7 +21108,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6540702.0500000007</v>
+        <v>6535456.9000000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21114,7 +21126,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21123,7 +21135,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.99560000000000004</v>
+        <v>0.9829</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21193,7 +21205,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.6422000000000008E-2</v>
+        <v>9.6070500000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21202,7 +21214,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.6422000000000008E-2</v>
+        <v>9.6070500000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21664,7 +21676,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="85" customWidth="1"/>
@@ -22633,7 +22645,7 @@
         <v>-22.043158871603321</v>
       </c>
       <c r="D35" s="168">
-        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
         <v>-12.448147509708797</v>
       </c>
       <c r="E35" s="168">
@@ -22656,285 +22668,421 @@
       <c r="N35" s="93"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C36" s="168">
+        <f>C33/C6</f>
+        <v>14.921177817477574</v>
+      </c>
+      <c r="D36" s="168">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>5.8803677186724492</v>
+      </c>
+      <c r="E36" s="168">
+        <f t="shared" si="14"/>
+        <v>10.48460539633904</v>
+      </c>
+      <c r="F36" s="168">
+        <f t="shared" si="14"/>
+        <v>4.5046893116144773</v>
+      </c>
+      <c r="G36" s="169">
+        <f t="shared" si="14"/>
+        <v>3.2102330103838885</v>
+      </c>
+      <c r="H36" s="158"/>
+      <c r="I36" s="158"/>
+      <c r="J36" s="158"/>
+      <c r="K36" s="158"/>
+      <c r="L36" s="158"/>
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="252" t="s">
+      <c r="N38" s="93"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="252" t="s">
         <v>244</v>
       </c>
-      <c r="C38" s="252"/>
-      <c r="N38" s="93"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="252"/>
+      <c r="N39" s="93"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>427920.24826000072</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C40" s="156">
+      <c r="C41" s="156">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="C41" s="114">
+      <c r="C42" s="114">
         <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>10698006.206500018</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>10698006.206500018</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C40)^5</f>
+      <c r="C44" s="24">
+        <f>C43/(1+C41)^5</f>
         <v>6642620.1678350428</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="C44" s="127">
-        <f>SUM(H9:K9)+C43</f>
+      <c r="C45" s="127">
+        <f>SUM(H9:K9)+C44</f>
         <v>6724958.1072617248</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C45" s="90">
+      <c r="C46" s="90">
         <f>Statement!AC107</f>
         <v>1405025</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C46" s="90">
+      <c r="C47" s="90">
         <f>Statement!AC108</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="C47" s="127">
-        <f>C44+C45-C46</f>
+      <c r="C48" s="127">
+        <f>C45+C46-C47</f>
         <v>8129983.1072617248</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="90">
+      <c r="C49" s="90">
         <f>Statement!AC78</f>
         <v>524515</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="249" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="249" t="s">
         <v>248</v>
       </c>
-      <c r="C49" s="250">
-        <f>C47/C48</f>
+      <c r="C50" s="250">
+        <f>C48/C49</f>
         <v>15.500001157758549</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="252" t="s">
         <v>249</v>
       </c>
-      <c r="C51" s="252"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="252"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>2473527.4465896003</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C53" s="156">
+      <c r="C54" s="156">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="C54" s="114">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="114">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>482510.33681860787</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
-        <v>25.631859649874027</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="249" t="s">
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
+        <v>20.505487719899222</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="249" t="s">
         <v>248</v>
       </c>
-      <c r="C57" s="250">
-        <f>C56/(1+C53)^5</f>
-        <v>14.544205527348455</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="252" t="s">
+      <c r="C58" s="250">
+        <f>C57/(1+C54)^5</f>
+        <v>11.635364421878764</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="252" t="s">
         <v>368</v>
       </c>
-      <c r="C59" s="252"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="252"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>199738.80479990577</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C61" s="156">
+      <c r="C62" s="156">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>398</v>
       </c>
-      <c r="C62" s="114">
+      <c r="C63" s="114">
         <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>5992164.1439971728</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>5992164.1439971728</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C64" s="24">
-        <f>C63/(1+C61)^5</f>
+      <c r="C65" s="24">
+        <f>C64/(1+C62)^5</f>
         <v>3720662.4882783531</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="C65" s="127">
-        <f>SUM(H9:K9)+C64</f>
+      <c r="C66" s="127">
+        <f>SUM(H9:K9)+C65</f>
         <v>3803000.4277050351</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C66" s="90">
+      <c r="C67" s="90">
         <f>Statement!AC107</f>
         <v>1405025</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C67" s="90">
+      <c r="C68" s="90">
         <f>Statement!AC108</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="C68" s="127">
-        <f>C65+C66-C67</f>
+      <c r="C69" s="127">
+        <f>C66+C67-C68</f>
         <v>5208025.4277050346</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="90">
+      <c r="C70" s="90">
         <f>Statement!AC78</f>
         <v>524515</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="249" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="249" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="250">
-        <f>C68/C69</f>
+      <c r="C71" s="250">
+        <f>C69/C70</f>
         <v>9.9292211427795856</v>
       </c>
     </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="252" t="s">
+        <v>430</v>
+      </c>
+      <c r="C73" s="252"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>2473527.4465896003</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C75" s="156">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="C76" s="114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>7420582.3397688009</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C78" s="24">
+        <f>C77/(1+C75)^5</f>
+        <v>4607597.8042786438</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" s="127">
+        <f>SUM(H9:K9)+C78</f>
+        <v>4689935.7437053258</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C80" s="90">
+        <f>Statement!AC107</f>
+        <v>1405025</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="90">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C82" s="127">
+        <f>C79+C80-C81</f>
+        <v>6094960.7437053258</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="90">
+        <f>Statement!AC78</f>
+        <v>524515</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="249" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" s="250">
+        <f>C82/C83</f>
+        <v>11.620183872158711</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -22951,7 +23099,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="85" customWidth="1"/>
@@ -22998,7 +23146,7 @@
         <v>255</v>
       </c>
       <c r="C6" s="154">
-        <f>Multiples!C49</f>
+        <f>Multiples!C50</f>
         <v>15.500001157758549</v>
       </c>
     </row>
@@ -23007,8 +23155,8 @@
         <v>256</v>
       </c>
       <c r="C7" s="154">
-        <f>Multiples!C57</f>
-        <v>14.544205527348455</v>
+        <f>Multiples!C58</f>
+        <v>11.635364421878764</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23016,35 +23164,44 @@
         <v>369</v>
       </c>
       <c r="C8" s="154">
-        <f>Multiples!C70</f>
+        <f>Multiples!C71</f>
         <v>9.9292211427795856</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="249" t="s">
+      <c r="B9" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C9" s="154">
+        <f>Multiples!C84</f>
+        <v>11.620183872158711</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="249" t="s">
         <v>257</v>
       </c>
-      <c r="C9" s="250">
-        <f>AVERAGE(C5:C8)</f>
-        <v>11.515080158351775</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="154">
-        <f ca="1">Overview!C5</f>
-        <v>12.47</v>
+      <c r="C10" s="250">
+        <f>AVERAGE(C5:C9)</f>
+        <v>10.954332680019224</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="154">
+        <f ca="1">Overview!C5</f>
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="173">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-7.6577373027123113E-2</v>
+      <c r="C12" s="173">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.12084007383473329</v>
       </c>
     </row>
   </sheetData>
@@ -23861,10 +24018,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="267" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="268"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -23872,7 +24029,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23891,20 +24048,20 @@
       <c r="C17" s="177">
         <v>1.35</v>
       </c>
-      <c r="E17" s="268" t="s">
+      <c r="E17" s="266" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="267" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="268"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -23938,7 +24095,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6498815.3200000003</v>
+        <v>6493603.7600000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23965,15 +24122,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5093790.32</v>
+        <v>5088578.7600000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="267" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="268"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24049,16 +24206,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30749,7 +30906,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30820,7 +30977,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32126,7 +32283,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.611940298507459</v>
+        <v>18.597014925373131</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32163,7 +32320,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.867999060643005</v>
+        <v>3.8648972169696747</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32381,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.3352041183422965</v>
+        <v>3.3325295360501213</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32285,7 +32442,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6540702.0500000007</v>
+        <v>6535456.9000000004</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32346,7 +32503,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5135677.0500000007</v>
+        <v>5130431.9000000004</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32383,7 +32540,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>2.9843700351801257</v>
+        <v>2.9813220498146857</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32420,7 +32577,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>33.577928773177817</v>
+        <v>33.543635091665145</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32555,7 +32712,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>50.949570402567467</v>
+        <v>50.908712687729796</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32592,7 +32749,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-113.80497374077605</v>
+        <v>-113.68874288120195</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32629,7 +32786,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.9627250869805327E-2</v>
+        <v>1.9643003077566005E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32666,7 +32823,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.3728949478749004E-2</v>
+        <v>5.377207062600322E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32740,7 +32897,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32777,7 +32934,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33280,7 +33437,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.21481256740627711</v>
+        <v>0.21498496914576851</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34822,7 +34979,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34838,7 +34995,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6540702.0500000007</v>
+        <v>6535456.9000000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34858,7 +35015,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5135677.0500000007</v>
+        <v>5130431.9000000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34878,7 +35035,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.611940298507459</v>
+        <v>18.597014925373131</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -34898,7 +35055,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.867999060643005</v>
+        <v>3.8648972169696747</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -34918,7 +35075,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.3352041183422965</v>
+        <v>3.3325295360501213</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34938,7 +35095,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>2.9843700351801257</v>
+        <v>2.9813220498146857</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34947,7 +35104,7 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.577928773177817</v>
+        <v>33.543635091665145</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35183,7 +35340,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.3728949478749004E-2</v>
+        <v>5.377207062600322E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35199,7 +35356,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.9627250869805327E-2</v>
+        <v>1.9643003077566005E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35231,7 +35388,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35240,7 +35397,7 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35284,7 +35441,7 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.21481256740627711</v>
+        <v>0.21498496914576851</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35463,7 +35620,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>12.47</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35492,7 +35649,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6540702.0500000007</v>
+        <v>6535456.9000000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35521,7 +35678,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5135677.0500000007</v>
+        <v>5130431.9000000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35550,7 +35707,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.611940298507459</v>
+        <v>18.597014925373131</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35579,7 +35736,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.867999060643005</v>
+        <v>3.8648972169696747</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35608,7 +35765,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.3352041183422965</v>
+        <v>3.3325295360501213</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35637,7 +35794,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>2.9843700351801257</v>
+        <v>2.9813220498146857</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35666,7 +35823,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.577928773177817</v>
+        <v>33.543635091665145</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36439,7 +36596,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.3728949478749004E-2</v>
+        <v>5.377207062600322E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36468,7 +36625,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.9627250869805327E-2</v>
+        <v>1.9643003077566005E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36526,7 +36683,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36555,7 +36712,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.1057977866458532E-2</v>
+        <v>4.1090929694601763E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36791,7 +36948,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.21481256740627711</v>
+        <v>0.21498496914576851</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37277,14 +37434,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="260" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="F3" s="260" t="s">
+      <c r="D3" s="261"/>
+      <c r="F3" s="262" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="259"/>
+      <c r="G3" s="261"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37351,19 +37508,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="261">
+      <c r="C7" s="258">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="262"/>
-      <c r="F7" s="261">
+      <c r="D7" s="259"/>
+      <c r="F7" s="258">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="262"/>
+      <c r="G7" s="259"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37390,19 +37547,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="261">
+      <c r="C9" s="258">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="F9" s="261">
+      <c r="D9" s="259"/>
+      <c r="F9" s="258">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="262"/>
+      <c r="G9" s="259"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37429,19 +37586,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="261">
+      <c r="C11" s="258">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="F11" s="261">
+      <c r="D11" s="259"/>
+      <c r="F11" s="258">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="262"/>
+      <c r="G11" s="259"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37468,19 +37625,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="261">
+      <c r="C13" s="258">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="F13" s="261">
+      <c r="D13" s="259"/>
+      <c r="F13" s="258">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="262"/>
+      <c r="G13" s="259"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37507,19 +37664,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="261">
+      <c r="C15" s="258">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="262"/>
-      <c r="F15" s="261">
+      <c r="D15" s="259"/>
+      <c r="F15" s="258">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="262"/>
+      <c r="G15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37546,19 +37703,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="261">
+      <c r="C17" s="258">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="262"/>
-      <c r="F17" s="261">
+      <c r="D17" s="259"/>
+      <c r="F17" s="258">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="262"/>
+      <c r="G17" s="259"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37585,22 +37742,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="261">
+      <c r="C19" s="258">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="262"/>
-      <c r="F19" s="261">
+      <c r="D19" s="259"/>
+      <c r="F19" s="258">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="262"/>
+      <c r="G19" s="259"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -37627,22 +37784,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="261">
+      <c r="C21" s="258">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="262"/>
-      <c r="F21" s="261">
+      <c r="D21" s="259"/>
+      <c r="F21" s="258">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="262"/>
+      <c r="G21" s="259"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37690,22 +37847,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="261">
+      <c r="C25" s="258">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="262"/>
-      <c r="F25" s="261">
+      <c r="D25" s="259"/>
+      <c r="F25" s="258">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="262"/>
+      <c r="G25" s="259"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37732,22 +37889,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="261">
+      <c r="C27" s="258">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="262"/>
-      <c r="F27" s="261">
+      <c r="D27" s="259"/>
+      <c r="F27" s="258">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="262"/>
+      <c r="G27" s="259"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37774,22 +37931,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="261">
+      <c r="C29" s="258">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="262"/>
-      <c r="F29" s="261">
+      <c r="D29" s="259"/>
+      <c r="F29" s="258">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="262"/>
+      <c r="G29" s="259"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37837,22 +37994,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="261">
+      <c r="C33" s="258">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="262"/>
-      <c r="F33" s="261">
+      <c r="D33" s="259"/>
+      <c r="F33" s="258">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="262"/>
+      <c r="G33" s="259"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37879,25 +38036,43 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="261">
+      <c r="C35" s="258">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="262"/>
-      <c r="F35" s="261">
+      <c r="D35" s="259"/>
+      <c r="F35" s="258">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="262"/>
+      <c r="G35" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37908,24 +38083,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E0709-4AA7-8A42-85BE-096929668063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EE935A-78E5-534B-B2FE-EAFF2D7BE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="434">
   <si>
     <t>Ticker</t>
   </si>
@@ -1469,6 +1469,9 @@
   </si>
   <si>
     <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2422,16 +2425,7 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2443,12 +2437,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2458,23 +2446,38 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13749,18 +13752,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="E2" s="255" t="s">
+      <c r="C2" s="253"/>
+      <c r="E2" s="252" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="256"/>
-      <c r="H2" s="255" t="s">
+      <c r="F2" s="253"/>
+      <c r="H2" s="252" t="s">
         <v>371</v>
       </c>
-      <c r="I2" s="256"/>
+      <c r="I2" s="253"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="202" t="s">
@@ -13873,13 +13876,13 @@
         <f ca="1">Statement!AC151</f>
         <v>3.8648972169696747</v>
       </c>
-      <c r="H7" s="201" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="229">
-        <f>'AVG target price'!C10</f>
-        <v>10.954332680019224</v>
+      <c r="H7" s="202" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales</v>
+      </c>
+      <c r="I7" s="228">
+        <f>'AVG target price'!C9</f>
+        <v>11.620183872158711</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13898,12 +13901,12 @@
         <v>1.9643003077566005E-2</v>
       </c>
       <c r="H8" s="201" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="230">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.12084007383473329</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="229">
+        <f>'AVG target price'!C10</f>
+        <v>10.954332680019224</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13921,6 +13924,14 @@
         <f ca="1">Statement!AC162</f>
         <v>5.377207062600322E-2</v>
       </c>
+      <c r="H9" s="201" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="230">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.12084007383473329</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
@@ -13937,13 +13948,6 @@
         <f ca="1">Statement!AC164</f>
         <v>4.1090929694601763E-2</v>
       </c>
-      <c r="H10" s="201" t="s">
-        <v>418</v>
-      </c>
-      <c r="I10" s="229">
-        <f>DDM!C26</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="202" t="s">
@@ -13960,6 +13964,13 @@
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
+      <c r="H11" s="201" t="s">
+        <v>418</v>
+      </c>
+      <c r="I11" s="229">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
@@ -13992,6 +14003,13 @@
         <f>Statement!AC125</f>
         <v>0.18573545162533595</v>
       </c>
+      <c r="H13" s="201" t="s">
+        <v>433</v>
+      </c>
+      <c r="I13" s="230">
+        <f>'Reverse DCF'!C17</f>
+        <v>1.35</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -14028,10 +14046,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="254" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="257"/>
+      <c r="C17" s="254"/>
       <c r="E17" s="201" t="s">
         <v>338</v>
       </c>
@@ -14104,14 +14122,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="257" t="s">
+      <c r="B25" s="254" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="257"/>
-      <c r="E25" s="255" t="s">
+      <c r="C25" s="254"/>
+      <c r="E25" s="252" t="s">
         <v>391</v>
       </c>
-      <c r="F25" s="256"/>
+      <c r="F25" s="253"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="201" t="s">
@@ -14160,15 +14178,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="252" t="s">
+      <c r="B33" s="153" t="s">
         <v>381</v>
       </c>
-      <c r="C33" s="252"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14187,24 +14205,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="252"/>
-      <c r="C39" s="252"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
+      <c r="B39" s="153"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="153"/>
+      <c r="H39" s="153"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="153" t="s">
         <v>384</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="153"/>
+      <c r="H42" s="153"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14235,24 +14253,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="252"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="252"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="252"/>
-      <c r="G49" s="252"/>
-      <c r="H49" s="252"/>
+      <c r="B49" s="153"/>
+      <c r="C49" s="153"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="153"/>
+      <c r="F49" s="153"/>
+      <c r="G49" s="153"/>
+      <c r="H49" s="153"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="153" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="252"/>
-      <c r="D52" s="252"/>
-      <c r="E52" s="252"/>
-      <c r="F52" s="252"/>
-      <c r="G52" s="252"/>
-      <c r="H52" s="252"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14267,22 +14285,16 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="252"/>
-      <c r="C59" s="252"/>
-      <c r="D59" s="252"/>
-      <c r="E59" s="252"/>
-      <c r="F59" s="252"/>
-      <c r="G59" s="252"/>
-      <c r="H59" s="252"/>
+      <c r="B59" s="153"/>
+      <c r="C59" s="153"/>
+      <c r="D59" s="153"/>
+      <c r="E59" s="153"/>
+      <c r="F59" s="153"/>
+      <c r="G59" s="153"/>
+      <c r="H59" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -14358,36 +14370,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14398,32 +14410,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="263" t="s">
+      <c r="S4" s="261" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
-      <c r="AA4" s="264"/>
-      <c r="AB4" s="264"/>
-      <c r="AC4" s="264"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14919,33 +14931,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="263" t="s">
+      <c r="S11" s="261" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="264"/>
-      <c r="U11" s="264"/>
-      <c r="V11" s="264"/>
-      <c r="W11" s="264"/>
-      <c r="X11" s="264"/>
-      <c r="Y11" s="264"/>
-      <c r="Z11" s="264"/>
-      <c r="AA11" s="264"/>
-      <c r="AB11" s="264"/>
-      <c r="AC11" s="264"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15386,33 +15398,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="251" t="s">
+      <c r="C19" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="251"/>
-      <c r="G19" s="251"/>
-      <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="251"/>
-      <c r="K19" s="251"/>
-      <c r="L19" s="251"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="260"/>
+      <c r="G19" s="260"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="260"/>
+      <c r="J19" s="260"/>
+      <c r="K19" s="260"/>
+      <c r="L19" s="260"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="263" t="s">
+      <c r="S19" s="261" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="264"/>
-      <c r="U19" s="264"/>
-      <c r="V19" s="264"/>
-      <c r="W19" s="264"/>
-      <c r="X19" s="264"/>
-      <c r="Y19" s="264"/>
-      <c r="Z19" s="264"/>
-      <c r="AA19" s="264"/>
-      <c r="AB19" s="264"/>
-      <c r="AC19" s="264"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16230,32 +16242,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="251" t="s">
+      <c r="C32" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="251"/>
-      <c r="E32" s="251"/>
-      <c r="F32" s="251"/>
-      <c r="G32" s="251"/>
-      <c r="H32" s="251"/>
-      <c r="I32" s="251"/>
-      <c r="J32" s="251"/>
-      <c r="K32" s="251"/>
-      <c r="L32" s="251"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="260"/>
+      <c r="H32" s="260"/>
+      <c r="I32" s="260"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="260"/>
+      <c r="L32" s="260"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="263" t="s">
+      <c r="S32" s="261" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="264"/>
-      <c r="U32" s="264"/>
-      <c r="V32" s="264"/>
-      <c r="W32" s="264"/>
-      <c r="X32" s="264"/>
-      <c r="Y32" s="264"/>
-      <c r="Z32" s="264"/>
-      <c r="AA32" s="264"/>
-      <c r="AB32" s="264"/>
-      <c r="AC32" s="264"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16512,18 +16524,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16560,35 +16572,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
+      <c r="P2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="251"/>
+      <c r="R2" s="251"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16597,31 +16609,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="P4" s="264" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="264"/>
-      <c r="R4" s="264"/>
-      <c r="S4" s="264"/>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16816,32 +16828,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="260" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="264" t="s">
+      <c r="P9" s="262" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="264"/>
-      <c r="R9" s="264"/>
-      <c r="S9" s="264"/>
-      <c r="T9" s="264"/>
-      <c r="U9" s="264"/>
-      <c r="V9" s="264"/>
-      <c r="W9" s="264"/>
-      <c r="X9" s="264"/>
-      <c r="Y9" s="264"/>
-      <c r="Z9" s="264"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17690,31 +17702,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="251" t="s">
+      <c r="C21" s="260" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="251"/>
-      <c r="G21" s="251"/>
-      <c r="H21" s="251"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="251"/>
-      <c r="P21" s="264" t="s">
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
+      <c r="P21" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="264"/>
-      <c r="R21" s="264"/>
-      <c r="S21" s="264"/>
-      <c r="T21" s="264"/>
-      <c r="U21" s="264"/>
-      <c r="V21" s="264"/>
-      <c r="W21" s="264"/>
-      <c r="X21" s="264"/>
-      <c r="Y21" s="264"/>
-      <c r="Z21" s="264"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18529,20 +18541,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -18560,18 +18572,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -18768,18 +18780,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="260" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19033,18 +19045,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="260" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19262,18 +19274,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="251" t="s">
+      <c r="C26" s="260" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="251"/>
-      <c r="E26" s="251"/>
-      <c r="F26" s="251"/>
-      <c r="G26" s="251"/>
-      <c r="H26" s="251"/>
-      <c r="I26" s="251"/>
-      <c r="J26" s="251"/>
-      <c r="K26" s="251"/>
-      <c r="L26" s="251"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19465,18 +19477,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="251" t="s">
+      <c r="C33" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
-      <c r="I33" s="251"/>
-      <c r="J33" s="251"/>
-      <c r="K33" s="251"/>
-      <c r="L33" s="251"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19660,18 +19672,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="251" t="s">
+      <c r="C40" s="260" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="251"/>
-      <c r="E40" s="251"/>
-      <c r="F40" s="251"/>
-      <c r="G40" s="251"/>
-      <c r="H40" s="251"/>
-      <c r="I40" s="251"/>
-      <c r="J40" s="251"/>
-      <c r="K40" s="251"/>
-      <c r="L40" s="251"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19935,12 +19947,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19948,6 +19954,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19985,20 +19997,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
       <c r="S2" s="265"/>
       <c r="T2" s="265"/>
       <c r="U2" s="265"/>
@@ -20016,18 +20028,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -20401,18 +20413,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="251" t="s">
+      <c r="C13" s="260" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="251"/>
-      <c r="F13" s="251"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="251"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="251"/>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20505,18 +20517,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20708,18 +20720,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="251" t="s">
+      <c r="C25" s="260" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="251"/>
-      <c r="H25" s="251"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20857,18 +20869,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="251" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="251"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="251"/>
-      <c r="G31" s="251"/>
-      <c r="H31" s="251"/>
-      <c r="I31" s="251"/>
-      <c r="J31" s="251"/>
-      <c r="K31" s="251"/>
-      <c r="L31" s="251"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21007,16 +21019,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21079,10 +21091,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="251" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="251"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21167,10 +21179,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="251" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="251"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21259,20 +21271,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -21290,18 +21302,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -21558,10 +21570,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="251" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="251"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21581,10 +21593,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="251" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="251"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21698,37 +21710,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21948,18 +21960,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22153,18 +22165,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="260" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
+      <c r="D17" s="260"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="260"/>
+      <c r="J17" s="260"/>
+      <c r="K17" s="260"/>
+      <c r="L17" s="260"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22298,18 +22310,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="251" t="s">
+      <c r="C22" s="260" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="251"/>
-      <c r="G22" s="251"/>
-      <c r="H22" s="251"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
+      <c r="D22" s="260"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="260"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="260"/>
+      <c r="I22" s="260"/>
+      <c r="J22" s="260"/>
+      <c r="K22" s="260"/>
+      <c r="L22" s="260"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22393,18 +22405,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="251" t="s">
+      <c r="C27" s="260" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="251"/>
-      <c r="G27" s="251"/>
-      <c r="H27" s="251"/>
-      <c r="I27" s="251"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
+      <c r="D27" s="260"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="260"/>
+      <c r="G27" s="260"/>
+      <c r="H27" s="260"/>
+      <c r="I27" s="260"/>
+      <c r="J27" s="260"/>
+      <c r="K27" s="260"/>
+      <c r="L27" s="260"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22645,7 +22657,7 @@
         <v>-22.043158871603321</v>
       </c>
       <c r="D35" s="168">
-        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
         <v>-12.448147509708797</v>
       </c>
       <c r="E35" s="168">
@@ -22705,10 +22717,10 @@
       <c r="N38" s="93"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="252" t="s">
+      <c r="B39" s="251" t="s">
         <v>244</v>
       </c>
-      <c r="C39" s="252"/>
+      <c r="C39" s="251"/>
       <c r="N39" s="93"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22810,10 +22822,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="251" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="252"/>
+      <c r="C52" s="251"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22869,10 +22881,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="252" t="s">
+      <c r="B60" s="251" t="s">
         <v>368</v>
       </c>
-      <c r="C60" s="252"/>
+      <c r="C60" s="251"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22973,10 +22985,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="252" t="s">
+      <c r="B73" s="251" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="252"/>
+      <c r="C73" s="251"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23078,17 +23090,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C17:L17"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23126,10 +23138,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="251" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="251"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23257,37 +23269,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="251"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="251"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23400,18 +23412,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23532,18 +23544,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="251" t="s">
+      <c r="C14" s="260" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="251"/>
-      <c r="H14" s="251"/>
-      <c r="I14" s="251"/>
-      <c r="J14" s="251"/>
-      <c r="K14" s="251"/>
-      <c r="L14" s="251"/>
+      <c r="D14" s="260"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="260"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="260"/>
+      <c r="I14" s="260"/>
+      <c r="J14" s="260"/>
+      <c r="K14" s="260"/>
+      <c r="L14" s="260"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23633,10 +23645,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="252" t="s">
+      <c r="B20" s="251" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="252"/>
+      <c r="C20" s="251"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23737,20 +23749,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -23768,18 +23780,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -24018,10 +24030,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="266" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="268"/>
+      <c r="C14" s="267"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24048,20 +24060,20 @@
       <c r="C17" s="177">
         <v>1.35</v>
       </c>
-      <c r="E17" s="266" t="s">
+      <c r="E17" s="268" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="267" t="s">
+      <c r="B19" s="266" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="268"/>
+      <c r="C19" s="267"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24127,10 +24139,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="266" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="267"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24206,16 +24218,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -34963,15 +34975,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="251" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="251"/>
+      <c r="E4" s="251" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35108,14 +35120,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="251" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="251"/>
+      <c r="E15" s="251" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35166,14 +35178,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="251" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="251"/>
+      <c r="E21" s="251" t="s">
         <v>291</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="251"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35242,14 +35254,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="251" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="251"/>
+      <c r="E29" s="251" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="251"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35325,14 +35337,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="251" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="251"/>
+      <c r="E37" s="251" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="251"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35401,14 +35413,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="251" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="251"/>
+      <c r="E45" s="251" t="s">
         <v>327</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="251"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35445,14 +35457,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="251" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="251"/>
+      <c r="E51" s="251" t="s">
         <v>345</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="251"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37434,14 +37446,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="255" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="F3" s="262" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="261"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38055,24 +38067,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38083,6 +38077,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EE935A-78E5-534B-B2FE-EAFF2D7BE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F73C0E1-A885-5443-A293-C7778230321E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2425,9 +2425,6 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2435,6 +2432,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2446,10 +2452,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2461,23 +2467,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12887,11 +12887,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.9829</v>
-    <v>-0.14000000000000001</v>
-    <v>-1.1110999999999999E-2</v>
-    <v>0.02</v>
-    <v>1.6050000000000001E-3</v>
+    <v>1.0584</v>
+    <v>4.4999999999999998E-2</v>
+    <v>3.4300000000000003E-3</v>
+    <v>0.01</v>
+    <v>7.5989999999999999E-4</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12899,25 +12899,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>12.81</v>
+    <v>13.249700000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.999607175778</v>
+    <v>46300.889504652347</v>
     <v>0</v>
-    <v>12.36</v>
-    <v>6493596284</v>
+    <v>12.81</v>
+    <v>6861010841</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.6</v>
-    <v>18.79</v>
-    <v>12.6</v>
-    <v>12.46</v>
-    <v>12.48</v>
+    <v>13.12</v>
+    <v>19.631699999999999</v>
+    <v>13.12</v>
+    <v>13.164999999999999</v>
+    <v>13.17</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>45670205</v>
-    <v>59393997</v>
+    <v>29522059</v>
+    <v>53761763</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12939,19 +12939,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13173,9 +13173,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13752,18 +13752,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="E2" s="252" t="s">
+      <c r="C2" s="252"/>
+      <c r="E2" s="251" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="253"/>
-      <c r="H2" s="252" t="s">
+      <c r="F2" s="252"/>
+      <c r="H2" s="251" t="s">
         <v>371</v>
       </c>
-      <c r="I2" s="253"/>
+      <c r="I2" s="252"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="202" t="s">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6535456.9000000004</v>
+        <v>6905239.9749999996</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5130431.9000000004</v>
+        <v>5500214.9749999996</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13843,14 +13843,14 @@
       </c>
       <c r="C6" s="225" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>12.48</v>
+        <v>13.17</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>18.597014925373131</v>
+        <v>19.649253731343279</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13867,14 +13867,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.14000000000000001</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>3.8648972169696747</v>
+        <v>4.0835771959394673</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13891,14 +13891,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.9643003077566005E-2</v>
+        <v>1.8591099000871438E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -13915,14 +13915,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.1110999999999999E-2</v>
+        <v>3.4300000000000003E-3</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.377207062600322E-2</v>
+        <v>5.0892518040258274E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.12084007383473329</v>
+        <v>-0.16792003949721043</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.6050000000000001E-3</v>
+        <v>7.5989999999999999E-4</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.9829</v>
+        <v>1.0584</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>59393997</v>
+        <v>53761763</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.21498496914576851</v>
+        <v>0.20347229134495071</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14046,10 +14046,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="253" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="254"/>
+      <c r="C17" s="253"/>
       <c r="E17" s="201" t="s">
         <v>338</v>
       </c>
@@ -14122,14 +14122,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="253" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="254"/>
-      <c r="E25" s="252" t="s">
+      <c r="C25" s="253"/>
+      <c r="E25" s="251" t="s">
         <v>391</v>
       </c>
-      <c r="F25" s="253"/>
+      <c r="F25" s="252"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="201" t="s">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14370,36 +14370,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="251" t="s">
+      <c r="S2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251" t="s">
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="251"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14410,32 +14410,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="263" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
+      <c r="AA4" s="264"/>
+      <c r="AB4" s="264"/>
+      <c r="AC4" s="264"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14931,33 +14931,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="262" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="261" t="s">
+      <c r="S11" s="263" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
-      <c r="AA11" s="262"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="262"/>
+      <c r="T11" s="264"/>
+      <c r="U11" s="264"/>
+      <c r="V11" s="264"/>
+      <c r="W11" s="264"/>
+      <c r="X11" s="264"/>
+      <c r="Y11" s="264"/>
+      <c r="Z11" s="264"/>
+      <c r="AA11" s="264"/>
+      <c r="AB11" s="264"/>
+      <c r="AC11" s="264"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15398,33 +15398,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="260" t="s">
+      <c r="C19" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="260"/>
-      <c r="G19" s="260"/>
-      <c r="H19" s="260"/>
-      <c r="I19" s="260"/>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="260"/>
+      <c r="D19" s="262"/>
+      <c r="E19" s="262"/>
+      <c r="F19" s="262"/>
+      <c r="G19" s="262"/>
+      <c r="H19" s="262"/>
+      <c r="I19" s="262"/>
+      <c r="J19" s="262"/>
+      <c r="K19" s="262"/>
+      <c r="L19" s="262"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="261" t="s">
+      <c r="S19" s="263" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="262"/>
-      <c r="U19" s="262"/>
-      <c r="V19" s="262"/>
-      <c r="W19" s="262"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="262"/>
-      <c r="Z19" s="262"/>
-      <c r="AA19" s="262"/>
-      <c r="AB19" s="262"/>
-      <c r="AC19" s="262"/>
+      <c r="T19" s="264"/>
+      <c r="U19" s="264"/>
+      <c r="V19" s="264"/>
+      <c r="W19" s="264"/>
+      <c r="X19" s="264"/>
+      <c r="Y19" s="264"/>
+      <c r="Z19" s="264"/>
+      <c r="AA19" s="264"/>
+      <c r="AB19" s="264"/>
+      <c r="AC19" s="264"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16242,32 +16242,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="262" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260"/>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="D32" s="262"/>
+      <c r="E32" s="262"/>
+      <c r="F32" s="262"/>
+      <c r="G32" s="262"/>
+      <c r="H32" s="262"/>
+      <c r="I32" s="262"/>
+      <c r="J32" s="262"/>
+      <c r="K32" s="262"/>
+      <c r="L32" s="262"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="261" t="s">
+      <c r="S32" s="263" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="262"/>
-      <c r="X32" s="262"/>
-      <c r="Y32" s="262"/>
-      <c r="Z32" s="262"/>
-      <c r="AA32" s="262"/>
-      <c r="AB32" s="262"/>
-      <c r="AC32" s="262"/>
+      <c r="T32" s="264"/>
+      <c r="U32" s="264"/>
+      <c r="V32" s="264"/>
+      <c r="W32" s="264"/>
+      <c r="X32" s="264"/>
+      <c r="Y32" s="264"/>
+      <c r="Z32" s="264"/>
+      <c r="AA32" s="264"/>
+      <c r="AB32" s="264"/>
+      <c r="AC32" s="264"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16524,18 +16524,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16572,35 +16572,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="P2" s="251" t="s">
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="P2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="251"/>
-      <c r="R2" s="251"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251" t="s">
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16609,31 +16609,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="P4" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16828,32 +16828,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="262" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="264" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="264"/>
+      <c r="R9" s="264"/>
+      <c r="S9" s="264"/>
+      <c r="T9" s="264"/>
+      <c r="U9" s="264"/>
+      <c r="V9" s="264"/>
+      <c r="W9" s="264"/>
+      <c r="X9" s="264"/>
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17702,31 +17702,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
-      <c r="P21" s="262" t="s">
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
+      <c r="P21" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
-      <c r="T21" s="262"/>
-      <c r="U21" s="262"/>
-      <c r="V21" s="262"/>
-      <c r="W21" s="262"/>
-      <c r="X21" s="262"/>
-      <c r="Y21" s="262"/>
-      <c r="Z21" s="262"/>
+      <c r="Q21" s="264"/>
+      <c r="R21" s="264"/>
+      <c r="S21" s="264"/>
+      <c r="T21" s="264"/>
+      <c r="U21" s="264"/>
+      <c r="V21" s="264"/>
+      <c r="W21" s="264"/>
+      <c r="X21" s="264"/>
+      <c r="Y21" s="264"/>
+      <c r="Z21" s="264"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18541,20 +18541,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -18572,18 +18572,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -18780,18 +18780,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="262" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="N11" s="93"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19045,18 +19045,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="262" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19274,18 +19274,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="262" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19477,18 +19477,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="262" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19672,18 +19672,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="262" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19947,6 +19947,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19954,12 +19960,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19997,20 +19997,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
       <c r="S2" s="265"/>
       <c r="T2" s="265"/>
       <c r="U2" s="265"/>
@@ -20028,18 +20028,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -20413,18 +20413,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="262" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20517,18 +20517,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="262" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20720,18 +20720,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="262" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="262"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="262"/>
+      <c r="K25" s="262"/>
+      <c r="L25" s="262"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20869,18 +20869,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21019,16 +21019,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21091,10 +21091,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="254"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6535456.9000000004</v>
+        <v>6905239.9749999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.9829</v>
+        <v>1.0584</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21179,10 +21179,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="254" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="251"/>
+      <c r="C15" s="254"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.6070500000000003E-2</v>
+        <v>0.100398</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.6070500000000003E-2</v>
+        <v>0.100398</v>
       </c>
     </row>
   </sheetData>
@@ -21271,20 +21271,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -21302,18 +21302,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -21570,10 +21570,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="251" t="s">
+      <c r="B13" s="254" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="251"/>
+      <c r="C13" s="254"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21593,10 +21593,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="251" t="s">
+      <c r="B18" s="254" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="251"/>
+      <c r="C18" s="254"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21710,37 +21710,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21960,18 +21960,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="262" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22165,18 +22165,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="260" t="s">
+      <c r="C17" s="262" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
+      <c r="D17" s="262"/>
+      <c r="E17" s="262"/>
+      <c r="F17" s="262"/>
+      <c r="G17" s="262"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="262"/>
+      <c r="J17" s="262"/>
+      <c r="K17" s="262"/>
+      <c r="L17" s="262"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22310,18 +22310,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="260" t="s">
+      <c r="C22" s="262" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="260"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="260"/>
-      <c r="J22" s="260"/>
-      <c r="K22" s="260"/>
-      <c r="L22" s="260"/>
+      <c r="D22" s="262"/>
+      <c r="E22" s="262"/>
+      <c r="F22" s="262"/>
+      <c r="G22" s="262"/>
+      <c r="H22" s="262"/>
+      <c r="I22" s="262"/>
+      <c r="J22" s="262"/>
+      <c r="K22" s="262"/>
+      <c r="L22" s="262"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22405,18 +22405,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="260" t="s">
+      <c r="C27" s="262" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="260"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="260"/>
-      <c r="I27" s="260"/>
-      <c r="J27" s="260"/>
-      <c r="K27" s="260"/>
-      <c r="L27" s="260"/>
+      <c r="D27" s="262"/>
+      <c r="E27" s="262"/>
+      <c r="F27" s="262"/>
+      <c r="G27" s="262"/>
+      <c r="H27" s="262"/>
+      <c r="I27" s="262"/>
+      <c r="J27" s="262"/>
+      <c r="K27" s="262"/>
+      <c r="L27" s="262"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22717,10 +22717,10 @@
       <c r="N38" s="93"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="251" t="s">
+      <c r="B39" s="254" t="s">
         <v>244</v>
       </c>
-      <c r="C39" s="251"/>
+      <c r="C39" s="254"/>
       <c r="N39" s="93"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22822,10 +22822,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="251" t="s">
+      <c r="B52" s="254" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="251"/>
+      <c r="C52" s="254"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22881,10 +22881,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="251" t="s">
+      <c r="B60" s="254" t="s">
         <v>368</v>
       </c>
-      <c r="C60" s="251"/>
+      <c r="C60" s="254"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22985,10 +22985,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="251" t="s">
+      <c r="B73" s="254" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="251"/>
+      <c r="C73" s="254"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23090,17 +23090,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23138,10 +23138,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="251"/>
+      <c r="C4" s="254"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.12084007383473329</v>
+        <v>-0.16792003949721043</v>
       </c>
     </row>
   </sheetData>
@@ -23269,37 +23269,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="262" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23412,18 +23412,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="262" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23544,18 +23544,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="260" t="s">
+      <c r="C14" s="262" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="260"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="260"/>
-      <c r="H14" s="260"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="260"/>
-      <c r="K14" s="260"/>
-      <c r="L14" s="260"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="262"/>
+      <c r="J14" s="262"/>
+      <c r="K14" s="262"/>
+      <c r="L14" s="262"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23645,10 +23645,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="251" t="s">
+      <c r="B20" s="254" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="251"/>
+      <c r="C20" s="254"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23749,20 +23749,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
       <c r="P3" s="265"/>
       <c r="Q3" s="265"/>
       <c r="R3" s="265"/>
@@ -23780,18 +23780,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="262" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -24030,10 +24030,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="267" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="268"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24060,20 +24060,20 @@
       <c r="C17" s="177">
         <v>1.35</v>
       </c>
-      <c r="E17" s="268" t="s">
+      <c r="E17" s="266" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="267" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="268"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6493603.7600000007</v>
+        <v>6861018.7399999993</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24134,15 +24134,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5088578.7600000007</v>
+        <v>5455993.7399999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="267" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="268"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24218,16 +24218,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30989,7 +30989,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32295,7 +32295,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.597014925373131</v>
+        <v>19.649253731343279</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32332,7 +32332,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.8648972169696747</v>
+        <v>4.0835771959394673</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.3325295360501213</v>
+        <v>3.5210875876484624</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6535456.9000000004</v>
+        <v>6905239.9749999996</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5130431.9000000004</v>
+        <v>5500214.9749999996</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32552,7 +32552,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>2.9813220498146857</v>
+        <v>3.1962050180781909</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32589,7 +32589,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>33.543635091665145</v>
+        <v>35.961339638308445</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32686,7 +32686,7 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="64">
-        <f>AC109+AC53+AC110+AC55+AC57+AC58</f>
+        <f>AC109+AC53+AC110+AC55+AC57+AC58+AC56</f>
         <v>-45127</v>
       </c>
     </row>
@@ -32724,7 +32724,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>50.908712687729796</v>
+        <v>53.78918158378513</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32761,7 +32761,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-113.68874288120195</v>
+        <v>-121.88301848117534</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32798,7 +32798,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.9643003077566005E-2</v>
+        <v>1.8591099000871438E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32835,7 +32835,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.377207062600322E-2</v>
+        <v>5.0892518040258274E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32909,7 +32909,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32946,7 +32946,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33449,7 +33449,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.21498496914576851</v>
+        <v>0.20347229134495071</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34975,15 +34975,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="254" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="251"/>
-      <c r="E4" s="251" t="s">
+      <c r="C4" s="254"/>
+      <c r="E4" s="254" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34991,7 +34991,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35007,7 +35007,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6535456.9000000004</v>
+        <v>6905239.9749999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5130431.9000000004</v>
+        <v>5500214.9749999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35047,7 +35047,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.597014925373131</v>
+        <v>19.649253731343279</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35067,7 +35067,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.8648972169696747</v>
+        <v>4.0835771959394673</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35087,7 +35087,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.3325295360501213</v>
+        <v>3.5210875876484624</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>2.9813220498146857</v>
+        <v>3.1962050180781909</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35116,18 +35116,18 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.543635091665145</v>
+        <v>35.961339638308445</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="251" t="s">
+      <c r="B15" s="254" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="251"/>
-      <c r="E15" s="251" t="s">
+      <c r="C15" s="254"/>
+      <c r="E15" s="254" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="251"/>
+      <c r="F15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35178,14 +35178,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="251" t="s">
+      <c r="B21" s="254" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="251"/>
-      <c r="E21" s="251" t="s">
+      <c r="C21" s="254"/>
+      <c r="E21" s="254" t="s">
         <v>291</v>
       </c>
-      <c r="F21" s="251"/>
+      <c r="F21" s="254"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35254,14 +35254,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="251" t="s">
+      <c r="B29" s="254" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="251"/>
-      <c r="E29" s="251" t="s">
+      <c r="C29" s="254"/>
+      <c r="E29" s="254" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="251"/>
+      <c r="F29" s="254"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35337,14 +35337,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="251" t="s">
+      <c r="B37" s="254" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="251"/>
-      <c r="E37" s="251" t="s">
+      <c r="C37" s="254"/>
+      <c r="E37" s="254" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="251"/>
+      <c r="F37" s="254"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.377207062600322E-2</v>
+        <v>5.0892518040258274E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.9643003077566005E-2</v>
+        <v>1.8591099000871438E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35400,7 +35400,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35409,18 +35409,18 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="251" t="s">
+      <c r="B45" s="254" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="251"/>
-      <c r="E45" s="251" t="s">
+      <c r="C45" s="254"/>
+      <c r="E45" s="254" t="s">
         <v>327</v>
       </c>
-      <c r="F45" s="251"/>
+      <c r="F45" s="254"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35453,18 +35453,18 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.21498496914576851</v>
+        <v>0.20347229134495071</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="251" t="s">
+      <c r="B51" s="254" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="251"/>
-      <c r="E51" s="251" t="s">
+      <c r="C51" s="254"/>
+      <c r="E51" s="254" t="s">
         <v>345</v>
       </c>
-      <c r="F51" s="251"/>
+      <c r="F51" s="254"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>12.46</v>
+        <v>13.164999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35661,7 +35661,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6535456.9000000004</v>
+        <v>6905239.9749999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35690,7 +35690,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5130431.9000000004</v>
+        <v>5500214.9749999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>18.597014925373131</v>
+        <v>19.649253731343279</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.8648972169696747</v>
+        <v>4.0835771959394673</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +35777,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.3325295360501213</v>
+        <v>3.5210875876484624</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>2.9813220498146857</v>
+        <v>3.1962050180781909</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35835,7 +35835,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>33.543635091665145</v>
+        <v>35.961339638308445</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.377207062600322E-2</v>
+        <v>5.0892518040258274E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.9643003077566005E-2</v>
+        <v>1.8591099000871438E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.1090929694601763E-2</v>
+        <v>3.8890465931996812E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36960,7 +36960,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.21498496914576851</v>
+        <v>0.20347229134495071</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37446,14 +37446,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="257" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="258"/>
+      <c r="F3" s="259" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="258"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37520,19 +37520,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="258">
+      <c r="C7" s="255">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="259"/>
-      <c r="F7" s="258">
+      <c r="D7" s="256"/>
+      <c r="F7" s="255">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="259"/>
+      <c r="G7" s="256"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37559,19 +37559,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="258">
+      <c r="C9" s="255">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="F9" s="258">
+      <c r="D9" s="256"/>
+      <c r="F9" s="255">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="259"/>
+      <c r="G9" s="256"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37598,19 +37598,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="258">
+      <c r="C11" s="255">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="F11" s="258">
+      <c r="D11" s="256"/>
+      <c r="F11" s="255">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="259"/>
+      <c r="G11" s="256"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37637,19 +37637,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="258">
+      <c r="C13" s="255">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="F13" s="258">
+      <c r="D13" s="256"/>
+      <c r="F13" s="255">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="259"/>
+      <c r="G13" s="256"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37676,19 +37676,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="258">
+      <c r="C15" s="255">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="F15" s="258">
+      <c r="D15" s="256"/>
+      <c r="F15" s="255">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="259"/>
+      <c r="G15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37715,19 +37715,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="258">
+      <c r="C17" s="255">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="259"/>
-      <c r="F17" s="258">
+      <c r="D17" s="256"/>
+      <c r="F17" s="255">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="259"/>
+      <c r="G17" s="256"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37754,22 +37754,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="258">
+      <c r="C19" s="255">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="F19" s="258">
+      <c r="D19" s="256"/>
+      <c r="F19" s="255">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="259"/>
+      <c r="G19" s="256"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -37796,22 +37796,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="258">
+      <c r="C21" s="255">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="F21" s="258">
+      <c r="D21" s="256"/>
+      <c r="F21" s="255">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="259"/>
+      <c r="G21" s="256"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37859,22 +37859,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="258">
+      <c r="C25" s="255">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="F25" s="258">
+      <c r="D25" s="256"/>
+      <c r="F25" s="255">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="259"/>
+      <c r="G25" s="256"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37901,22 +37901,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="258">
+      <c r="C27" s="255">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="259"/>
-      <c r="F27" s="258">
+      <c r="D27" s="256"/>
+      <c r="F27" s="255">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="259"/>
+      <c r="G27" s="256"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37943,22 +37943,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="258">
+      <c r="C29" s="255">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="259"/>
-      <c r="F29" s="258">
+      <c r="D29" s="256"/>
+      <c r="F29" s="255">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="259"/>
+      <c r="G29" s="256"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38006,22 +38006,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="258">
+      <c r="C33" s="255">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="F33" s="258">
+      <c r="D33" s="256"/>
+      <c r="F33" s="255">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="259"/>
+      <c r="G33" s="256"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38048,25 +38048,43 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="258">
+      <c r="C35" s="255">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="259"/>
-      <c r="F35" s="258">
+      <c r="D35" s="256"/>
+      <c r="F35" s="255">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="259"/>
+      <c r="G35" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38077,24 +38095,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F73C0E1-A885-5443-A293-C7778230321E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACE29FF-0040-C243-AB90-1450CF098768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2437,12 +2437,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2452,10 +2446,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2467,17 +2461,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12887,11 +12887,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>1.0584</v>
-    <v>4.4999999999999998E-2</v>
-    <v>3.4300000000000003E-3</v>
-    <v>0.01</v>
-    <v>7.5989999999999999E-4</v>
+    <v>1.0629999999999999</v>
+    <v>0.23</v>
+    <v>1.7357999999999998E-2</v>
+    <v>-0.04</v>
+    <v>-2.967E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12899,25 +12899,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>13.249700000000001</v>
+    <v>13.58</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46300.889504652347</v>
+    <v>46304.999111411722</v>
     <v>0</v>
-    <v>12.81</v>
-    <v>6861010841</v>
+    <v>13.19</v>
+    <v>7025174792</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.12</v>
-    <v>19.631699999999999</v>
-    <v>13.12</v>
-    <v>13.164999999999999</v>
-    <v>13.17</v>
+    <v>13.38</v>
+    <v>19.7593</v>
+    <v>13.25</v>
+    <v>13.48</v>
+    <v>13.44</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>29522059</v>
-    <v>53761763</v>
+    <v>25617369</v>
+    <v>48451119</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12939,19 +12939,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13173,9 +13173,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6905239.9749999996</v>
+        <v>7070462.2000000002</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5500214.9749999996</v>
+        <v>5665437.2000000002</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13843,14 +13843,14 @@
       </c>
       <c r="C6" s="225" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>13.17</v>
+        <v>13.44</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>19.649253731343279</v>
+        <v>20.119402985074622</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13867,14 +13867,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.4999999999999998E-2</v>
+        <v>0.23</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>4.0835771959394673</v>
+        <v>4.1812852716493749</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13891,14 +13891,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.8591099000871438E-2</v>
+        <v>1.8156663082082525E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -13915,14 +13915,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.4300000000000003E-3</v>
+        <v>1.7357999999999998E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.0892518040258274E-2</v>
+        <v>4.9703264094955499E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.16792003949721043</v>
+        <v>-0.18736404450895966</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.5989999999999999E-4</v>
+        <v>-2.967E-3</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0584</v>
+        <v>1.0629999999999999</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="I13" s="230">
         <f>'Reverse DCF'!C17</f>
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>53761763</v>
+        <v>48451119</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.20347229134495071</v>
+        <v>0.1987175605012074</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14376,8 +14376,8 @@
       <c r="D2" s="254"/>
       <c r="E2" s="254"/>
       <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="254"/>
@@ -14410,32 +14410,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="263" t="s">
+      <c r="S4" s="261" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
-      <c r="AA4" s="264"/>
-      <c r="AB4" s="264"/>
-      <c r="AC4" s="264"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14931,33 +14931,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="263" t="s">
+      <c r="S11" s="261" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="264"/>
-      <c r="U11" s="264"/>
-      <c r="V11" s="264"/>
-      <c r="W11" s="264"/>
-      <c r="X11" s="264"/>
-      <c r="Y11" s="264"/>
-      <c r="Z11" s="264"/>
-      <c r="AA11" s="264"/>
-      <c r="AB11" s="264"/>
-      <c r="AC11" s="264"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15398,33 +15398,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="262" t="s">
+      <c r="C19" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="262"/>
-      <c r="E19" s="262"/>
-      <c r="F19" s="262"/>
-      <c r="G19" s="262"/>
-      <c r="H19" s="262"/>
-      <c r="I19" s="262"/>
-      <c r="J19" s="262"/>
-      <c r="K19" s="262"/>
-      <c r="L19" s="262"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="260"/>
+      <c r="G19" s="260"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="260"/>
+      <c r="J19" s="260"/>
+      <c r="K19" s="260"/>
+      <c r="L19" s="260"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="263" t="s">
+      <c r="S19" s="261" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="264"/>
-      <c r="U19" s="264"/>
-      <c r="V19" s="264"/>
-      <c r="W19" s="264"/>
-      <c r="X19" s="264"/>
-      <c r="Y19" s="264"/>
-      <c r="Z19" s="264"/>
-      <c r="AA19" s="264"/>
-      <c r="AB19" s="264"/>
-      <c r="AC19" s="264"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16242,32 +16242,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="262" t="s">
+      <c r="C32" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="262"/>
-      <c r="E32" s="262"/>
-      <c r="F32" s="262"/>
-      <c r="G32" s="262"/>
-      <c r="H32" s="262"/>
-      <c r="I32" s="262"/>
-      <c r="J32" s="262"/>
-      <c r="K32" s="262"/>
-      <c r="L32" s="262"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="260"/>
+      <c r="H32" s="260"/>
+      <c r="I32" s="260"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="260"/>
+      <c r="L32" s="260"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="263" t="s">
+      <c r="S32" s="261" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="264"/>
-      <c r="U32" s="264"/>
-      <c r="V32" s="264"/>
-      <c r="W32" s="264"/>
-      <c r="X32" s="264"/>
-      <c r="Y32" s="264"/>
-      <c r="Z32" s="264"/>
-      <c r="AA32" s="264"/>
-      <c r="AB32" s="264"/>
-      <c r="AC32" s="264"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16524,18 +16524,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16578,8 +16578,8 @@
       <c r="D2" s="254"/>
       <c r="E2" s="254"/>
       <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="254"/>
@@ -16609,31 +16609,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="P4" s="264" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="264"/>
-      <c r="R4" s="264"/>
-      <c r="S4" s="264"/>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16828,32 +16828,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="260" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="264" t="s">
+      <c r="P9" s="262" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="264"/>
-      <c r="R9" s="264"/>
-      <c r="S9" s="264"/>
-      <c r="T9" s="264"/>
-      <c r="U9" s="264"/>
-      <c r="V9" s="264"/>
-      <c r="W9" s="264"/>
-      <c r="X9" s="264"/>
-      <c r="Y9" s="264"/>
-      <c r="Z9" s="264"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17702,31 +17702,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="262" t="s">
+      <c r="C21" s="260" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="262"/>
-      <c r="J21" s="262"/>
-      <c r="K21" s="262"/>
-      <c r="L21" s="262"/>
-      <c r="P21" s="264" t="s">
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
+      <c r="P21" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="264"/>
-      <c r="R21" s="264"/>
-      <c r="S21" s="264"/>
-      <c r="T21" s="264"/>
-      <c r="U21" s="264"/>
-      <c r="V21" s="264"/>
-      <c r="W21" s="264"/>
-      <c r="X21" s="264"/>
-      <c r="Y21" s="264"/>
-      <c r="Z21" s="264"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18547,8 +18547,8 @@
       <c r="D3" s="254"/>
       <c r="E3" s="254"/>
       <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="254"/>
@@ -18572,18 +18572,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -18780,18 +18780,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="260" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
       <c r="P11" s="265"/>
       <c r="Q11" s="265"/>
@@ -19045,18 +19045,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="260" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19274,18 +19274,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="262" t="s">
+      <c r="C26" s="260" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="262"/>
-      <c r="E26" s="262"/>
-      <c r="F26" s="262"/>
-      <c r="G26" s="262"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="262"/>
-      <c r="J26" s="262"/>
-      <c r="K26" s="262"/>
-      <c r="L26" s="262"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19477,18 +19477,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="262" t="s">
+      <c r="C33" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="262"/>
-      <c r="E33" s="262"/>
-      <c r="F33" s="262"/>
-      <c r="G33" s="262"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="262"/>
-      <c r="J33" s="262"/>
-      <c r="K33" s="262"/>
-      <c r="L33" s="262"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19672,18 +19672,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="262" t="s">
+      <c r="C40" s="260" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="262"/>
-      <c r="E40" s="262"/>
-      <c r="F40" s="262"/>
-      <c r="G40" s="262"/>
-      <c r="H40" s="262"/>
-      <c r="I40" s="262"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="262"/>
-      <c r="L40" s="262"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19947,12 +19947,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19960,6 +19954,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20003,8 +20003,8 @@
       <c r="D2" s="254"/>
       <c r="E2" s="254"/>
       <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="254"/>
@@ -20028,18 +20028,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="S4" s="265"/>
       <c r="T4" s="265"/>
       <c r="U4" s="265"/>
@@ -20413,18 +20413,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="262" t="s">
+      <c r="C13" s="260" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="262"/>
-      <c r="G13" s="262"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="262"/>
-      <c r="J13" s="262"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20517,18 +20517,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="260" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="262"/>
-      <c r="G18" s="262"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
-      <c r="K18" s="262"/>
-      <c r="L18" s="262"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20720,18 +20720,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="260" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="262"/>
-      <c r="E25" s="262"/>
-      <c r="F25" s="262"/>
-      <c r="G25" s="262"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="262"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="262"/>
-      <c r="L25" s="262"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20869,18 +20869,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="262" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21019,16 +21019,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6905239.9749999996</v>
+        <v>7070462.2000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>1.0584</v>
+        <v>1.0629999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.100398</v>
+        <v>0.100275</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.100398</v>
+        <v>0.100275</v>
       </c>
     </row>
   </sheetData>
@@ -21277,8 +21277,8 @@
       <c r="D3" s="254"/>
       <c r="E3" s="254"/>
       <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="254"/>
@@ -21302,18 +21302,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -21716,8 +21716,8 @@
       <c r="D2" s="254"/>
       <c r="E2" s="254"/>
       <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="254"/>
@@ -21729,18 +21729,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21960,18 +21960,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="262" t="s">
+      <c r="C11" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="262"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="262"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="262"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22165,18 +22165,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="262" t="s">
+      <c r="C17" s="260" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="262"/>
-      <c r="E17" s="262"/>
-      <c r="F17" s="262"/>
-      <c r="G17" s="262"/>
-      <c r="H17" s="262"/>
-      <c r="I17" s="262"/>
-      <c r="J17" s="262"/>
-      <c r="K17" s="262"/>
-      <c r="L17" s="262"/>
+      <c r="D17" s="260"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="260"/>
+      <c r="J17" s="260"/>
+      <c r="K17" s="260"/>
+      <c r="L17" s="260"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22310,18 +22310,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="262" t="s">
+      <c r="C22" s="260" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="262"/>
-      <c r="E22" s="262"/>
-      <c r="F22" s="262"/>
-      <c r="G22" s="262"/>
-      <c r="H22" s="262"/>
-      <c r="I22" s="262"/>
-      <c r="J22" s="262"/>
-      <c r="K22" s="262"/>
-      <c r="L22" s="262"/>
+      <c r="D22" s="260"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="260"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="260"/>
+      <c r="I22" s="260"/>
+      <c r="J22" s="260"/>
+      <c r="K22" s="260"/>
+      <c r="L22" s="260"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22405,18 +22405,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="262" t="s">
+      <c r="C27" s="260" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="262"/>
-      <c r="E27" s="262"/>
-      <c r="F27" s="262"/>
-      <c r="G27" s="262"/>
-      <c r="H27" s="262"/>
-      <c r="I27" s="262"/>
-      <c r="J27" s="262"/>
-      <c r="K27" s="262"/>
-      <c r="L27" s="262"/>
+      <c r="D27" s="260"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="260"/>
+      <c r="G27" s="260"/>
+      <c r="H27" s="260"/>
+      <c r="I27" s="260"/>
+      <c r="J27" s="260"/>
+      <c r="K27" s="260"/>
+      <c r="L27" s="260"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -23090,17 +23090,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23204,7 +23204,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.16792003949721043</v>
+        <v>-0.18736404450895966</v>
       </c>
     </row>
   </sheetData>
@@ -23275,8 +23275,8 @@
       <c r="D2" s="254"/>
       <c r="E2" s="254"/>
       <c r="F2" s="254"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="G2" s="263"/>
+      <c r="H2" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="254"/>
@@ -23288,18 +23288,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="262" t="s">
+      <c r="C4" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23412,18 +23412,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="260" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="262"/>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="262"/>
-      <c r="I9" s="262"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23544,18 +23544,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="262" t="s">
+      <c r="C14" s="260" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="262"/>
-      <c r="E14" s="262"/>
-      <c r="F14" s="262"/>
-      <c r="G14" s="262"/>
-      <c r="H14" s="262"/>
-      <c r="I14" s="262"/>
-      <c r="J14" s="262"/>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
+      <c r="D14" s="260"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="260"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="260"/>
+      <c r="I14" s="260"/>
+      <c r="J14" s="260"/>
+      <c r="K14" s="260"/>
+      <c r="L14" s="260"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23755,8 +23755,8 @@
       <c r="D3" s="254"/>
       <c r="E3" s="254"/>
       <c r="F3" s="254"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="G3" s="263"/>
+      <c r="H3" s="264" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="254"/>
@@ -23780,18 +23780,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="265"/>
       <c r="Q5" s="265"/>
       <c r="R5" s="265"/>
@@ -23888,23 +23888,23 @@
       </c>
       <c r="H7" s="147">
         <f>G7*(1+$C$17)</f>
-        <v>18800</v>
+        <v>19200</v>
       </c>
       <c r="I7" s="147">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>44180</v>
+        <v>46080</v>
       </c>
       <c r="J7" s="147">
         <f t="shared" si="0"/>
-        <v>103823</v>
+        <v>110592</v>
       </c>
       <c r="K7" s="147">
         <f t="shared" si="0"/>
-        <v>243984.05000000002</v>
+        <v>265420.79999999999</v>
       </c>
       <c r="L7" s="147">
         <f t="shared" si="0"/>
-        <v>573362.51750000007</v>
+        <v>637009.91999999993</v>
       </c>
       <c r="N7" s="93"/>
       <c r="O7" s="16"/>
@@ -23936,7 +23936,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>7310372.0981250005</v>
+        <v>8121876.4799999986</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -23990,23 +23990,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f>H7/(1+$C$21)^H9</f>
-        <v>17090.909090909088</v>
+        <v>17454.545454545452</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>36512.396694214869</v>
+        <v>38082.644628099166</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" si="1"/>
-        <v>78003.756574004481</v>
+        <v>83089.40646130727</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" si="1"/>
-        <v>166644.38904446413</v>
+        <v>181285.9777337613</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" si="1"/>
-        <v>356013.01295862795</v>
+        <v>395533.04232820641</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -24025,15 +24025,15 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f>L8/(1+C21)^L9</f>
-        <v>4539165.915222506</v>
+        <v>5043046.2896846319</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="266" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="268"/>
+      <c r="C14" s="267"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="C16" s="175">
         <f>C36</f>
-        <v>12.661190468083888</v>
+        <v>13.745436887017615</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24058,22 +24058,22 @@
         <v>370</v>
       </c>
       <c r="C17" s="177">
-        <v>1.35</v>
-      </c>
-      <c r="E17" s="266" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E17" s="268" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="267" t="s">
+      <c r="B19" s="266" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="268"/>
+      <c r="C19" s="267"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6861018.7399999993</v>
+        <v>7025182.8799999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24134,15 +24134,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5455993.7399999993</v>
+        <v>5620157.8799999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="266" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="267"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="C29" s="180">
         <f>SUM(H10:L10)</f>
-        <v>654264.46436222061</v>
+        <v>715445.61660591955</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="C30" s="180">
         <f>L11</f>
-        <v>4539165.915222506</v>
+        <v>5043046.2896846319</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="C31" s="183">
         <f>C29+C30</f>
-        <v>5193430.3795847269</v>
+        <v>5758491.9062905516</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="C34" s="183">
         <f>C31+C32-C33</f>
-        <v>6598455.3795847269</v>
+        <v>7163516.9062905516</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24213,21 +24213,21 @@
       </c>
       <c r="C36" s="186">
         <f>C34/C35</f>
-        <v>12.661190468083888</v>
+        <v>13.745436887017615</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30989,7 +30989,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32295,7 +32295,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.649253731343279</v>
+        <v>20.119402985074622</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32332,7 +32332,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.0835771959394673</v>
+        <v>4.1812852716493749</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.5210875876484624</v>
+        <v>3.6053369298519771</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6905239.9749999996</v>
+        <v>7070462.2000000002</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5500214.9749999996</v>
+        <v>5665437.2000000002</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32552,7 +32552,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.1962050180781909</v>
+        <v>3.292216557089545</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32589,7 +32589,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>35.961339638308445</v>
+        <v>37.04159060595758</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32724,7 +32724,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>53.78918158378513</v>
+        <v>55.07619960117156</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32761,7 +32761,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-121.88301848117534</v>
+        <v>-125.54429055775921</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32798,7 +32798,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.8591099000871438E-2</v>
+        <v>1.8156663082082525E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32835,7 +32835,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.0892518040258274E-2</v>
+        <v>4.9703264094955499E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32909,7 +32909,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32946,7 +32946,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33449,7 +33449,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.20347229134495071</v>
+        <v>0.1987175605012074</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34991,7 +34991,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35007,7 +35007,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6905239.9749999996</v>
+        <v>7070462.2000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5500214.9749999996</v>
+        <v>5665437.2000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35047,7 +35047,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.649253731343279</v>
+        <v>20.119402985074622</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35067,7 +35067,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.0835771959394673</v>
+        <v>4.1812852716493749</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35087,7 +35087,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.5210875876484624</v>
+        <v>3.6053369298519771</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.1962050180781909</v>
+        <v>3.292216557089545</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>35.961339638308445</v>
+        <v>37.04159060595758</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.0892518040258274E-2</v>
+        <v>4.9703264094955499E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.8591099000871438E-2</v>
+        <v>1.8156663082082525E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35400,7 +35400,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.20347229134495071</v>
+        <v>0.1987175605012074</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>13.164999999999999</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35661,7 +35661,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6905239.9749999996</v>
+        <v>7070462.2000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35690,7 +35690,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5500214.9749999996</v>
+        <v>5665437.2000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.649253731343279</v>
+        <v>20.119402985074622</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.0835771959394673</v>
+        <v>4.1812852716493749</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +35777,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.5210875876484624</v>
+        <v>3.6053369298519771</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.1962050180781909</v>
+        <v>3.292216557089545</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35835,7 +35835,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>35.961339638308445</v>
+        <v>37.04159060595758</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.0892518040258274E-2</v>
+        <v>4.9703264094955499E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.8591099000871438E-2</v>
+        <v>1.8156663082082525E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.8890465931996812E-2</v>
+        <v>3.7981675370529523E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36960,7 +36960,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.20347229134495071</v>
+        <v>0.1987175605012074</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37446,14 +37446,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="255" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37520,19 +37520,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="258">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="259"/>
+      <c r="F7" s="258">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="259"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37559,19 +37559,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="258">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="259"/>
+      <c r="F9" s="258">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="259"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37598,19 +37598,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="258">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="259"/>
+      <c r="F11" s="258">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="259"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37637,19 +37637,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="258">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="259"/>
+      <c r="F13" s="258">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="259"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37676,19 +37676,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="258">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="259"/>
+      <c r="F15" s="258">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37715,19 +37715,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="258">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="259"/>
+      <c r="F17" s="258">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="259"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37754,22 +37754,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="258">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="259"/>
+      <c r="F19" s="258">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="259"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -37796,22 +37796,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="258">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="259"/>
+      <c r="F21" s="258">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="259"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37859,22 +37859,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="258">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="259"/>
+      <c r="F25" s="258">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="259"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37901,22 +37901,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="258">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="259"/>
+      <c r="F27" s="258">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="259"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37943,22 +37943,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="258">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="259"/>
+      <c r="F29" s="258">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="259"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38006,22 +38006,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="258">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="F33" s="255">
+      <c r="D33" s="259"/>
+      <c r="F33" s="258">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="259"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38048,43 +38048,25 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="255">
+      <c r="C35" s="258">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="256"/>
-      <c r="F35" s="255">
+      <c r="D35" s="259"/>
+      <c r="F35" s="258">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="256"/>
+      <c r="G35" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38095,6 +38077,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACE29FF-0040-C243-AB90-1450CF098768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF7EC2-BA11-9645-9682-D05CDBD6917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="442">
   <si>
     <t>Ticker</t>
   </si>
@@ -1472,6 +1472,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1512,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1667,6 +1691,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2093,11 +2125,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2425,6 +2458,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="27" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2437,6 +2478,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2446,10 +2493,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2461,14 +2508,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2476,11 +2520,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12888,10 +12930,10 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>1.0629999999999999</v>
-    <v>0.23</v>
-    <v>1.7357999999999998E-2</v>
-    <v>-0.04</v>
-    <v>-2.967E-3</v>
+    <v>-0.155</v>
+    <v>-1.1498999999999999E-2</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12899,25 +12941,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>13.58</v>
+    <v>13.824999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46304.999111411722</v>
+    <v>46307.862073425778</v>
     <v>0</v>
-    <v>13.19</v>
-    <v>7025174792</v>
+    <v>13.11</v>
+    <v>6944395705</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.38</v>
-    <v>19.7593</v>
-    <v>13.25</v>
+    <v>13.64</v>
+    <v>19.8703</v>
     <v>13.48</v>
-    <v>13.44</v>
+    <v>13.324999999999999</v>
+    <v>13.32</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>25617369</v>
-    <v>48451119</v>
+    <v>22817057</v>
+    <v>46968664</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -13173,9 +13215,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13735,7 +13777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I59"/>
+  <dimension ref="B1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13747,25 +13789,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="251" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="252"/>
-      <c r="E2" s="251" t="s">
+      <c r="C2" s="256"/>
+      <c r="E2" s="255" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="252"/>
-      <c r="H2" s="251" t="s">
+      <c r="F2" s="256"/>
+      <c r="H2" s="255" t="s">
         <v>371</v>
       </c>
-      <c r="I2" s="252"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="256"/>
+      <c r="K2" s="153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="202" t="s">
         <v>11</v>
       </c>
@@ -13778,7 +13825,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>7070462.2000000002</v>
+        <v>6989162.375</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13788,8 +13835,11 @@
         <f>'AVG target price'!C5</f>
         <v>6.0868928055205176</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="253" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="202" t="s">
         <v>0</v>
       </c>
@@ -13802,7 +13852,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5665437.2000000002</v>
+        <v>5584137.375</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13812,14 +13862,17 @@
         <f>'AVG target price'!C6</f>
         <v>15.500001157758549</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="253" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="202" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13836,21 +13889,24 @@
         <f>'AVG target price'!C7</f>
         <v>11.635364421878764</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="253" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="202" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="225" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>13.44</v>
+        <v>13.32</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>20.119402985074622</v>
+        <v>19.88805970149253</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13860,21 +13916,24 @@
         <f>'AVG target price'!C8</f>
         <v>9.9292211427795856</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="202" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.23</v>
+        <v>-0.155</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>4.1812852716493749</v>
+        <v>4.1332066947127535</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13885,20 +13944,20 @@
         <v>11.620183872158711</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.8156663082082525E-2</v>
+        <v>1.8367866292418194E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -13909,20 +13968,20 @@
         <v>10.954332680019224</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="202" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.7357999999999998E-2</v>
+        <v>-1.1498999999999999E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>4.9703264094955499E-2</v>
+        <v>5.0281425891182001E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -13930,26 +13989,26 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.18736404450895966</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-0.17791124352576176</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.967E-3</v>
+        <v>0</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.7981675370529523E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>3.8423488479905288E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="202" t="s">
         <v>7</v>
       </c>
@@ -13972,7 +14031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
         <v>8</v>
       </c>
@@ -13988,7 +14047,7 @@
         <v>0.12448204853394841</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="202" t="s">
         <v>9</v>
       </c>
@@ -14011,13 +14070,13 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>48451119</v>
+        <v>46968664</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14027,16 +14086,16 @@
         <v>0.28139960185897273</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="202" t="s">
         <v>332</v>
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.1987175605012074</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.20102909685225334</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="203" t="s">
         <v>337</v>
       </c>
@@ -14044,12 +14103,16 @@
         <f>Statement!AC175</f>
         <v>2.6959777878408766</v>
       </c>
+      <c r="H16" s="255" t="s">
+        <v>434</v>
+      </c>
+      <c r="I16" s="256"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="253" t="s">
+      <c r="B17" s="257" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="253"/>
+      <c r="C17" s="257"/>
       <c r="E17" s="201" t="s">
         <v>338</v>
       </c>
@@ -14057,6 +14120,13 @@
         <f>Statement!AC171</f>
         <v>0.2226990648503856</v>
       </c>
+      <c r="H17" s="202" t="s">
+        <v>204</v>
+      </c>
+      <c r="I17" s="251">
+        <f>DCF!C15</f>
+        <v>0.1</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="201" t="s">
@@ -14072,7 +14142,13 @@
         <f>Statement!AC144</f>
         <v>45.101495784048865</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="203" t="s">
+        <v>435</v>
+      </c>
+      <c r="I18" s="252">
+        <f>Multiples!C54</f>
+        <v>0.12</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="201" t="s">
@@ -14122,14 +14198,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="253" t="s">
+      <c r="B25" s="257" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="253"/>
-      <c r="E25" s="251" t="s">
+      <c r="C25" s="257"/>
+      <c r="E25" s="255" t="s">
         <v>391</v>
       </c>
-      <c r="F25" s="252"/>
+      <c r="F25" s="256"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="201" t="s">
@@ -14294,13 +14370,14 @@
       <c r="H59" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14313,6 +14390,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{07A374E3-A90C-C541-BD83-0654A3D02307}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{5E6B57E8-C262-AE48-869D-CDD3B301EEE2}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{AA5F9CEA-31B2-764E-8F02-A27DAE03F15E}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{DCBD3BE1-7BD3-EA45-A5B8-9E5F9A6B387F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14322,18 +14405,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="253" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="253" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="253" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="253" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{AE83799E-225D-604F-9D69-5BFC5A531C5C}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{5CDECC07-667D-524A-B7CC-AB9CA3D5B46A}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{19DA5A41-6615-CD4E-B92F-034919BDD731}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{663BA583-AB34-5642-BA76-DF3C8370ADD6}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{A15FD498-8447-354F-AACB-70FDA2390BC3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14370,36 +14492,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254" t="s">
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14410,32 +14532,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="267" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
+      <c r="AA4" s="268"/>
+      <c r="AB4" s="268"/>
+      <c r="AC4" s="268"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14931,33 +15053,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="266" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="261" t="s">
+      <c r="S11" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
-      <c r="AA11" s="262"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="262"/>
+      <c r="T11" s="268"/>
+      <c r="U11" s="268"/>
+      <c r="V11" s="268"/>
+      <c r="W11" s="268"/>
+      <c r="X11" s="268"/>
+      <c r="Y11" s="268"/>
+      <c r="Z11" s="268"/>
+      <c r="AA11" s="268"/>
+      <c r="AB11" s="268"/>
+      <c r="AC11" s="268"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15398,33 +15520,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="260" t="s">
+      <c r="C19" s="266" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="260"/>
-      <c r="G19" s="260"/>
-      <c r="H19" s="260"/>
-      <c r="I19" s="260"/>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="260"/>
+      <c r="D19" s="266"/>
+      <c r="E19" s="266"/>
+      <c r="F19" s="266"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="266"/>
+      <c r="I19" s="266"/>
+      <c r="J19" s="266"/>
+      <c r="K19" s="266"/>
+      <c r="L19" s="266"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="261" t="s">
+      <c r="S19" s="267" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="262"/>
-      <c r="U19" s="262"/>
-      <c r="V19" s="262"/>
-      <c r="W19" s="262"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="262"/>
-      <c r="Z19" s="262"/>
-      <c r="AA19" s="262"/>
-      <c r="AB19" s="262"/>
-      <c r="AC19" s="262"/>
+      <c r="T19" s="268"/>
+      <c r="U19" s="268"/>
+      <c r="V19" s="268"/>
+      <c r="W19" s="268"/>
+      <c r="X19" s="268"/>
+      <c r="Y19" s="268"/>
+      <c r="Z19" s="268"/>
+      <c r="AA19" s="268"/>
+      <c r="AB19" s="268"/>
+      <c r="AC19" s="268"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16242,32 +16364,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="266" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260"/>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="D32" s="266"/>
+      <c r="E32" s="266"/>
+      <c r="F32" s="266"/>
+      <c r="G32" s="266"/>
+      <c r="H32" s="266"/>
+      <c r="I32" s="266"/>
+      <c r="J32" s="266"/>
+      <c r="K32" s="266"/>
+      <c r="L32" s="266"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="261" t="s">
+      <c r="S32" s="267" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="262"/>
-      <c r="X32" s="262"/>
-      <c r="Y32" s="262"/>
-      <c r="Z32" s="262"/>
-      <c r="AA32" s="262"/>
-      <c r="AB32" s="262"/>
-      <c r="AC32" s="262"/>
+      <c r="T32" s="268"/>
+      <c r="U32" s="268"/>
+      <c r="V32" s="268"/>
+      <c r="W32" s="268"/>
+      <c r="X32" s="268"/>
+      <c r="Y32" s="268"/>
+      <c r="Z32" s="268"/>
+      <c r="AA32" s="268"/>
+      <c r="AB32" s="268"/>
+      <c r="AC32" s="268"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16524,18 +16646,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16572,35 +16694,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="P2" s="254" t="s">
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="P2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254" t="s">
+      <c r="Q2" s="258"/>
+      <c r="R2" s="258"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16609,31 +16731,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="P4" s="268" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="268"/>
+      <c r="R4" s="268"/>
+      <c r="S4" s="268"/>
+      <c r="T4" s="268"/>
+      <c r="U4" s="268"/>
+      <c r="V4" s="268"/>
+      <c r="W4" s="268"/>
+      <c r="X4" s="268"/>
+      <c r="Y4" s="268"/>
+      <c r="Z4" s="268"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16828,32 +16950,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="266" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="268" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="268"/>
+      <c r="R9" s="268"/>
+      <c r="S9" s="268"/>
+      <c r="T9" s="268"/>
+      <c r="U9" s="268"/>
+      <c r="V9" s="268"/>
+      <c r="W9" s="268"/>
+      <c r="X9" s="268"/>
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17702,31 +17824,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="266" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
-      <c r="P21" s="262" t="s">
+      <c r="D21" s="266"/>
+      <c r="E21" s="266"/>
+      <c r="F21" s="266"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="266"/>
+      <c r="I21" s="266"/>
+      <c r="J21" s="266"/>
+      <c r="K21" s="266"/>
+      <c r="L21" s="266"/>
+      <c r="P21" s="268" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
-      <c r="T21" s="262"/>
-      <c r="U21" s="262"/>
-      <c r="V21" s="262"/>
-      <c r="W21" s="262"/>
-      <c r="X21" s="262"/>
-      <c r="Y21" s="262"/>
-      <c r="Z21" s="262"/>
+      <c r="Q21" s="268"/>
+      <c r="R21" s="268"/>
+      <c r="S21" s="268"/>
+      <c r="T21" s="268"/>
+      <c r="U21" s="268"/>
+      <c r="V21" s="268"/>
+      <c r="W21" s="268"/>
+      <c r="X21" s="268"/>
+      <c r="Y21" s="268"/>
+      <c r="Z21" s="268"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18541,60 +18663,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="P3" s="269"/>
+      <c r="Q3" s="269"/>
+      <c r="R3" s="269"/>
+      <c r="S3" s="269"/>
+      <c r="T3" s="269"/>
+      <c r="U3" s="269"/>
+      <c r="V3" s="269"/>
+      <c r="W3" s="269"/>
+      <c r="X3" s="269"/>
+      <c r="Y3" s="269"/>
+      <c r="Z3" s="269"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
+      <c r="P5" s="269"/>
+      <c r="Q5" s="269"/>
+      <c r="R5" s="269"/>
+      <c r="S5" s="269"/>
+      <c r="T5" s="269"/>
+      <c r="U5" s="269"/>
+      <c r="V5" s="269"/>
+      <c r="W5" s="269"/>
+      <c r="X5" s="269"/>
+      <c r="Y5" s="269"/>
+      <c r="Z5" s="269"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18780,30 +18902,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="266" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="265"/>
-      <c r="R11" s="265"/>
-      <c r="S11" s="265"/>
-      <c r="T11" s="265"/>
-      <c r="U11" s="265"/>
-      <c r="V11" s="265"/>
-      <c r="W11" s="265"/>
-      <c r="X11" s="265"/>
-      <c r="Y11" s="265"/>
-      <c r="Z11" s="265"/>
+      <c r="P11" s="269"/>
+      <c r="Q11" s="269"/>
+      <c r="R11" s="269"/>
+      <c r="S11" s="269"/>
+      <c r="T11" s="269"/>
+      <c r="U11" s="269"/>
+      <c r="V11" s="269"/>
+      <c r="W11" s="269"/>
+      <c r="X11" s="269"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="269"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19045,18 +19167,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="266" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19269,23 +19391,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="265"/>
-      <c r="C25" s="265"/>
+      <c r="B25" s="269"/>
+      <c r="C25" s="269"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="266" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="266"/>
+      <c r="E26" s="266"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="266"/>
+      <c r="I26" s="266"/>
+      <c r="J26" s="266"/>
+      <c r="K26" s="266"/>
+      <c r="L26" s="266"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19477,18 +19599,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="266" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="266"/>
+      <c r="E33" s="266"/>
+      <c r="F33" s="266"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="266"/>
+      <c r="I33" s="266"/>
+      <c r="J33" s="266"/>
+      <c r="K33" s="266"/>
+      <c r="L33" s="266"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19672,18 +19794,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="266" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="266"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="266"/>
+      <c r="K40" s="266"/>
+      <c r="L40" s="266"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19947,6 +20069,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19954,12 +20082,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19997,60 +20119,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="S2" s="265"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="265"/>
-      <c r="V2" s="265"/>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265"/>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
-      <c r="AA2" s="265"/>
-      <c r="AB2" s="265"/>
-      <c r="AC2" s="265"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="S2" s="269"/>
+      <c r="T2" s="269"/>
+      <c r="U2" s="269"/>
+      <c r="V2" s="269"/>
+      <c r="W2" s="269"/>
+      <c r="X2" s="269"/>
+      <c r="Y2" s="269"/>
+      <c r="Z2" s="269"/>
+      <c r="AA2" s="269"/>
+      <c r="AB2" s="269"/>
+      <c r="AC2" s="269"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="S4" s="265"/>
-      <c r="T4" s="265"/>
-      <c r="U4" s="265"/>
-      <c r="V4" s="265"/>
-      <c r="W4" s="265"/>
-      <c r="X4" s="265"/>
-      <c r="Y4" s="265"/>
-      <c r="Z4" s="265"/>
-      <c r="AA4" s="265"/>
-      <c r="AB4" s="265"/>
-      <c r="AC4" s="265"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20413,18 +20535,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="266" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="266"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="266"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20517,18 +20639,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="266" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20720,18 +20842,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="266" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="266"/>
+      <c r="E25" s="266"/>
+      <c r="F25" s="266"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="266"/>
+      <c r="I25" s="266"/>
+      <c r="J25" s="266"/>
+      <c r="K25" s="266"/>
+      <c r="L25" s="266"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20869,18 +20991,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="266" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="266"/>
+      <c r="I31" s="266"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="266"/>
+      <c r="L31" s="266"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21019,16 +21141,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21042,18 +21164,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="253" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="253" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="253" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="253" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>203</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{60C777D3-B454-B740-A85C-413B897A6526}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{4BA4A61B-F707-3A44-9212-8AFED0C81859}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{5D9EBEA6-4D49-F240-B19C-AF1A7B2D638A}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{A73A0022-45DD-6D43-803F-9FB5E3B859B9}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{7A977C7A-4ACC-F24D-BB36-E1438C150EA0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21091,10 +21252,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="258" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="258"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21111,7 +21272,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21120,7 +21281,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>7070462.2000000002</v>
+        <v>6989162.375</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21179,10 +21340,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="258" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="254"/>
+      <c r="C15" s="258"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21271,60 +21432,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="P3" s="269"/>
+      <c r="Q3" s="269"/>
+      <c r="R3" s="269"/>
+      <c r="S3" s="269"/>
+      <c r="T3" s="269"/>
+      <c r="U3" s="269"/>
+      <c r="V3" s="269"/>
+      <c r="W3" s="269"/>
+      <c r="X3" s="269"/>
+      <c r="Y3" s="269"/>
+      <c r="Z3" s="269"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="266" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
+      <c r="P5" s="269"/>
+      <c r="Q5" s="269"/>
+      <c r="R5" s="269"/>
+      <c r="S5" s="269"/>
+      <c r="T5" s="269"/>
+      <c r="U5" s="269"/>
+      <c r="V5" s="269"/>
+      <c r="W5" s="269"/>
+      <c r="X5" s="269"/>
+      <c r="Y5" s="269"/>
+      <c r="Z5" s="269"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21570,10 +21731,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="258" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="258"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21593,10 +21754,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="258" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="254"/>
+      <c r="C18" s="258"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21710,37 +21871,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="266" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21960,18 +22121,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="266" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="266"/>
+      <c r="I11" s="266"/>
+      <c r="J11" s="266"/>
+      <c r="K11" s="266"/>
+      <c r="L11" s="266"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22165,18 +22326,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="260" t="s">
+      <c r="C17" s="266" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
+      <c r="J17" s="266"/>
+      <c r="K17" s="266"/>
+      <c r="L17" s="266"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22310,18 +22471,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="260" t="s">
+      <c r="C22" s="266" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="260"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="260"/>
-      <c r="J22" s="260"/>
-      <c r="K22" s="260"/>
-      <c r="L22" s="260"/>
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="266"/>
+      <c r="J22" s="266"/>
+      <c r="K22" s="266"/>
+      <c r="L22" s="266"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22405,18 +22566,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="260" t="s">
+      <c r="C27" s="266" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="260"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="260"/>
-      <c r="I27" s="260"/>
-      <c r="J27" s="260"/>
-      <c r="K27" s="260"/>
-      <c r="L27" s="260"/>
+      <c r="D27" s="266"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="266"/>
+      <c r="I27" s="266"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="266"/>
+      <c r="L27" s="266"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22717,10 +22878,10 @@
       <c r="N38" s="93"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="254" t="s">
+      <c r="B39" s="258" t="s">
         <v>244</v>
       </c>
-      <c r="C39" s="254"/>
+      <c r="C39" s="258"/>
       <c r="N39" s="93"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22822,10 +22983,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="258" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="254"/>
+      <c r="C52" s="258"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -22881,10 +23042,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="254" t="s">
+      <c r="B60" s="258" t="s">
         <v>368</v>
       </c>
-      <c r="C60" s="254"/>
+      <c r="C60" s="258"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -22985,10 +23146,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="254" t="s">
+      <c r="B73" s="258" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="254"/>
+      <c r="C73" s="258"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23090,17 +23251,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23138,10 +23299,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="258" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="258"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23204,7 +23365,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23213,7 +23374,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.18736404450895966</v>
+        <v>-0.17791124352576176</v>
       </c>
     </row>
   </sheetData>
@@ -23229,18 +23390,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="253" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="253" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="253" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="253" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{ABC91E57-74F5-F947-881A-74D7B468126D}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{7D780858-565A-AA45-AA40-5ACC73A0F661}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{2B957273-5E1D-AD4F-BA8D-3F533013EA14}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{C9DC62F4-1FB6-8E4D-8933-496B7E82272E}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{A6C56304-CFA6-F649-98A4-DE698827E243}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23269,37 +23469,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="266" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23412,18 +23612,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="266" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="266"/>
+      <c r="E9" s="266"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="266"/>
+      <c r="L9" s="266"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23544,18 +23744,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="260" t="s">
+      <c r="C14" s="266" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="260"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="260"/>
-      <c r="H14" s="260"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="260"/>
-      <c r="K14" s="260"/>
-      <c r="L14" s="260"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="266"/>
+      <c r="L14" s="266"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23645,10 +23845,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="258" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="254"/>
+      <c r="C20" s="258"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23749,60 +23949,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="258" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="P3" s="269"/>
+      <c r="Q3" s="269"/>
+      <c r="R3" s="269"/>
+      <c r="S3" s="269"/>
+      <c r="T3" s="269"/>
+      <c r="U3" s="269"/>
+      <c r="V3" s="269"/>
+      <c r="W3" s="269"/>
+      <c r="X3" s="269"/>
+      <c r="Y3" s="269"/>
+      <c r="Z3" s="269"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="266" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
+      <c r="P5" s="269"/>
+      <c r="Q5" s="269"/>
+      <c r="R5" s="269"/>
+      <c r="S5" s="269"/>
+      <c r="T5" s="269"/>
+      <c r="U5" s="269"/>
+      <c r="V5" s="269"/>
+      <c r="W5" s="269"/>
+      <c r="X5" s="269"/>
+      <c r="Y5" s="269"/>
+      <c r="Z5" s="269"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24030,10 +24230,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="271" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="272"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24041,7 +24241,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24060,20 +24260,20 @@
       <c r="C17" s="177">
         <v>1.4</v>
       </c>
-      <c r="E17" s="268" t="s">
+      <c r="E17" s="270" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="271" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="272"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24107,7 +24307,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>7025182.8799999999</v>
+        <v>6944403.6999999993</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24134,15 +24334,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5620157.8799999999</v>
+        <v>5539378.6999999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="271" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="272"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24218,16 +24418,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30918,7 +31118,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30989,7 +31189,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32295,7 +32495,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>20.119402985074622</v>
+        <v>19.88805970149253</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32332,7 +32532,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1812852716493749</v>
+        <v>4.1332066947127535</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32393,7 +32593,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.6053369298519771</v>
+        <v>3.5638809043232635</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32454,7 +32654,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7070462.2000000002</v>
+        <v>6989162.375</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32515,7 +32715,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5665437.2000000002</v>
+        <v>5584137.375</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32552,7 +32752,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.292216557089545</v>
+        <v>3.244972783925228</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32589,7 +32789,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>37.04159060595758</v>
+        <v>36.510038542511182</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32724,7 +32924,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>55.07619960117156</v>
+        <v>54.442905021187762</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32761,7 +32961,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-125.54429055775921</v>
+        <v>-123.74271223436081</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32798,7 +32998,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.8156663082082525E-2</v>
+        <v>1.8367866292418194E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32835,7 +33035,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.9703264094955499E-2</v>
+        <v>5.0281425891182001E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32909,7 +33109,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32946,7 +33146,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33449,7 +33649,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.1987175605012074</v>
+        <v>0.20102909685225334</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34940,18 +35140,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="253" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="253" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="253" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="253" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>274</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{9358075E-BDDD-F04C-B85E-603B0E75FC86}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{A1184EF3-9BAF-6E49-998B-6E47058B62A6}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{BD3B7A15-6BA2-FF4A-8B39-17EC92F84AD4}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{52F1DA72-C103-D54B-B18D-DAEC3C15E402}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{74AA57F8-BD4A-A24E-A284-0359F23986E9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -34975,15 +35214,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="258" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="254"/>
-      <c r="E4" s="254" t="s">
+      <c r="C4" s="258"/>
+      <c r="E4" s="258" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34991,7 +35230,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35007,7 +35246,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7070462.2000000002</v>
+        <v>6989162.375</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35027,7 +35266,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5665437.2000000002</v>
+        <v>5584137.375</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35047,7 +35286,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.119402985074622</v>
+        <v>19.88805970149253</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35067,7 +35306,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1812852716493749</v>
+        <v>4.1332066947127535</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35087,7 +35326,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.6053369298519771</v>
+        <v>3.5638809043232635</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35107,7 +35346,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.292216557089545</v>
+        <v>3.244972783925228</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35116,18 +35355,18 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>37.04159060595758</v>
+        <v>36.510038542511182</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="254"/>
-      <c r="E15" s="254" t="s">
+      <c r="C15" s="258"/>
+      <c r="E15" s="258" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="254"/>
+      <c r="F15" s="258"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35178,14 +35417,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="258" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="254"/>
-      <c r="E21" s="254" t="s">
+      <c r="C21" s="258"/>
+      <c r="E21" s="258" t="s">
         <v>291</v>
       </c>
-      <c r="F21" s="254"/>
+      <c r="F21" s="258"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35254,14 +35493,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="258" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="254"/>
-      <c r="E29" s="254" t="s">
+      <c r="C29" s="258"/>
+      <c r="E29" s="258" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="254"/>
+      <c r="F29" s="258"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35337,14 +35576,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="258" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="E37" s="254" t="s">
+      <c r="C37" s="258"/>
+      <c r="E37" s="258" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="254"/>
+      <c r="F37" s="258"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35352,7 +35591,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.9703264094955499E-2</v>
+        <v>5.0281425891182001E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35368,7 +35607,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.8156663082082525E-2</v>
+        <v>1.8367866292418194E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35400,7 +35639,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35409,18 +35648,18 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="254" t="s">
+      <c r="B45" s="258" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="254"/>
-      <c r="E45" s="254" t="s">
+      <c r="C45" s="258"/>
+      <c r="E45" s="258" t="s">
         <v>327</v>
       </c>
-      <c r="F45" s="254"/>
+      <c r="F45" s="258"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35453,18 +35692,18 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.1987175605012074</v>
+        <v>0.20102909685225334</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="258" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="254"/>
-      <c r="E51" s="254" t="s">
+      <c r="C51" s="258"/>
+      <c r="E51" s="258" t="s">
         <v>345</v>
       </c>
-      <c r="F51" s="254"/>
+      <c r="F51" s="258"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35632,7 +35871,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>13.48</v>
+        <v>13.324999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35661,7 +35900,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7070462.2000000002</v>
+        <v>6989162.375</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35690,7 +35929,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5665437.2000000002</v>
+        <v>5584137.375</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35958,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.119402985074622</v>
+        <v>19.88805970149253</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35987,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1812852716493749</v>
+        <v>4.1332066947127535</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +36016,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.6053369298519771</v>
+        <v>3.5638809043232635</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +36045,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.292216557089545</v>
+        <v>3.244972783925228</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35835,7 +36074,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>37.04159060595758</v>
+        <v>36.510038542511182</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36608,7 +36847,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.9703264094955499E-2</v>
+        <v>5.0281425891182001E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36637,7 +36876,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.8156663082082525E-2</v>
+        <v>1.8367866292418194E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36695,7 +36934,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36724,7 +36963,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.7981675370529523E-2</v>
+        <v>3.8423488479905288E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36960,7 +37199,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.1987175605012074</v>
+        <v>0.20102909685225334</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37446,14 +37685,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="261" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="262"/>
+      <c r="F3" s="263" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="262"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37520,19 +37759,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="258">
+      <c r="C7" s="259">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="259"/>
-      <c r="F7" s="258">
+      <c r="D7" s="260"/>
+      <c r="F7" s="259">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="259"/>
+      <c r="G7" s="260"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37559,19 +37798,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="258">
+      <c r="C9" s="259">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="F9" s="258">
+      <c r="D9" s="260"/>
+      <c r="F9" s="259">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="259"/>
+      <c r="G9" s="260"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37598,19 +37837,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="258">
+      <c r="C11" s="259">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="F11" s="258">
+      <c r="D11" s="260"/>
+      <c r="F11" s="259">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="259"/>
+      <c r="G11" s="260"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37637,19 +37876,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="258">
+      <c r="C13" s="259">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="F13" s="258">
+      <c r="D13" s="260"/>
+      <c r="F13" s="259">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="259"/>
+      <c r="G13" s="260"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37676,19 +37915,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="258">
+      <c r="C15" s="259">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="F15" s="258">
+      <c r="D15" s="260"/>
+      <c r="F15" s="259">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="259"/>
+      <c r="G15" s="260"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37715,19 +37954,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="258">
+      <c r="C17" s="259">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="259"/>
-      <c r="F17" s="258">
+      <c r="D17" s="260"/>
+      <c r="F17" s="259">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="259"/>
+      <c r="G17" s="260"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37754,22 +37993,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="258">
+      <c r="C19" s="259">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="F19" s="258">
+      <c r="D19" s="260"/>
+      <c r="F19" s="259">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="259"/>
+      <c r="G19" s="260"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -37796,22 +38035,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="258">
+      <c r="C21" s="259">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="F21" s="258">
+      <c r="D21" s="260"/>
+      <c r="F21" s="259">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="259"/>
+      <c r="G21" s="260"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37859,22 +38098,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="258">
+      <c r="C25" s="259">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="F25" s="258">
+      <c r="D25" s="260"/>
+      <c r="F25" s="259">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="259"/>
+      <c r="G25" s="260"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37901,22 +38140,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="258">
+      <c r="C27" s="259">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="259"/>
-      <c r="F27" s="258">
+      <c r="D27" s="260"/>
+      <c r="F27" s="259">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="259"/>
+      <c r="G27" s="260"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37943,22 +38182,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="258">
+      <c r="C29" s="259">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="259"/>
-      <c r="F29" s="258">
+      <c r="D29" s="260"/>
+      <c r="F29" s="259">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="259"/>
+      <c r="G29" s="260"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38006,22 +38245,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="258">
+      <c r="C33" s="259">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="F33" s="258">
+      <c r="D33" s="260"/>
+      <c r="F33" s="259">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="259"/>
+      <c r="G33" s="260"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38048,25 +38287,43 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="258">
+      <c r="C35" s="259">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="259"/>
-      <c r="F35" s="258">
+      <c r="D35" s="260"/>
+      <c r="F35" s="259">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="259"/>
+      <c r="G35" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38077,24 +38334,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF7EC2-BA11-9645-9682-D05CDBD6917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3917E2-4FA2-7443-BF6B-E27396B1ED4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12929,11 +12929,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>1.0629999999999999</v>
-    <v>-0.155</v>
-    <v>-1.1498999999999999E-2</v>
-    <v>0</v>
-    <v>0</v>
+    <v>1.0570999999999999</v>
+    <v>-0.86</v>
+    <v>-6.2728000000000006E-2</v>
+    <v>-1.6199999999999999E-2</v>
+    <v>-1.261E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12941,25 +12941,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>13.824999999999999</v>
+    <v>14</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46307.862073425778</v>
+    <v>46311.999942303126</v>
     <v>0</v>
-    <v>13.11</v>
-    <v>6944395705</v>
+    <v>12.73</v>
+    <v>6696846890</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.64</v>
-    <v>19.8703</v>
-    <v>13.48</v>
-    <v>13.324999999999999</v>
-    <v>13.32</v>
+    <v>13.82</v>
+    <v>20.4453</v>
+    <v>13.71</v>
+    <v>12.85</v>
+    <v>12.8338</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>22817057</v>
-    <v>46968664</v>
+    <v>29329166</v>
+    <v>39538922</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12983,17 +12983,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>0.09</v>
+    <v>1.769E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>51.33</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>50.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.14</v>
+    <v>50.89</v>
+    <v>50.98</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13215,9 +13215,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13825,15 +13825,15 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6989162.375</v>
+        <v>6740017.75</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
       <c r="I3" s="228">
-        <f>'AVG target price'!C5</f>
-        <v>6.0868928055205176</v>
+        <f ca="1">'AVG target price'!C5</f>
+        <v>6.1654016785253178</v>
       </c>
       <c r="K3" s="253" t="s">
         <v>437</v>
@@ -13852,15 +13852,15 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5584137.375</v>
+        <v>5334992.75</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
       <c r="I4" s="228">
-        <f>'AVG target price'!C6</f>
-        <v>15.500001157758549</v>
+        <f ca="1">'AVG target price'!C6</f>
+        <v>15.584779571873772</v>
       </c>
       <c r="K4" s="253" t="s">
         <v>438</v>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13886,8 +13886,8 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="228">
-        <f>'AVG target price'!C7</f>
-        <v>11.635364421878764</v>
+        <f ca="1">'AVG target price'!C7</f>
+        <v>12.816574006568194</v>
       </c>
       <c r="K5" s="253" t="s">
         <v>439</v>
@@ -13899,22 +13899,22 @@
       </c>
       <c r="C6" s="225" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>13.32</v>
+        <v>12.8338</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>19.88805970149253</v>
+        <v>19.179104477611936</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
       <c r="I6" s="228">
-        <f>'AVG target price'!C8</f>
-        <v>9.9292211427795856</v>
+        <f ca="1">'AVG target price'!C8</f>
+        <v>9.9771246459122338</v>
       </c>
       <c r="K6" s="254" t="s">
         <v>440</v>
@@ -13926,22 +13926,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.155</v>
+        <v>-0.86</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>4.1332066947127535</v>
+        <v>3.9858691202295597</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
         <v>EV/Sales</v>
       </c>
       <c r="I7" s="228">
-        <f>'AVG target price'!C9</f>
-        <v>11.620183872158711</v>
+        <f ca="1">'AVG target price'!C9</f>
+        <v>11.679280439808901</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13950,22 +13950,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.6199999999999999E-2</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.8367866292418194E-2</v>
+        <v>1.9046834112565948E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I8" s="229">
-        <f>'AVG target price'!C10</f>
-        <v>10.954332680019224</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>11.244632068537683</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13974,14 +13974,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.1498999999999999E-2</v>
+        <v>-6.2728000000000006E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.0281425891182001E-2</v>
+        <v>5.2140077821011689E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.17791124352576176</v>
+        <v>-0.12493135653403241</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13998,14 +13998,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.261E-3</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14027,7 +14027,7 @@
         <v>418</v>
       </c>
       <c r="I11" s="229">
-        <f>DDM!C26</f>
+        <f ca="1">DDM!C26</f>
         <v>0</v>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0629999999999999</v>
+        <v>1.0570999999999999</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>46968664</v>
+        <v>39538922</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.20102909685225334</v>
+        <v>0.20846013350632497</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14124,8 +14124,8 @@
         <v>204</v>
       </c>
       <c r="I17" s="251">
-        <f>DCF!C15</f>
-        <v>0.1</v>
+        <f ca="1">DCF!C15</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14146,8 +14146,8 @@
         <v>435</v>
       </c>
       <c r="I18" s="252">
-        <f>Multiples!C54</f>
-        <v>0.12</v>
+        <f ca="1">Multiples!C54</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14242,7 +14242,7 @@
         <v>396</v>
       </c>
       <c r="C28" s="238">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -14250,7 +14250,7 @@
         <v>408</v>
       </c>
       <c r="C29" s="238">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6989162.375</v>
+        <v>6740017.75</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>1.0629999999999999</v>
+        <v>1.0570999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.100275</v>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.100275</v>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21637,8 +21637,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="147">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>2546669.7611987987</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>2593696.7249429207</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -21691,24 +21691,24 @@
       <c r="F10" s="158"/>
       <c r="G10" s="159"/>
       <c r="H10" s="147">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>-20536.052638107143</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>-20563.167979156024</v>
       </c>
       <c r="I10" s="147">
-        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>-16548.335891588267</v>
+        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <v>-16592.064841370357</v>
       </c>
       <c r="J10" s="147">
-        <f t="shared" si="0"/>
-        <v>47809.018190426032</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>47998.646200931391</v>
       </c>
       <c r="K10" s="147">
-        <f t="shared" si="0"/>
-        <v>71613.309765951213</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>71992.28592858593</v>
       </c>
       <c r="L10" s="147">
-        <f t="shared" si="0"/>
-        <v>124022.08294261179</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>124843.02781138883</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -21726,8 +21726,8 @@
       <c r="J11" s="158"/>
       <c r="K11" s="158"/>
       <c r="L11" s="147">
-        <f>L8/(1+C15)^L9</f>
-        <v>1581281.5575183004</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>1621141.9342913276</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21749,8 +21749,8 @@
         <v>204</v>
       </c>
       <c r="C15" s="156">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21764,8 +21764,8 @@
         <v>226</v>
       </c>
       <c r="C19" s="64">
-        <f>SUM(H10:L10)</f>
-        <v>206360.02236929361</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>207678.72712037977</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21773,8 +21773,8 @@
         <v>222</v>
       </c>
       <c r="C20" s="64">
-        <f>L11</f>
-        <v>1581281.5575183004</v>
+        <f ca="1">L11</f>
+        <v>1621141.9342913276</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21782,8 +21782,8 @@
         <v>227</v>
       </c>
       <c r="C21" s="96">
-        <f>C19+C20</f>
-        <v>1787641.5798875941</v>
+        <f ca="1">C19+C20</f>
+        <v>1828820.6614117073</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21809,8 +21809,8 @@
         <v>230</v>
       </c>
       <c r="C24" s="96">
-        <f>C21+C22-C23</f>
-        <v>3192666.5798875941</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>3233845.6614117073</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21827,8 +21827,8 @@
         <v>231</v>
       </c>
       <c r="C26" s="250">
-        <f>C24/C25</f>
-        <v>6.0868928055205176</v>
+        <f ca="1">C24/C25</f>
+        <v>6.1654016785253178</v>
       </c>
     </row>
   </sheetData>
@@ -22096,24 +22096,24 @@
       <c r="F9" s="158"/>
       <c r="G9" s="159"/>
       <c r="H9" s="94">
-        <f>DCF!H10</f>
-        <v>-20536.052638107143</v>
+        <f ca="1">DCF!H10</f>
+        <v>-20563.167979156024</v>
       </c>
       <c r="I9" s="94">
-        <f>DCF!I10</f>
-        <v>-16548.335891588267</v>
+        <f ca="1">DCF!I10</f>
+        <v>-16592.064841370357</v>
       </c>
       <c r="J9" s="94">
-        <f>DCF!J10</f>
-        <v>47809.018190426032</v>
+        <f ca="1">DCF!J10</f>
+        <v>47998.646200931391</v>
       </c>
       <c r="K9" s="94">
-        <f>DCF!K10</f>
-        <v>71613.309765951213</v>
+        <f ca="1">DCF!K10</f>
+        <v>71992.28592858593</v>
       </c>
       <c r="L9" s="94">
-        <f>DCF!L10</f>
-        <v>124022.08294261179</v>
+        <f ca="1">DCF!L10</f>
+        <v>124843.02781138883</v>
       </c>
       <c r="N9" s="93"/>
     </row>
@@ -22898,8 +22898,8 @@
         <v>204</v>
       </c>
       <c r="C41" s="156">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22924,8 +22924,8 @@
         <v>426</v>
       </c>
       <c r="C44" s="24">
-        <f>C43/(1+C41)^5</f>
-        <v>6642620.1678350428</v>
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>6686589.9578323811</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22933,8 +22933,8 @@
         <v>427</v>
       </c>
       <c r="C45" s="127">
-        <f>SUM(H9:K9)+C44</f>
-        <v>6724958.1072617248</v>
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>6769425.6571413716</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22960,8 +22960,8 @@
         <v>230</v>
       </c>
       <c r="C48" s="127">
-        <f>C45+C46-C47</f>
-        <v>8129983.1072617248</v>
+        <f ca="1">C45+C46-C47</f>
+        <v>8174450.6571413716</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22978,8 +22978,8 @@
         <v>248</v>
       </c>
       <c r="C50" s="250">
-        <f>C48/C49</f>
-        <v>15.500001157758549</v>
+        <f ca="1">C48/C49</f>
+        <v>15.584779571873772</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23002,8 +23002,8 @@
         <v>397</v>
       </c>
       <c r="C54" s="156">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23037,8 +23037,8 @@
         <v>248</v>
       </c>
       <c r="C58" s="250">
-        <f>C57/(1+C54)^5</f>
-        <v>11.635364421878764</v>
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>12.816574006568194</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23061,8 +23061,8 @@
         <v>204</v>
       </c>
       <c r="C62" s="156">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23087,8 +23087,8 @@
         <v>426</v>
       </c>
       <c r="C65" s="24">
-        <f>C64/(1+C62)^5</f>
-        <v>3720662.4882783531</v>
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>3745290.8343416648</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23096,8 +23096,8 @@
         <v>427</v>
       </c>
       <c r="C66" s="127">
-        <f>SUM(H9:K9)+C65</f>
-        <v>3803000.4277050351</v>
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>3828126.5336506558</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23123,8 +23123,8 @@
         <v>230</v>
       </c>
       <c r="C69" s="127">
-        <f>C66+C67-C68</f>
-        <v>5208025.4277050346</v>
+        <f ca="1">C66+C67-C68</f>
+        <v>5233151.5336506553</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23141,8 +23141,8 @@
         <v>248</v>
       </c>
       <c r="C71" s="250">
-        <f>C69/C70</f>
-        <v>9.9292211427795856</v>
+        <f ca="1">C69/C70</f>
+        <v>9.9771246459122338</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23165,8 +23165,8 @@
         <v>204</v>
       </c>
       <c r="C75" s="156">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23191,8 +23191,8 @@
         <v>426</v>
       </c>
       <c r="C78" s="24">
-        <f>C77/(1+C75)^5</f>
-        <v>4607597.8042786438</v>
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>4638097.0805773754</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23200,8 +23200,8 @@
         <v>427</v>
       </c>
       <c r="C79" s="127">
-        <f>SUM(H9:K9)+C78</f>
-        <v>4689935.7437053258</v>
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>4720932.7798863659</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23227,8 +23227,8 @@
         <v>230</v>
       </c>
       <c r="C82" s="127">
-        <f>C79+C80-C81</f>
-        <v>6094960.7437053258</v>
+        <f ca="1">C79+C80-C81</f>
+        <v>6125957.7798863659</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23245,8 +23245,8 @@
         <v>248</v>
       </c>
       <c r="C84" s="250">
-        <f>C82/C83</f>
-        <v>11.620183872158711</v>
+        <f ca="1">C82/C83</f>
+        <v>11.679280439808901</v>
       </c>
     </row>
   </sheetData>
@@ -23310,8 +23310,8 @@
         <v>254</v>
       </c>
       <c r="C5" s="154">
-        <f>DCF!C26</f>
-        <v>6.0868928055205176</v>
+        <f ca="1">DCF!C26</f>
+        <v>6.1654016785253178</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23319,8 +23319,8 @@
         <v>255</v>
       </c>
       <c r="C6" s="154">
-        <f>Multiples!C50</f>
-        <v>15.500001157758549</v>
+        <f ca="1">Multiples!C50</f>
+        <v>15.584779571873772</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23328,8 +23328,8 @@
         <v>256</v>
       </c>
       <c r="C7" s="154">
-        <f>Multiples!C58</f>
-        <v>11.635364421878764</v>
+        <f ca="1">Multiples!C58</f>
+        <v>12.816574006568194</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23337,8 +23337,8 @@
         <v>369</v>
       </c>
       <c r="C8" s="154">
-        <f>Multiples!C71</f>
-        <v>9.9292211427795856</v>
+        <f ca="1">Multiples!C71</f>
+        <v>9.9771246459122338</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23346,8 +23346,8 @@
         <v>429</v>
       </c>
       <c r="C9" s="154">
-        <f>Multiples!C84</f>
-        <v>11.620183872158711</v>
+        <f ca="1">Multiples!C84</f>
+        <v>11.679280439808901</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23355,8 +23355,8 @@
         <v>257</v>
       </c>
       <c r="C10" s="250">
-        <f>AVERAGE(C5:C9)</f>
-        <v>10.954332680019224</v>
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>11.244632068537683</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23374,7 +23374,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.17791124352576176</v>
+        <v>-0.12493135653403241</v>
       </c>
     </row>
   </sheetData>
@@ -23882,8 +23882,8 @@
         <v>397</v>
       </c>
       <c r="C24" s="156">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23899,7 +23899,7 @@
         <v>248</v>
       </c>
       <c r="C26" s="250">
-        <f>C23/(C24-C25)</f>
+        <f ca="1">C23/(C24-C25)</f>
         <v>0</v>
       </c>
     </row>
@@ -24135,8 +24135,8 @@
       <c r="J8" s="158"/>
       <c r="K8" s="158"/>
       <c r="L8" s="147">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>8121876.4799999986</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>8271855.5611429745</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -24189,24 +24189,24 @@
       <c r="F10" s="158"/>
       <c r="G10" s="159"/>
       <c r="H10" s="147">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>17454.545454545452</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>17477.592042962104</v>
       </c>
       <c r="I10" s="147">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>38082.644628099166</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>38183.277952526536</v>
       </c>
       <c r="J10" s="147">
-        <f t="shared" si="1"/>
-        <v>83089.40646130727</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>83418.96936466101</v>
       </c>
       <c r="K10" s="147">
-        <f t="shared" si="1"/>
-        <v>181285.9777337613</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>182245.33939998734</v>
       </c>
       <c r="L10" s="147">
-        <f t="shared" si="1"/>
-        <v>395533.04232820641</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>398151.2117205183</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -24224,8 +24224,8 @@
       <c r="J11" s="158"/>
       <c r="K11" s="158"/>
       <c r="L11" s="147">
-        <f>L8/(1+C21)^L9</f>
-        <v>5043046.2896846319</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>5170169.5867564883</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24241,7 +24241,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24249,8 +24249,8 @@
         <v>263</v>
       </c>
       <c r="C16" s="175">
-        <f>C36</f>
-        <v>13.745436887017615</v>
+        <f ca="1">C36</f>
+        <v>13.997096794888947</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24288,8 +24288,8 @@
         <v>204</v>
       </c>
       <c r="C21" s="239">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.8549499999999984E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6944403.6999999993</v>
+        <v>6696854.5999999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5539378.6999999993</v>
+        <v>5291829.5999999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24349,8 +24349,8 @@
         <v>226</v>
       </c>
       <c r="C29" s="180">
-        <f>SUM(H10:L10)</f>
-        <v>715445.61660591955</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>719476.39048065525</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24358,8 +24358,8 @@
         <v>222</v>
       </c>
       <c r="C30" s="180">
-        <f>L11</f>
-        <v>5043046.2896846319</v>
+        <f ca="1">L11</f>
+        <v>5170169.5867564883</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24367,8 +24367,8 @@
         <v>227</v>
       </c>
       <c r="C31" s="183">
-        <f>C29+C30</f>
-        <v>5758491.9062905516</v>
+        <f ca="1">C29+C30</f>
+        <v>5889645.9772371436</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24394,8 +24394,8 @@
         <v>230</v>
       </c>
       <c r="C34" s="183">
-        <f>C31+C32-C33</f>
-        <v>7163516.9062905516</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>7294670.9772371436</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24412,8 +24412,8 @@
         <v>231</v>
       </c>
       <c r="C36" s="186">
-        <f>C34/C35</f>
-        <v>13.745436887017615</v>
+        <f ca="1">C34/C35</f>
+        <v>13.997096794888947</v>
       </c>
     </row>
   </sheetData>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31189,7 +31189,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32495,7 +32495,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.88805970149253</v>
+        <v>19.179104477611936</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32532,7 +32532,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1332066947127535</v>
+        <v>3.9858691202295597</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32593,7 +32593,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.5638809043232635</v>
+        <v>3.4368382454449482</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6989162.375</v>
+        <v>6740017.75</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32715,7 +32715,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5584137.375</v>
+        <v>5334992.75</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32752,7 +32752,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.244972783925228</v>
+        <v>3.1001934790668377</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32789,7 +32789,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>36.510038542511182</v>
+        <v>34.88108867065931</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32924,7 +32924,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>54.442905021187762</v>
+        <v>52.502163566398707</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32961,7 +32961,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-123.74271223436081</v>
+        <v>-118.22174640459149</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32998,7 +32998,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.8367866292418194E-2</v>
+        <v>1.9046834112565948E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33035,7 +33035,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.0281425891182001E-2</v>
+        <v>5.2140077821011689E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33109,7 +33109,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -33146,7 +33146,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33649,7 +33649,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.20102909685225334</v>
+        <v>0.20846013350632497</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35230,7 +35230,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35246,7 +35246,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6989162.375</v>
+        <v>6740017.75</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35266,7 +35266,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5584137.375</v>
+        <v>5334992.75</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.88805970149253</v>
+        <v>19.179104477611936</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35306,7 +35306,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1332066947127535</v>
+        <v>3.9858691202295597</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.5638809043232635</v>
+        <v>3.4368382454449482</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35346,7 +35346,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.244972783925228</v>
+        <v>3.1001934790668377</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35355,7 +35355,7 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>36.510038542511182</v>
+        <v>34.88108867065931</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35591,7 +35591,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.0281425891182001E-2</v>
+        <v>5.2140077821011689E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35607,7 +35607,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.8367866292418194E-2</v>
+        <v>1.9046834112565948E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35639,7 +35639,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35692,7 +35692,7 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.20102909685225334</v>
+        <v>0.20846013350632497</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>13.324999999999999</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35900,7 +35900,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6989162.375</v>
+        <v>6740017.75</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5584137.375</v>
+        <v>5334992.75</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.88805970149253</v>
+        <v>19.179104477611936</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35987,7 +35987,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1332066947127535</v>
+        <v>3.9858691202295597</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.5638809043232635</v>
+        <v>3.4368382454449482</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36045,7 +36045,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.244972783925228</v>
+        <v>3.1001934790668377</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36074,7 +36074,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>36.510038542511182</v>
+        <v>34.88108867065931</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36847,7 +36847,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.0281425891182001E-2</v>
+        <v>5.2140077821011689E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36876,7 +36876,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.8367866292418194E-2</v>
+        <v>1.9046834112565948E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.8423488479905288E-2</v>
+        <v>3.9843811984026305E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.20102909685225334</v>
+        <v>0.20846013350632497</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3917E2-4FA2-7443-BF6B-E27396B1ED4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61E221-9121-C84C-B1C4-0E80A1D8C487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,19 +179,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="443">
   <si>
     <t>Ticker</t>
   </si>
@@ -1496,6 +1526,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2130,7 +2163,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2478,12 +2511,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2493,10 +2520,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2508,11 +2535,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2520,6 +2550,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12910,7 +12946,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12930,10 +12966,8 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>1.0570999999999999</v>
-    <v>-0.86</v>
-    <v>-6.2728000000000006E-2</v>
-    <v>-1.6199999999999999E-2</v>
-    <v>-1.261E-3</v>
+    <v>0.39500000000000002</v>
+    <v>3.0106999999999998E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12941,35 +12975,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>14</v>
+    <v>13.61</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46311.999942303126</v>
+    <v>46315.725339664059</v>
     <v>0</v>
-    <v>12.73</v>
-    <v>6696846890</v>
+    <v>13.12</v>
+    <v>7043415231</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.82</v>
-    <v>20.4453</v>
-    <v>13.71</v>
-    <v>12.85</v>
-    <v>12.8338</v>
+    <v>13.14</v>
+    <v>20.153600000000001</v>
+    <v>13.12</v>
+    <v>13.515000000000001</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>29329166</v>
-    <v>39538922</v>
+    <v>18791043</v>
+    <v>37474468</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12983,28 +13031,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.09</v>
-    <v>1.769E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>51.33</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>50.67</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.14</v>
-    <v>50.89</v>
+    <v>50.9</v>
     <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13026,8 +13074,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13048,7 +13094,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13058,6 +13103,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13093,7 +13143,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13104,16 +13154,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13207,19 +13254,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13291,9 +13332,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13301,9 +13339,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13787,7 +13822,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13825,7 +13860,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>6740017.75</v>
+        <v>7088820.2250000006</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13833,7 +13868,7 @@
       </c>
       <c r="I3" s="228">
         <f ca="1">'AVG target price'!C5</f>
-        <v>6.1654016785253178</v>
+        <v>6.144546720051661</v>
       </c>
       <c r="K3" s="253" t="s">
         <v>437</v>
@@ -13852,7 +13887,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5334992.75</v>
+        <v>5683795.2250000006</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13860,7 +13895,7 @@
       </c>
       <c r="I4" s="228">
         <f ca="1">'AVG target price'!C6</f>
-        <v>15.584779571873772</v>
+        <v>15.562504631749382</v>
       </c>
       <c r="K4" s="253" t="s">
         <v>438</v>
@@ -13872,7 +13907,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13887,7 +13922,7 @@
       </c>
       <c r="I5" s="228">
         <f ca="1">'AVG target price'!C7</f>
-        <v>12.816574006568194</v>
+        <v>12.794430042483771</v>
       </c>
       <c r="K5" s="253" t="s">
         <v>439</v>
@@ -13897,16 +13932,16 @@
       <c r="B6" s="202" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="225" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>12.8338</v>
+      <c r="C6" s="225" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>19.179104477611936</v>
+        <v>20.171641791044774</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13914,7 +13949,7 @@
       </c>
       <c r="I6" s="228">
         <f ca="1">'AVG target price'!C8</f>
-        <v>9.9771246459122338</v>
+        <v>9.9645383877409692</v>
       </c>
       <c r="K6" s="254" t="s">
         <v>440</v>
@@ -13926,14 +13961,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.86</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>3.9858691202295597</v>
+        <v>4.1921417245060315</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13941,23 +13976,23 @@
       </c>
       <c r="I7" s="228">
         <f ca="1">'AVG target price'!C9</f>
-        <v>11.679280439808901</v>
+        <v>11.663753264919423</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.6199999999999999E-2</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.9046834112565948E-2</v>
+        <v>1.8109642496964295E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -13965,7 +14000,7 @@
       </c>
       <c r="I8" s="229">
         <f ca="1">'AVG target price'!C10</f>
-        <v>11.244632068537683</v>
+        <v>11.22595460938904</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13974,14 +14009,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.2728000000000006E-2</v>
+        <v>3.0106999999999998E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>5.2140077821011689E-2</v>
+        <v>4.9574546799852022E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -13989,23 +14024,23 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.12493135653403241</v>
+        <v>-0.16937072812511728</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.261E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14062,10 +14097,10 @@
         <f>Statement!AC125</f>
         <v>0.18573545162533595</v>
       </c>
-      <c r="H13" s="201" t="s">
+      <c r="H13" s="275" t="s">
         <v>433</v>
       </c>
-      <c r="I13" s="230">
+      <c r="I13" s="273">
         <f>'Reverse DCF'!C17</f>
         <v>1.4</v>
       </c>
@@ -14076,7 +14111,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>39538922</v>
+        <v>37474468</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14085,6 +14120,13 @@
         <f>Statement!AC140</f>
         <v>0.28139960185897273</v>
       </c>
+      <c r="H14" s="203" t="s">
+        <v>442</v>
+      </c>
+      <c r="I14" s="274">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>13.930245418047543</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="202" t="s">
@@ -14092,7 +14134,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.20846013350632497</v>
+        <v>0.19820293862791533</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14125,7 +14167,7 @@
       </c>
       <c r="I17" s="251">
         <f ca="1">DCF!C15</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14147,7 +14189,7 @@
       </c>
       <c r="I18" s="252">
         <f ca="1">Multiples!C54</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14214,12 +14256,12 @@
       <c r="C26" s="187">
         <v>0.21</v>
       </c>
-      <c r="E26" s="202" t="e" vm="2">
+      <c r="E26" s="202" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>50.98</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14234,7 +14276,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14498,8 +14540,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="258"/>
@@ -14532,32 +14574,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="267" t="s">
+      <c r="S4" s="265" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="268"/>
-      <c r="AC4" s="268"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
+      <c r="AA4" s="266"/>
+      <c r="AB4" s="266"/>
+      <c r="AC4" s="266"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15053,33 +15095,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="267" t="s">
+      <c r="S11" s="265" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="268"/>
-      <c r="U11" s="268"/>
-      <c r="V11" s="268"/>
-      <c r="W11" s="268"/>
-      <c r="X11" s="268"/>
-      <c r="Y11" s="268"/>
-      <c r="Z11" s="268"/>
-      <c r="AA11" s="268"/>
-      <c r="AB11" s="268"/>
-      <c r="AC11" s="268"/>
+      <c r="T11" s="266"/>
+      <c r="U11" s="266"/>
+      <c r="V11" s="266"/>
+      <c r="W11" s="266"/>
+      <c r="X11" s="266"/>
+      <c r="Y11" s="266"/>
+      <c r="Z11" s="266"/>
+      <c r="AA11" s="266"/>
+      <c r="AB11" s="266"/>
+      <c r="AC11" s="266"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15520,33 +15562,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="266" t="s">
+      <c r="C19" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="266"/>
-      <c r="E19" s="266"/>
-      <c r="F19" s="266"/>
-      <c r="G19" s="266"/>
-      <c r="H19" s="266"/>
-      <c r="I19" s="266"/>
-      <c r="J19" s="266"/>
-      <c r="K19" s="266"/>
-      <c r="L19" s="266"/>
+      <c r="D19" s="264"/>
+      <c r="E19" s="264"/>
+      <c r="F19" s="264"/>
+      <c r="G19" s="264"/>
+      <c r="H19" s="264"/>
+      <c r="I19" s="264"/>
+      <c r="J19" s="264"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="267" t="s">
+      <c r="S19" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="268"/>
-      <c r="U19" s="268"/>
-      <c r="V19" s="268"/>
-      <c r="W19" s="268"/>
-      <c r="X19" s="268"/>
-      <c r="Y19" s="268"/>
-      <c r="Z19" s="268"/>
-      <c r="AA19" s="268"/>
-      <c r="AB19" s="268"/>
-      <c r="AC19" s="268"/>
+      <c r="T19" s="266"/>
+      <c r="U19" s="266"/>
+      <c r="V19" s="266"/>
+      <c r="W19" s="266"/>
+      <c r="X19" s="266"/>
+      <c r="Y19" s="266"/>
+      <c r="Z19" s="266"/>
+      <c r="AA19" s="266"/>
+      <c r="AB19" s="266"/>
+      <c r="AC19" s="266"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16364,32 +16406,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="266" t="s">
+      <c r="C32" s="264" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="266"/>
-      <c r="E32" s="266"/>
-      <c r="F32" s="266"/>
-      <c r="G32" s="266"/>
-      <c r="H32" s="266"/>
-      <c r="I32" s="266"/>
-      <c r="J32" s="266"/>
-      <c r="K32" s="266"/>
-      <c r="L32" s="266"/>
+      <c r="D32" s="264"/>
+      <c r="E32" s="264"/>
+      <c r="F32" s="264"/>
+      <c r="G32" s="264"/>
+      <c r="H32" s="264"/>
+      <c r="I32" s="264"/>
+      <c r="J32" s="264"/>
+      <c r="K32" s="264"/>
+      <c r="L32" s="264"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="267" t="s">
+      <c r="S32" s="265" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="268"/>
-      <c r="U32" s="268"/>
-      <c r="V32" s="268"/>
-      <c r="W32" s="268"/>
-      <c r="X32" s="268"/>
-      <c r="Y32" s="268"/>
-      <c r="Z32" s="268"/>
-      <c r="AA32" s="268"/>
-      <c r="AB32" s="268"/>
-      <c r="AC32" s="268"/>
+      <c r="T32" s="266"/>
+      <c r="U32" s="266"/>
+      <c r="V32" s="266"/>
+      <c r="W32" s="266"/>
+      <c r="X32" s="266"/>
+      <c r="Y32" s="266"/>
+      <c r="Z32" s="266"/>
+      <c r="AA32" s="266"/>
+      <c r="AB32" s="266"/>
+      <c r="AC32" s="266"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16646,18 +16688,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16700,8 +16742,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="258"/>
@@ -16731,31 +16773,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="P4" s="268" t="s">
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="P4" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="268"/>
-      <c r="R4" s="268"/>
-      <c r="S4" s="268"/>
-      <c r="T4" s="268"/>
-      <c r="U4" s="268"/>
-      <c r="V4" s="268"/>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
+      <c r="Q4" s="266"/>
+      <c r="R4" s="266"/>
+      <c r="S4" s="266"/>
+      <c r="T4" s="266"/>
+      <c r="U4" s="266"/>
+      <c r="V4" s="266"/>
+      <c r="W4" s="266"/>
+      <c r="X4" s="266"/>
+      <c r="Y4" s="266"/>
+      <c r="Z4" s="266"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16950,32 +16992,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="268" t="s">
+      <c r="P9" s="266" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="268"/>
-      <c r="R9" s="268"/>
-      <c r="S9" s="268"/>
-      <c r="T9" s="268"/>
-      <c r="U9" s="268"/>
-      <c r="V9" s="268"/>
-      <c r="W9" s="268"/>
-      <c r="X9" s="268"/>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
+      <c r="Q9" s="266"/>
+      <c r="R9" s="266"/>
+      <c r="S9" s="266"/>
+      <c r="T9" s="266"/>
+      <c r="U9" s="266"/>
+      <c r="V9" s="266"/>
+      <c r="W9" s="266"/>
+      <c r="X9" s="266"/>
+      <c r="Y9" s="266"/>
+      <c r="Z9" s="266"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17824,31 +17866,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="266" t="s">
+      <c r="C21" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="266"/>
-      <c r="E21" s="266"/>
-      <c r="F21" s="266"/>
-      <c r="G21" s="266"/>
-      <c r="H21" s="266"/>
-      <c r="I21" s="266"/>
-      <c r="J21" s="266"/>
-      <c r="K21" s="266"/>
-      <c r="L21" s="266"/>
-      <c r="P21" s="268" t="s">
+      <c r="D21" s="264"/>
+      <c r="E21" s="264"/>
+      <c r="F21" s="264"/>
+      <c r="G21" s="264"/>
+      <c r="H21" s="264"/>
+      <c r="I21" s="264"/>
+      <c r="J21" s="264"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="P21" s="266" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="268"/>
-      <c r="R21" s="268"/>
-      <c r="S21" s="268"/>
-      <c r="T21" s="268"/>
-      <c r="U21" s="268"/>
-      <c r="V21" s="268"/>
-      <c r="W21" s="268"/>
-      <c r="X21" s="268"/>
-      <c r="Y21" s="268"/>
-      <c r="Z21" s="268"/>
+      <c r="Q21" s="266"/>
+      <c r="R21" s="266"/>
+      <c r="S21" s="266"/>
+      <c r="T21" s="266"/>
+      <c r="U21" s="266"/>
+      <c r="V21" s="266"/>
+      <c r="W21" s="266"/>
+      <c r="X21" s="266"/>
+      <c r="Y21" s="266"/>
+      <c r="Z21" s="266"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18669,8 +18711,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="258"/>
@@ -18694,18 +18736,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -18902,18 +18944,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="93"/>
       <c r="P11" s="269"/>
       <c r="Q11" s="269"/>
@@ -19167,18 +19209,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19396,18 +19438,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="266" t="s">
+      <c r="C26" s="264" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="266"/>
-      <c r="J26" s="266"/>
-      <c r="K26" s="266"/>
-      <c r="L26" s="266"/>
+      <c r="D26" s="264"/>
+      <c r="E26" s="264"/>
+      <c r="F26" s="264"/>
+      <c r="G26" s="264"/>
+      <c r="H26" s="264"/>
+      <c r="I26" s="264"/>
+      <c r="J26" s="264"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19599,18 +19641,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="264" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="266"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="266"/>
-      <c r="J33" s="266"/>
-      <c r="K33" s="266"/>
-      <c r="L33" s="266"/>
+      <c r="D33" s="264"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="264"/>
+      <c r="G33" s="264"/>
+      <c r="H33" s="264"/>
+      <c r="I33" s="264"/>
+      <c r="J33" s="264"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19794,18 +19836,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="264" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="266"/>
-      <c r="I40" s="266"/>
-      <c r="J40" s="266"/>
-      <c r="K40" s="266"/>
-      <c r="L40" s="266"/>
+      <c r="D40" s="264"/>
+      <c r="E40" s="264"/>
+      <c r="F40" s="264"/>
+      <c r="G40" s="264"/>
+      <c r="H40" s="264"/>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="264"/>
+      <c r="L40" s="264"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20069,12 +20111,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20082,6 +20118,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20125,8 +20167,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="258"/>
@@ -20150,18 +20192,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
       <c r="S4" s="269"/>
       <c r="T4" s="269"/>
       <c r="U4" s="269"/>
@@ -20535,18 +20577,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="264" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
+      <c r="D13" s="264"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="264"/>
+      <c r="J13" s="264"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20639,18 +20681,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="264" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20842,18 +20884,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="264" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="266"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="266"/>
-      <c r="I25" s="266"/>
-      <c r="J25" s="266"/>
-      <c r="K25" s="266"/>
-      <c r="L25" s="266"/>
+      <c r="D25" s="264"/>
+      <c r="E25" s="264"/>
+      <c r="F25" s="264"/>
+      <c r="G25" s="264"/>
+      <c r="H25" s="264"/>
+      <c r="I25" s="264"/>
+      <c r="J25" s="264"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20991,18 +21033,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="264" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="266"/>
-      <c r="E31" s="266"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="266"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="266"/>
-      <c r="L31" s="266"/>
+      <c r="D31" s="264"/>
+      <c r="E31" s="264"/>
+      <c r="F31" s="264"/>
+      <c r="G31" s="264"/>
+      <c r="H31" s="264"/>
+      <c r="I31" s="264"/>
+      <c r="J31" s="264"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21141,16 +21183,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21272,7 +21314,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21281,7 +21323,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6740017.75</v>
+        <v>7088820.2250000006</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21299,7 +21341,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21378,7 +21420,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21387,7 +21429,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21438,8 +21480,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="258"/>
@@ -21463,18 +21505,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -21638,7 +21680,7 @@
       </c>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2593696.7249429207</v>
+        <v>2581209.5717811957</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -21692,23 +21734,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-20563.167979156024</v>
+        <v>-20556.057419441247</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-16592.064841370357</v>
+        <v>-16580.59204982904</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>47998.646200931391</v>
+        <v>47948.870908069846</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>71992.28592858593</v>
+        <v>71892.760409691662</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>124843.02781138883</v>
+        <v>124627.32901991546</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -21727,7 +21769,7 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1621141.9342913276</v>
+        <v>1610549.6119994903</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21750,7 +21792,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21765,7 +21807,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>207678.72712037977</v>
+        <v>207332.31086840667</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21774,7 +21816,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1621141.9342913276</v>
+        <v>1610549.6119994903</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21783,7 +21825,7 @@
       </c>
       <c r="C21" s="96">
         <f ca="1">C19+C20</f>
-        <v>1828820.6614117073</v>
+        <v>1817881.922867897</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21810,7 +21852,7 @@
       </c>
       <c r="C24" s="96">
         <f ca="1">C21+C22-C23</f>
-        <v>3233845.6614117073</v>
+        <v>3222906.922867897</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21828,7 +21870,7 @@
       </c>
       <c r="C26" s="250">
         <f ca="1">C24/C25</f>
-        <v>6.1654016785253178</v>
+        <v>6.144546720051661</v>
       </c>
     </row>
   </sheetData>
@@ -21877,8 +21919,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="258"/>
@@ -21890,18 +21932,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22097,23 +22139,23 @@
       <c r="G9" s="159"/>
       <c r="H9" s="94">
         <f ca="1">DCF!H10</f>
-        <v>-20563.167979156024</v>
+        <v>-20556.057419441247</v>
       </c>
       <c r="I9" s="94">
         <f ca="1">DCF!I10</f>
-        <v>-16592.064841370357</v>
+        <v>-16580.59204982904</v>
       </c>
       <c r="J9" s="94">
         <f ca="1">DCF!J10</f>
-        <v>47998.646200931391</v>
+        <v>47948.870908069846</v>
       </c>
       <c r="K9" s="94">
         <f ca="1">DCF!K10</f>
-        <v>71992.28592858593</v>
+        <v>71892.760409691662</v>
       </c>
       <c r="L9" s="94">
         <f ca="1">DCF!L10</f>
-        <v>124843.02781138883</v>
+        <v>124627.32901991546</v>
       </c>
       <c r="N9" s="93"/>
     </row>
@@ -22121,18 +22163,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
+      <c r="D11" s="264"/>
+      <c r="E11" s="264"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22326,18 +22368,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="264" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
+      <c r="D17" s="264"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22471,18 +22513,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="266" t="s">
+      <c r="C22" s="264" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="266"/>
-      <c r="L22" s="266"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="264"/>
+      <c r="G22" s="264"/>
+      <c r="H22" s="264"/>
+      <c r="I22" s="264"/>
+      <c r="J22" s="264"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22566,18 +22608,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="266" t="s">
+      <c r="C27" s="264" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="266"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="266"/>
-      <c r="L27" s="266"/>
+      <c r="D27" s="264"/>
+      <c r="E27" s="264"/>
+      <c r="F27" s="264"/>
+      <c r="G27" s="264"/>
+      <c r="H27" s="264"/>
+      <c r="I27" s="264"/>
+      <c r="J27" s="264"/>
+      <c r="K27" s="264"/>
+      <c r="L27" s="264"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22899,7 +22941,7 @@
       </c>
       <c r="C41" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22925,7 +22967,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>6686589.9578323811</v>
+        <v>6675037.1350735361</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22934,7 +22976,7 @@
       </c>
       <c r="C45" s="127">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>6769425.6571413716</v>
+        <v>6757742.1169220274</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -22961,7 +23003,7 @@
       </c>
       <c r="C48" s="127">
         <f ca="1">C45+C46-C47</f>
-        <v>8174450.6571413716</v>
+        <v>8162767.1169220274</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -22979,7 +23021,7 @@
       </c>
       <c r="C50" s="250">
         <f ca="1">C48/C49</f>
-        <v>15.584779571873772</v>
+        <v>15.562504631749382</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23003,7 +23045,7 @@
       </c>
       <c r="C54" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23038,7 +23080,7 @@
       </c>
       <c r="C58" s="250">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>12.816574006568194</v>
+        <v>12.794430042483771</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23062,7 +23104,7 @@
       </c>
       <c r="C62" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23088,7 +23130,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>3745290.8343416648</v>
+        <v>3738819.8705974636</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23097,7 +23139,7 @@
       </c>
       <c r="C66" s="127">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>3828126.5336506558</v>
+        <v>3821524.8524459549</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23124,7 +23166,7 @@
       </c>
       <c r="C69" s="127">
         <f ca="1">C66+C67-C68</f>
-        <v>5233151.5336506553</v>
+        <v>5226549.8524459545</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23142,7 +23184,7 @@
       </c>
       <c r="C71" s="250">
         <f ca="1">C69/C70</f>
-        <v>9.9771246459122338</v>
+        <v>9.9645383877409692</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23166,7 +23208,7 @@
       </c>
       <c r="C75" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23192,7 +23234,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>4638097.0805773754</v>
+        <v>4630083.56190072</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23201,7 +23243,7 @@
       </c>
       <c r="C79" s="127">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>4720932.7798863659</v>
+        <v>4712788.5437492114</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23228,7 +23270,7 @@
       </c>
       <c r="C82" s="127">
         <f ca="1">C79+C80-C81</f>
-        <v>6125957.7798863659</v>
+        <v>6117813.5437492114</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23246,22 +23288,22 @@
       </c>
       <c r="C84" s="250">
         <f ca="1">C82/C83</f>
-        <v>11.679280439808901</v>
+        <v>11.663753264919423</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23311,7 +23353,7 @@
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
-        <v>6.1654016785253178</v>
+        <v>6.144546720051661</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23320,7 +23362,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Multiples!C50</f>
-        <v>15.584779571873772</v>
+        <v>15.562504631749382</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23329,7 +23371,7 @@
       </c>
       <c r="C7" s="154">
         <f ca="1">Multiples!C58</f>
-        <v>12.816574006568194</v>
+        <v>12.794430042483771</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23338,7 +23380,7 @@
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C71</f>
-        <v>9.9771246459122338</v>
+        <v>9.9645383877409692</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23347,7 +23389,7 @@
       </c>
       <c r="C9" s="154">
         <f ca="1">Multiples!C84</f>
-        <v>11.679280439808901</v>
+        <v>11.663753264919423</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23356,7 +23398,7 @@
       </c>
       <c r="C10" s="250">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>11.244632068537683</v>
+        <v>11.22595460938904</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23365,7 +23407,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23374,7 +23416,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.12493135653403241</v>
+        <v>-0.16937072812511728</v>
       </c>
     </row>
   </sheetData>
@@ -23475,8 +23517,8 @@
       <c r="D2" s="258"/>
       <c r="E2" s="258"/>
       <c r="F2" s="258"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="265" t="s">
+      <c r="G2" s="267"/>
+      <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="258"/>
@@ -23488,18 +23530,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="264" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23612,18 +23654,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="264" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23744,18 +23786,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="264" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
+      <c r="D14" s="264"/>
+      <c r="E14" s="264"/>
+      <c r="F14" s="264"/>
+      <c r="G14" s="264"/>
+      <c r="H14" s="264"/>
+      <c r="I14" s="264"/>
+      <c r="J14" s="264"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23883,7 +23925,7 @@
       </c>
       <c r="C24" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23955,8 +23997,8 @@
       <c r="D3" s="258"/>
       <c r="E3" s="258"/>
       <c r="F3" s="258"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="265" t="s">
+      <c r="G3" s="267"/>
+      <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="258"/>
@@ -23980,18 +24022,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
       <c r="P5" s="269"/>
       <c r="Q5" s="269"/>
       <c r="R5" s="269"/>
@@ -24136,7 +24178,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>8271855.5611429745</v>
+        <v>8232031.3494954351</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -24190,23 +24232,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>17477.592042962104</v>
+        <v>17471.548447830362</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>38183.277952526536</v>
+        <v>38156.875645610453</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>83418.96936466101</v>
+        <v>83332.462682515179</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>182245.33939998734</v>
+        <v>181993.39487932247</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>398151.2117205183</v>
+        <v>397463.30197740055</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -24225,15 +24267,15 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>5170169.5867564883</v>
+        <v>5136388.3974553067</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="271" t="s">
+      <c r="B14" s="270" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="272"/>
+      <c r="C14" s="271"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24241,7 +24283,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24250,7 +24292,7 @@
       </c>
       <c r="C16" s="175">
         <f ca="1">C36</f>
-        <v>13.997096794888947</v>
+        <v>13.930245418047543</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24260,20 +24302,20 @@
       <c r="C17" s="177">
         <v>1.4</v>
       </c>
-      <c r="E17" s="270" t="s">
+      <c r="E17" s="272" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="270"/>
-      <c r="G17" s="270"/>
-      <c r="H17" s="270"/>
-      <c r="I17" s="270"/>
+      <c r="F17" s="272"/>
+      <c r="G17" s="272"/>
+      <c r="H17" s="272"/>
+      <c r="I17" s="272"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="271" t="s">
+      <c r="B19" s="270" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="272"/>
+      <c r="C19" s="271"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24289,7 +24331,7 @@
       </c>
       <c r="C21" s="239">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8549499999999984E-2</v>
+        <v>9.8929500000000004E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24307,7 +24349,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>6696854.5999999996</v>
+        <v>7043423.3399999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24334,15 +24376,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5291829.5999999996</v>
+        <v>5638398.3399999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="271" t="s">
+      <c r="B28" s="270" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="272"/>
+      <c r="C28" s="271"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24350,7 +24392,7 @@
       </c>
       <c r="C29" s="180">
         <f ca="1">SUM(H10:L10)</f>
-        <v>719476.39048065525</v>
+        <v>718417.58363267896</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24359,7 +24401,7 @@
       </c>
       <c r="C30" s="180">
         <f ca="1">L11</f>
-        <v>5170169.5867564883</v>
+        <v>5136388.3974553067</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24368,7 +24410,7 @@
       </c>
       <c r="C31" s="183">
         <f ca="1">C29+C30</f>
-        <v>5889645.9772371436</v>
+        <v>5854805.9810879854</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24395,7 +24437,7 @@
       </c>
       <c r="C34" s="183">
         <f ca="1">C31+C32-C33</f>
-        <v>7294670.9772371436</v>
+        <v>7259830.9810879854</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24413,21 +24455,21 @@
       </c>
       <c r="C36" s="186">
         <f ca="1">C34/C35</f>
-        <v>13.997096794888947</v>
+        <v>13.930245418047543</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31118,7 +31160,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31189,7 +31231,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32495,7 +32537,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.179104477611936</v>
+        <v>20.171641791044774</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32532,7 +32574,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.9858691202295597</v>
+        <v>4.1921417245060315</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32593,7 +32635,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.4368382454449482</v>
+        <v>3.6146979678745899</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32654,7 +32696,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6740017.75</v>
+        <v>7088820.2250000006</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32715,7 +32757,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5334992.75</v>
+        <v>5683795.2250000006</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32752,7 +32794,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.1001934790668377</v>
+        <v>3.3028845058685845</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32789,7 +32831,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>34.88108867065931</v>
+        <v>37.161618491251936</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32924,7 +32966,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>52.502163566398707</v>
+        <v>55.219201603103386</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32961,7 +33003,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-118.22174640459149</v>
+        <v>-125.95109856626854</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32998,7 +33040,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.9046834112565948E-2</v>
+        <v>1.8109642496964295E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33035,7 +33077,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.2140077821011689E-2</v>
+        <v>4.9574546799852022E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33109,7 +33151,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -33146,7 +33188,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33649,7 +33691,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.20846013350632497</v>
+        <v>0.19820293862791533</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35230,7 +35272,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35246,7 +35288,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6740017.75</v>
+        <v>7088820.2250000006</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35266,7 +35308,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5334992.75</v>
+        <v>5683795.2250000006</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35286,7 +35328,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.179104477611936</v>
+        <v>20.171641791044774</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35306,7 +35348,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.9858691202295597</v>
+        <v>4.1921417245060315</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35326,7 +35368,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.4368382454449482</v>
+        <v>3.6146979678745899</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35346,7 +35388,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.1001934790668377</v>
+        <v>3.3028845058685845</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35355,7 +35397,7 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>34.88108867065931</v>
+        <v>37.161618491251936</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35591,7 +35633,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.2140077821011689E-2</v>
+        <v>4.9574546799852022E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35607,7 +35649,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.9046834112565948E-2</v>
+        <v>1.8109642496964295E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35639,7 +35681,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35648,7 +35690,7 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35692,7 +35734,7 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.20846013350632497</v>
+        <v>0.19820293862791533</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35871,7 +35913,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>12.85</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35900,7 +35942,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>6740017.75</v>
+        <v>7088820.2250000006</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35929,7 +35971,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5334992.75</v>
+        <v>5683795.2250000006</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35958,7 +36000,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>19.179104477611936</v>
+        <v>20.171641791044774</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35987,7 +36029,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>3.9858691202295597</v>
+        <v>4.1921417245060315</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36016,7 +36058,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.4368382454449482</v>
+        <v>3.6146979678745899</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36045,7 +36087,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.1001934790668377</v>
+        <v>3.3028845058685845</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36074,7 +36116,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>34.88108867065931</v>
+        <v>37.161618491251936</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36847,7 +36889,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>5.2140077821011689E-2</v>
+        <v>4.9574546799852022E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36876,7 +36918,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.9046834112565948E-2</v>
+        <v>1.8109642496964295E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36934,7 +36976,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36963,7 +37005,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.9843811984026305E-2</v>
+        <v>3.7883313651108988E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37199,7 +37241,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.20846013350632497</v>
+        <v>0.19820293862791533</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37685,14 +37727,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="262"/>
-      <c r="F3" s="263" t="s">
+      <c r="D3" s="260"/>
+      <c r="F3" s="261" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="262"/>
+      <c r="G3" s="260"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37759,19 +37801,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="259">
+      <c r="C7" s="262">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="260"/>
-      <c r="F7" s="259">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="260"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37798,19 +37840,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="259">
+      <c r="C9" s="262">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="F9" s="259">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="260"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37837,19 +37879,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="259">
+      <c r="C11" s="262">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="F11" s="259">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="260"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37876,19 +37918,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="259">
+      <c r="C13" s="262">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="F13" s="259">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="260"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37915,19 +37957,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="259">
+      <c r="C15" s="262">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="260"/>
-      <c r="F15" s="259">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="260"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37954,19 +37996,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="259">
+      <c r="C17" s="262">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="F17" s="259">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="260"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -37993,22 +38035,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="259">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="F19" s="259">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="260"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -38035,22 +38077,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="259">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="F21" s="259">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="260"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38098,22 +38140,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="259">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="F25" s="259">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="260"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38140,22 +38182,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="259">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="F27" s="259">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="260"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38182,22 +38224,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="259">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="260"/>
-      <c r="F29" s="259">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="260"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38245,22 +38287,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="259">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="F33" s="259">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="260"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38287,43 +38329,25 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="259">
+      <c r="C35" s="262">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="260"/>
-      <c r="F35" s="259">
+      <c r="D35" s="263"/>
+      <c r="F35" s="262">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="260"/>
+      <c r="G35" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38334,6 +38358,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61E221-9121-C84C-B1C4-0E80A1D8C487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98757CC1-2DD0-9C4D-90ED-AD9AFEF02D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2499,6 +2499,9 @@
     <xf numFmtId="0" fontId="26" fillId="8" borderId="27" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2511,6 +2514,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2520,10 +2529,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2535,14 +2544,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2550,12 +2556,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12965,9 +12965,9 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>1.0570999999999999</v>
-    <v>0.39500000000000002</v>
-    <v>3.0106999999999998E-2</v>
+    <v>1.0609999999999999</v>
+    <v>0.23</v>
+    <v>1.6775999999999999E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12975,24 +12975,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>13.61</v>
+    <v>14.1</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46315.725339664059</v>
+    <v>46317.999605404686</v>
     <v>0</v>
-    <v>13.12</v>
-    <v>7043415231</v>
+    <v>13.55</v>
+    <v>7264906276</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.14</v>
-    <v>20.153600000000001</v>
-    <v>13.12</v>
-    <v>13.515000000000001</v>
+    <v>13.71</v>
+    <v>20.7883</v>
+    <v>13.71</v>
+    <v>13.94</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>18791043</v>
-    <v>37474468</v>
+    <v>11796</v>
+    <v>34799606</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -13031,17 +13031,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
     <v>6</v>
-    <v>50.9</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13831,18 +13831,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="E2" s="255" t="s">
+      <c r="C2" s="259"/>
+      <c r="E2" s="258" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="256"/>
-      <c r="H2" s="255" t="s">
+      <c r="F2" s="259"/>
+      <c r="H2" s="258" t="s">
         <v>371</v>
       </c>
-      <c r="I2" s="256"/>
+      <c r="I2" s="259"/>
       <c r="K2" s="153" t="s">
         <v>436</v>
       </c>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>7088820.2250000006</v>
+        <v>7311739.0999999996</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="I3" s="228">
         <f ca="1">'AVG target price'!C5</f>
-        <v>6.144546720051661</v>
+        <v>6.2368901543502862</v>
       </c>
       <c r="K3" s="253" t="s">
         <v>437</v>
@@ -13887,7 +13887,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5683795.2250000006</v>
+        <v>5906714.0999999996</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="I4" s="228">
         <f ca="1">'AVG target price'!C6</f>
-        <v>15.562504631749382</v>
+        <v>15.659826435696912</v>
       </c>
       <c r="K4" s="253" t="s">
         <v>438</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="I5" s="228">
         <f ca="1">'AVG target price'!C7</f>
-        <v>12.794430042483771</v>
+        <v>12.891180252422014</v>
       </c>
       <c r="K5" s="253" t="s">
         <v>439</v>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>20.171641791044774</v>
+        <v>20.805970149253724</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="I6" s="228">
         <f ca="1">'AVG target price'!C8</f>
-        <v>9.9645383877409692</v>
+        <v>10.019528926635143</v>
       </c>
       <c r="K6" s="254" t="s">
         <v>440</v>
@@ -13961,14 +13961,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.39500000000000002</v>
+        <v>0.23</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>4.1921417245060315</v>
+        <v>4.3239700806225727</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="I7" s="228">
         <f ca="1">'AVG target price'!C9</f>
-        <v>11.663753264919423</v>
+        <v>11.731593098041735</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.8109642496964295E-2</v>
+        <v>1.7557519250105628E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="I8" s="229">
         <f ca="1">'AVG target price'!C10</f>
-        <v>11.22595460938904</v>
+        <v>11.307803773429217</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14009,14 +14009,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.0106999999999998E-2</v>
+        <v>1.6775999999999999E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>4.9574546799852022E-2</v>
+        <v>4.8063127690100446E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.16937072812511728</v>
+        <v>-0.18882325872100303</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0570999999999999</v>
+        <v>1.0609999999999999</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14097,10 +14097,10 @@
         <f>Statement!AC125</f>
         <v>0.18573545162533595</v>
       </c>
-      <c r="H13" s="275" t="s">
+      <c r="H13" s="257" t="s">
         <v>433</v>
       </c>
-      <c r="I13" s="273">
+      <c r="I13" s="255">
         <f>'Reverse DCF'!C17</f>
         <v>1.4</v>
       </c>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>37474468</v>
+        <v>34799606</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14123,9 +14123,9 @@
       <c r="H14" s="203" t="s">
         <v>442</v>
       </c>
-      <c r="I14" s="274">
+      <c r="I14" s="256">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>13.930245418047543</v>
+        <v>14.226260599451845</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.19820293862791533</v>
+        <v>0.1921601661087716</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14145,16 +14145,16 @@
         <f>Statement!AC175</f>
         <v>2.6959777878408766</v>
       </c>
-      <c r="H16" s="255" t="s">
+      <c r="H16" s="258" t="s">
         <v>434</v>
       </c>
-      <c r="I16" s="256"/>
+      <c r="I16" s="259"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="260" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="257"/>
+      <c r="C17" s="260"/>
       <c r="E17" s="201" t="s">
         <v>338</v>
       </c>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="I17" s="251">
         <f ca="1">DCF!C15</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="I18" s="252">
         <f ca="1">Multiples!C54</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14240,14 +14240,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="257" t="s">
+      <c r="B25" s="260" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="257"/>
-      <c r="E25" s="255" t="s">
+      <c r="C25" s="260"/>
+      <c r="E25" s="258" t="s">
         <v>391</v>
       </c>
-      <c r="F25" s="256"/>
+      <c r="F25" s="259"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="201" t="s">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14534,36 +14534,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="267"/>
       <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258" t="s">
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
+      <c r="AA2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="261"/>
       <c r="AE2" s="87" t="s">
         <v>137</v>
       </c>
@@ -14574,32 +14574,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="265" t="s">
+      <c r="S4" s="270" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
-      <c r="AA4" s="266"/>
-      <c r="AB4" s="266"/>
-      <c r="AC4" s="266"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
+      <c r="AA4" s="271"/>
+      <c r="AB4" s="271"/>
+      <c r="AC4" s="271"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15095,33 +15095,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="269" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="269"/>
+      <c r="I11" s="269"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="269"/>
+      <c r="L11" s="269"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="265" t="s">
+      <c r="S11" s="270" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="266"/>
-      <c r="U11" s="266"/>
-      <c r="V11" s="266"/>
-      <c r="W11" s="266"/>
-      <c r="X11" s="266"/>
-      <c r="Y11" s="266"/>
-      <c r="Z11" s="266"/>
-      <c r="AA11" s="266"/>
-      <c r="AB11" s="266"/>
-      <c r="AC11" s="266"/>
+      <c r="T11" s="271"/>
+      <c r="U11" s="271"/>
+      <c r="V11" s="271"/>
+      <c r="W11" s="271"/>
+      <c r="X11" s="271"/>
+      <c r="Y11" s="271"/>
+      <c r="Z11" s="271"/>
+      <c r="AA11" s="271"/>
+      <c r="AB11" s="271"/>
+      <c r="AC11" s="271"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15562,33 +15562,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="264" t="s">
+      <c r="C19" s="269" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="264"/>
-      <c r="E19" s="264"/>
-      <c r="F19" s="264"/>
-      <c r="G19" s="264"/>
-      <c r="H19" s="264"/>
-      <c r="I19" s="264"/>
-      <c r="J19" s="264"/>
-      <c r="K19" s="264"/>
-      <c r="L19" s="264"/>
+      <c r="D19" s="269"/>
+      <c r="E19" s="269"/>
+      <c r="F19" s="269"/>
+      <c r="G19" s="269"/>
+      <c r="H19" s="269"/>
+      <c r="I19" s="269"/>
+      <c r="J19" s="269"/>
+      <c r="K19" s="269"/>
+      <c r="L19" s="269"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="265" t="s">
+      <c r="S19" s="270" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="266"/>
-      <c r="U19" s="266"/>
-      <c r="V19" s="266"/>
-      <c r="W19" s="266"/>
-      <c r="X19" s="266"/>
-      <c r="Y19" s="266"/>
-      <c r="Z19" s="266"/>
-      <c r="AA19" s="266"/>
-      <c r="AB19" s="266"/>
-      <c r="AC19" s="266"/>
+      <c r="T19" s="271"/>
+      <c r="U19" s="271"/>
+      <c r="V19" s="271"/>
+      <c r="W19" s="271"/>
+      <c r="X19" s="271"/>
+      <c r="Y19" s="271"/>
+      <c r="Z19" s="271"/>
+      <c r="AA19" s="271"/>
+      <c r="AB19" s="271"/>
+      <c r="AC19" s="271"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16406,32 +16406,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="264" t="s">
+      <c r="C32" s="269" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="264"/>
-      <c r="E32" s="264"/>
-      <c r="F32" s="264"/>
-      <c r="G32" s="264"/>
-      <c r="H32" s="264"/>
-      <c r="I32" s="264"/>
-      <c r="J32" s="264"/>
-      <c r="K32" s="264"/>
-      <c r="L32" s="264"/>
+      <c r="D32" s="269"/>
+      <c r="E32" s="269"/>
+      <c r="F32" s="269"/>
+      <c r="G32" s="269"/>
+      <c r="H32" s="269"/>
+      <c r="I32" s="269"/>
+      <c r="J32" s="269"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="269"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="265" t="s">
+      <c r="S32" s="270" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="266"/>
-      <c r="U32" s="266"/>
-      <c r="V32" s="266"/>
-      <c r="W32" s="266"/>
-      <c r="X32" s="266"/>
-      <c r="Y32" s="266"/>
-      <c r="Z32" s="266"/>
-      <c r="AA32" s="266"/>
-      <c r="AB32" s="266"/>
-      <c r="AC32" s="266"/>
+      <c r="T32" s="271"/>
+      <c r="U32" s="271"/>
+      <c r="V32" s="271"/>
+      <c r="W32" s="271"/>
+      <c r="X32" s="271"/>
+      <c r="Y32" s="271"/>
+      <c r="Z32" s="271"/>
+      <c r="AA32" s="271"/>
+      <c r="AB32" s="271"/>
+      <c r="AC32" s="271"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16688,18 +16688,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16736,35 +16736,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="267"/>
       <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="P2" s="258" t="s">
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="P2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258" t="s">
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261" t="s">
         <v>136</v>
       </c>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
       <c r="AB2" s="87" t="s">
         <v>137</v>
       </c>
@@ -16773,31 +16773,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="P4" s="266" t="s">
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="P4" s="271" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
-      <c r="V4" s="266"/>
-      <c r="W4" s="266"/>
-      <c r="X4" s="266"/>
-      <c r="Y4" s="266"/>
-      <c r="Z4" s="266"/>
+      <c r="Q4" s="271"/>
+      <c r="R4" s="271"/>
+      <c r="S4" s="271"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16992,32 +16992,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="269" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="269"/>
+      <c r="K9" s="269"/>
+      <c r="L9" s="269"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="266" t="s">
+      <c r="P9" s="271" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="266"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
-      <c r="V9" s="266"/>
-      <c r="W9" s="266"/>
-      <c r="X9" s="266"/>
-      <c r="Y9" s="266"/>
-      <c r="Z9" s="266"/>
+      <c r="Q9" s="271"/>
+      <c r="R9" s="271"/>
+      <c r="S9" s="271"/>
+      <c r="T9" s="271"/>
+      <c r="U9" s="271"/>
+      <c r="V9" s="271"/>
+      <c r="W9" s="271"/>
+      <c r="X9" s="271"/>
+      <c r="Y9" s="271"/>
+      <c r="Z9" s="271"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17866,31 +17866,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="264" t="s">
+      <c r="C21" s="269" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="E21" s="264"/>
-      <c r="F21" s="264"/>
-      <c r="G21" s="264"/>
-      <c r="H21" s="264"/>
-      <c r="I21" s="264"/>
-      <c r="J21" s="264"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="P21" s="266" t="s">
+      <c r="D21" s="269"/>
+      <c r="E21" s="269"/>
+      <c r="F21" s="269"/>
+      <c r="G21" s="269"/>
+      <c r="H21" s="269"/>
+      <c r="I21" s="269"/>
+      <c r="J21" s="269"/>
+      <c r="K21" s="269"/>
+      <c r="L21" s="269"/>
+      <c r="P21" s="271" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="266"/>
-      <c r="R21" s="266"/>
-      <c r="S21" s="266"/>
-      <c r="T21" s="266"/>
-      <c r="U21" s="266"/>
-      <c r="V21" s="266"/>
-      <c r="W21" s="266"/>
-      <c r="X21" s="266"/>
-      <c r="Y21" s="266"/>
-      <c r="Z21" s="266"/>
+      <c r="Q21" s="271"/>
+      <c r="R21" s="271"/>
+      <c r="S21" s="271"/>
+      <c r="T21" s="271"/>
+      <c r="U21" s="271"/>
+      <c r="V21" s="271"/>
+      <c r="W21" s="271"/>
+      <c r="X21" s="271"/>
+      <c r="Y21" s="271"/>
+      <c r="Z21" s="271"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18705,60 +18705,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="267"/>
       <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18944,30 +18944,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="269" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="269"/>
+      <c r="I11" s="269"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="269"/>
+      <c r="L11" s="269"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="269"/>
-      <c r="Q11" s="269"/>
-      <c r="R11" s="269"/>
-      <c r="S11" s="269"/>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
+      <c r="P11" s="272"/>
+      <c r="Q11" s="272"/>
+      <c r="R11" s="272"/>
+      <c r="S11" s="272"/>
+      <c r="T11" s="272"/>
+      <c r="U11" s="272"/>
+      <c r="V11" s="272"/>
+      <c r="W11" s="272"/>
+      <c r="X11" s="272"/>
+      <c r="Y11" s="272"/>
+      <c r="Z11" s="272"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19209,18 +19209,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="269" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="269"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="269"/>
+      <c r="G18" s="269"/>
+      <c r="H18" s="269"/>
+      <c r="I18" s="269"/>
+      <c r="J18" s="269"/>
+      <c r="K18" s="269"/>
+      <c r="L18" s="269"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19433,23 +19433,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="269"/>
-      <c r="C25" s="269"/>
+      <c r="B25" s="272"/>
+      <c r="C25" s="272"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="264" t="s">
+      <c r="C26" s="269" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="264"/>
-      <c r="E26" s="264"/>
-      <c r="F26" s="264"/>
-      <c r="G26" s="264"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="264"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
+      <c r="D26" s="269"/>
+      <c r="E26" s="269"/>
+      <c r="F26" s="269"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="269"/>
+      <c r="I26" s="269"/>
+      <c r="J26" s="269"/>
+      <c r="K26" s="269"/>
+      <c r="L26" s="269"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19641,18 +19641,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="264" t="s">
+      <c r="C33" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="264"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="269"/>
+      <c r="G33" s="269"/>
+      <c r="H33" s="269"/>
+      <c r="I33" s="269"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="269"/>
+      <c r="L33" s="269"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19836,18 +19836,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="264" t="s">
+      <c r="C40" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="264"/>
-      <c r="E40" s="264"/>
-      <c r="F40" s="264"/>
-      <c r="G40" s="264"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="264"/>
-      <c r="J40" s="264"/>
-      <c r="K40" s="264"/>
-      <c r="L40" s="264"/>
+      <c r="D40" s="269"/>
+      <c r="E40" s="269"/>
+      <c r="F40" s="269"/>
+      <c r="G40" s="269"/>
+      <c r="H40" s="269"/>
+      <c r="I40" s="269"/>
+      <c r="J40" s="269"/>
+      <c r="K40" s="269"/>
+      <c r="L40" s="269"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20111,6 +20111,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20118,12 +20124,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20161,60 +20161,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="267"/>
       <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="S2" s="269"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="269"/>
-      <c r="AA2" s="269"/>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="269"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="S2" s="272"/>
+      <c r="T2" s="272"/>
+      <c r="U2" s="272"/>
+      <c r="V2" s="272"/>
+      <c r="W2" s="272"/>
+      <c r="X2" s="272"/>
+      <c r="Y2" s="272"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="272"/>
+      <c r="AB2" s="272"/>
+      <c r="AC2" s="272"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="269" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="S4" s="272"/>
+      <c r="T4" s="272"/>
+      <c r="U4" s="272"/>
+      <c r="V4" s="272"/>
+      <c r="W4" s="272"/>
+      <c r="X4" s="272"/>
+      <c r="Y4" s="272"/>
+      <c r="Z4" s="272"/>
+      <c r="AA4" s="272"/>
+      <c r="AB4" s="272"/>
+      <c r="AC4" s="272"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20577,18 +20577,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="264" t="s">
+      <c r="C13" s="269" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="264"/>
-      <c r="E13" s="264"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="264"/>
-      <c r="J13" s="264"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
+      <c r="D13" s="269"/>
+      <c r="E13" s="269"/>
+      <c r="F13" s="269"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="269"/>
+      <c r="I13" s="269"/>
+      <c r="J13" s="269"/>
+      <c r="K13" s="269"/>
+      <c r="L13" s="269"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20681,18 +20681,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="264" t="s">
+      <c r="C18" s="269" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
+      <c r="D18" s="269"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="269"/>
+      <c r="G18" s="269"/>
+      <c r="H18" s="269"/>
+      <c r="I18" s="269"/>
+      <c r="J18" s="269"/>
+      <c r="K18" s="269"/>
+      <c r="L18" s="269"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20884,18 +20884,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="264" t="s">
+      <c r="C25" s="269" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="264"/>
-      <c r="E25" s="264"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="264"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="264"/>
-      <c r="J25" s="264"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
+      <c r="D25" s="269"/>
+      <c r="E25" s="269"/>
+      <c r="F25" s="269"/>
+      <c r="G25" s="269"/>
+      <c r="H25" s="269"/>
+      <c r="I25" s="269"/>
+      <c r="J25" s="269"/>
+      <c r="K25" s="269"/>
+      <c r="L25" s="269"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21033,18 +21033,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="264" t="s">
+      <c r="C31" s="269" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="264"/>
-      <c r="E31" s="264"/>
-      <c r="F31" s="264"/>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="269"/>
+      <c r="L31" s="269"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21183,16 +21183,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="261"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21314,7 +21314,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21323,7 +21323,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>7088820.2250000006</v>
+        <v>7311739.0999999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>1.0570999999999999</v>
+        <v>1.0609999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21382,10 +21382,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="261" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="258"/>
+      <c r="C15" s="261"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21474,60 +21474,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="267"/>
       <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2581209.5717811957</v>
+        <v>2636474.6799858157</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -21734,23 +21734,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-20556.057419441247</v>
+        <v>-20587.052381506786</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-16580.59204982904</v>
+        <v>-16630.631048867843</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>47948.870908069846</v>
+        <v>48166.093805737451</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>71892.760409691662</v>
+        <v>72327.349254848305</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>124627.32901991546</v>
+        <v>125569.74851079404</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -21769,14 +21769,14 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1610549.6119994903</v>
+        <v>1657471.9311680354</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="258" t="s">
+      <c r="B13" s="261" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="258"/>
+      <c r="C13" s="261"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21792,14 +21792,14 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="261" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="258"/>
+      <c r="C18" s="261"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>207332.31086840667</v>
+        <v>208845.50814100518</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1610549.6119994903</v>
+        <v>1657471.9311680354</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21825,7 +21825,7 @@
       </c>
       <c r="C21" s="96">
         <f ca="1">C19+C20</f>
-        <v>1817881.922867897</v>
+        <v>1866317.4393090406</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21852,7 +21852,7 @@
       </c>
       <c r="C24" s="96">
         <f ca="1">C21+C22-C23</f>
-        <v>3222906.922867897</v>
+        <v>3271342.4393090406</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="C26" s="250">
         <f ca="1">C24/C25</f>
-        <v>6.144546720051661</v>
+        <v>6.2368901543502862</v>
       </c>
     </row>
   </sheetData>
@@ -21913,37 +21913,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="267"/>
       <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="269" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22139,23 +22139,23 @@
       <c r="G9" s="159"/>
       <c r="H9" s="94">
         <f ca="1">DCF!H10</f>
-        <v>-20556.057419441247</v>
+        <v>-20587.052381506786</v>
       </c>
       <c r="I9" s="94">
         <f ca="1">DCF!I10</f>
-        <v>-16580.59204982904</v>
+        <v>-16630.631048867843</v>
       </c>
       <c r="J9" s="94">
         <f ca="1">DCF!J10</f>
-        <v>47948.870908069846</v>
+        <v>48166.093805737451</v>
       </c>
       <c r="K9" s="94">
         <f ca="1">DCF!K10</f>
-        <v>71892.760409691662</v>
+        <v>72327.349254848305</v>
       </c>
       <c r="L9" s="94">
         <f ca="1">DCF!L10</f>
-        <v>124627.32901991546</v>
+        <v>125569.74851079404</v>
       </c>
       <c r="N9" s="93"/>
     </row>
@@ -22163,18 +22163,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="269" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="269"/>
+      <c r="I11" s="269"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="269"/>
+      <c r="L11" s="269"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22368,18 +22368,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="264" t="s">
+      <c r="C17" s="269" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="264"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
+      <c r="D17" s="269"/>
+      <c r="E17" s="269"/>
+      <c r="F17" s="269"/>
+      <c r="G17" s="269"/>
+      <c r="H17" s="269"/>
+      <c r="I17" s="269"/>
+      <c r="J17" s="269"/>
+      <c r="K17" s="269"/>
+      <c r="L17" s="269"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22513,18 +22513,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="264" t="s">
+      <c r="C22" s="269" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="264"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="264"/>
-      <c r="G22" s="264"/>
-      <c r="H22" s="264"/>
-      <c r="I22" s="264"/>
-      <c r="J22" s="264"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="264"/>
+      <c r="D22" s="269"/>
+      <c r="E22" s="269"/>
+      <c r="F22" s="269"/>
+      <c r="G22" s="269"/>
+      <c r="H22" s="269"/>
+      <c r="I22" s="269"/>
+      <c r="J22" s="269"/>
+      <c r="K22" s="269"/>
+      <c r="L22" s="269"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22608,18 +22608,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="264" t="s">
+      <c r="C27" s="269" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="264"/>
-      <c r="E27" s="264"/>
-      <c r="F27" s="264"/>
-      <c r="G27" s="264"/>
-      <c r="H27" s="264"/>
-      <c r="I27" s="264"/>
-      <c r="J27" s="264"/>
-      <c r="K27" s="264"/>
-      <c r="L27" s="264"/>
+      <c r="D27" s="269"/>
+      <c r="E27" s="269"/>
+      <c r="F27" s="269"/>
+      <c r="G27" s="269"/>
+      <c r="H27" s="269"/>
+      <c r="I27" s="269"/>
+      <c r="J27" s="269"/>
+      <c r="K27" s="269"/>
+      <c r="L27" s="269"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22920,10 +22920,10 @@
       <c r="N38" s="93"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="258" t="s">
+      <c r="B39" s="261" t="s">
         <v>244</v>
       </c>
-      <c r="C39" s="258"/>
+      <c r="C39" s="261"/>
       <c r="N39" s="93"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="C41" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>6675037.1350735361</v>
+        <v>6725513.1032893555</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="C45" s="127">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>6757742.1169220274</v>
+        <v>6808788.8629195662</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="C48" s="127">
         <f ca="1">C45+C46-C47</f>
-        <v>8162767.1169220274</v>
+        <v>8213813.8629195662</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23021,14 +23021,14 @@
       </c>
       <c r="C50" s="250">
         <f ca="1">C48/C49</f>
-        <v>15.562504631749382</v>
+        <v>15.659826435696912</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="258" t="s">
+      <c r="B52" s="261" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="258"/>
+      <c r="C52" s="261"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -23045,7 +23045,7 @@
       </c>
       <c r="C54" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23080,14 +23080,14 @@
       </c>
       <c r="C58" s="250">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>12.794430042483771</v>
+        <v>12.891180252422014</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="258" t="s">
+      <c r="B60" s="261" t="s">
         <v>368</v>
       </c>
-      <c r="C60" s="258"/>
+      <c r="C60" s="261"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -23104,7 +23104,7 @@
       </c>
       <c r="C62" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>3738819.8705974636</v>
+        <v>3767092.4553238209</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23139,7 +23139,7 @@
       </c>
       <c r="C66" s="127">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>3821524.8524459549</v>
+        <v>3850368.2149540321</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="C69" s="127">
         <f ca="1">C66+C67-C68</f>
-        <v>5226549.8524459545</v>
+        <v>5255393.2149540316</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23184,14 +23184,14 @@
       </c>
       <c r="C71" s="250">
         <f ca="1">C69/C70</f>
-        <v>9.9645383877409692</v>
+        <v>10.019528926635143</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="258" t="s">
+      <c r="B73" s="261" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="258"/>
+      <c r="C73" s="261"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C75" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>4630083.56190072</v>
+        <v>4665095.7941891495</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="C79" s="127">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>4712788.5437492114</v>
+        <v>4748371.5538193602</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="C82" s="127">
         <f ca="1">C79+C80-C81</f>
-        <v>6117813.5437492114</v>
+        <v>6153396.5538193602</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23288,22 +23288,22 @@
       </c>
       <c r="C84" s="250">
         <f ca="1">C82/C83</f>
-        <v>11.663753264919423</v>
+        <v>11.731593098041735</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23341,10 +23341,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="261"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
-        <v>6.144546720051661</v>
+        <v>6.2368901543502862</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Multiples!C50</f>
-        <v>15.562504631749382</v>
+        <v>15.659826435696912</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="C7" s="154">
         <f ca="1">Multiples!C58</f>
-        <v>12.794430042483771</v>
+        <v>12.891180252422014</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C71</f>
-        <v>9.9645383877409692</v>
+        <v>10.019528926635143</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="C9" s="154">
         <f ca="1">Multiples!C84</f>
-        <v>11.663753264919423</v>
+        <v>11.731593098041735</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="C10" s="250">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>11.22595460938904</v>
+        <v>11.307803773429217</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.16937072812511728</v>
+        <v>-0.18882325872100303</v>
       </c>
     </row>
   </sheetData>
@@ -23511,37 +23511,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="267"/>
       <c r="H2" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="264" t="s">
+      <c r="C4" s="269" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="264"/>
-      <c r="J4" s="264"/>
-      <c r="K4" s="264"/>
-      <c r="L4" s="264"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23654,18 +23654,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="264" t="s">
+      <c r="C9" s="269" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="269"/>
+      <c r="K9" s="269"/>
+      <c r="L9" s="269"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23786,18 +23786,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="264" t="s">
+      <c r="C14" s="269" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="264"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="264"/>
-      <c r="G14" s="264"/>
-      <c r="H14" s="264"/>
-      <c r="I14" s="264"/>
-      <c r="J14" s="264"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="269"/>
+      <c r="I14" s="269"/>
+      <c r="J14" s="269"/>
+      <c r="K14" s="269"/>
+      <c r="L14" s="269"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23887,10 +23887,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="258" t="s">
+      <c r="B20" s="261" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="258"/>
+      <c r="C20" s="261"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="C24" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23991,60 +23991,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="267"/>
       <c r="H3" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
-      <c r="S3" s="269"/>
-      <c r="T3" s="269"/>
-      <c r="U3" s="269"/>
-      <c r="V3" s="269"/>
-      <c r="W3" s="269"/>
-      <c r="X3" s="269"/>
-      <c r="Y3" s="269"/>
-      <c r="Z3" s="269"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="272"/>
+      <c r="S3" s="272"/>
+      <c r="T3" s="272"/>
+      <c r="U3" s="272"/>
+      <c r="V3" s="272"/>
+      <c r="W3" s="272"/>
+      <c r="X3" s="272"/>
+      <c r="Y3" s="272"/>
+      <c r="Z3" s="272"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="264" t="s">
+      <c r="C5" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="P5" s="269"/>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
-      <c r="S5" s="269"/>
-      <c r="T5" s="269"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="269"/>
-      <c r="W5" s="269"/>
-      <c r="X5" s="269"/>
-      <c r="Y5" s="269"/>
-      <c r="Z5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="272"/>
+      <c r="Q5" s="272"/>
+      <c r="R5" s="272"/>
+      <c r="S5" s="272"/>
+      <c r="T5" s="272"/>
+      <c r="U5" s="272"/>
+      <c r="V5" s="272"/>
+      <c r="W5" s="272"/>
+      <c r="X5" s="272"/>
+      <c r="Y5" s="272"/>
+      <c r="Z5" s="272"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24178,7 +24178,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>8232031.3494954351</v>
+        <v>8408283.6415399536</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -24232,23 +24232,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>17471.548447830362</v>
+        <v>17497.892506436398</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>38156.875645610453</v>
+        <v>38272.030270850388</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>83332.462682515179</v>
+        <v>83709.983960302503</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>181993.39487932247</v>
+        <v>183093.53763161102</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>397463.30197740055</v>
+        <v>400468.88001263718</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -24267,15 +24267,15 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>5136388.3974553067</v>
+        <v>5286033.7445860878</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="270" t="s">
+      <c r="B14" s="274" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="271"/>
+      <c r="C14" s="275"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="C16" s="175">
         <f ca="1">C36</f>
-        <v>13.930245418047543</v>
+        <v>14.226260599451845</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24302,20 +24302,20 @@
       <c r="C17" s="177">
         <v>1.4</v>
       </c>
-      <c r="E17" s="272" t="s">
+      <c r="E17" s="273" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="272"/>
-      <c r="G17" s="272"/>
-      <c r="H17" s="272"/>
-      <c r="I17" s="272"/>
+      <c r="F17" s="273"/>
+      <c r="G17" s="273"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="273"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="274" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="271"/>
+      <c r="C19" s="275"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="C21" s="239">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.8929500000000004E-2</v>
+        <v>9.7275E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>7043423.3399999999</v>
+        <v>7264914.6399999997</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24376,15 +24376,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5638398.3399999999</v>
+        <v>5859889.6399999997</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="270" t="s">
+      <c r="B28" s="274" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="271"/>
+      <c r="C28" s="275"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="C29" s="180">
         <f ca="1">SUM(H10:L10)</f>
-        <v>718417.58363267896</v>
+        <v>723042.32438183739</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="C30" s="180">
         <f ca="1">L11</f>
-        <v>5136388.3974553067</v>
+        <v>5286033.7445860878</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="C31" s="183">
         <f ca="1">C29+C30</f>
-        <v>5854805.9810879854</v>
+        <v>6009076.0689679254</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="C34" s="183">
         <f ca="1">C31+C32-C33</f>
-        <v>7259830.9810879854</v>
+        <v>7414101.0689679254</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24455,21 +24455,21 @@
       </c>
       <c r="C36" s="186">
         <f ca="1">C34/C35</f>
-        <v>13.930245418047543</v>
+        <v>14.226260599451845</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32537,7 +32537,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>20.171641791044774</v>
+        <v>20.805970149253724</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32574,7 +32574,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1921417245060315</v>
+        <v>4.3239700806225727</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.6146979678745899</v>
+        <v>3.7283677152920296</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7088820.2250000006</v>
+        <v>7311739.0999999996</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5683795.2250000006</v>
+        <v>5906714.0999999996</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32794,7 +32794,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.3028845058685845</v>
+        <v>3.4324238838997752</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32831,7 +32831,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>37.161618491251936</v>
+        <v>38.619099955540442</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32966,7 +32966,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>55.219201603103386</v>
+        <v>56.955654483704116</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33003,7 +33003,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-125.95109856626854</v>
+        <v>-130.89091009816738</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33040,7 +33040,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.8109642496964295E-2</v>
+        <v>1.7557519250105628E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33077,7 +33077,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.9574546799852022E-2</v>
+        <v>4.8063127690100446E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33151,7 +33151,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -33188,7 +33188,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33691,7 +33691,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.19820293862791533</v>
+        <v>0.1921601661087716</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35256,15 +35256,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="258"/>
-      <c r="E4" s="258" t="s">
+      <c r="C4" s="261"/>
+      <c r="E4" s="261" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35272,7 +35272,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7088820.2250000006</v>
+        <v>7311739.0999999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35308,7 +35308,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5683795.2250000006</v>
+        <v>5906714.0999999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35328,7 +35328,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.171641791044774</v>
+        <v>20.805970149253724</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35348,7 +35348,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1921417245060315</v>
+        <v>4.3239700806225727</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.6146979678745899</v>
+        <v>3.7283677152920296</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.3028845058685845</v>
+        <v>3.4324238838997752</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35397,18 +35397,18 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>37.161618491251936</v>
+        <v>38.619099955540442</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="261" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="258"/>
-      <c r="E15" s="258" t="s">
+      <c r="C15" s="261"/>
+      <c r="E15" s="261" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="258"/>
+      <c r="F15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35459,14 +35459,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="258" t="s">
+      <c r="B21" s="261" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="258"/>
-      <c r="E21" s="258" t="s">
+      <c r="C21" s="261"/>
+      <c r="E21" s="261" t="s">
         <v>291</v>
       </c>
-      <c r="F21" s="258"/>
+      <c r="F21" s="261"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35535,14 +35535,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="258" t="s">
+      <c r="B29" s="261" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="258"/>
-      <c r="E29" s="258" t="s">
+      <c r="C29" s="261"/>
+      <c r="E29" s="261" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="258"/>
+      <c r="F29" s="261"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35618,14 +35618,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="261" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="258"/>
-      <c r="E37" s="258" t="s">
+      <c r="C37" s="261"/>
+      <c r="E37" s="261" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="258"/>
+      <c r="F37" s="261"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35633,7 +35633,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.9574546799852022E-2</v>
+        <v>4.8063127690100446E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35649,7 +35649,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.8109642496964295E-2</v>
+        <v>1.7557519250105628E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35690,18 +35690,18 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="261" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="258"/>
-      <c r="E45" s="258" t="s">
+      <c r="C45" s="261"/>
+      <c r="E45" s="261" t="s">
         <v>327</v>
       </c>
-      <c r="F45" s="258"/>
+      <c r="F45" s="261"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35734,18 +35734,18 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.19820293862791533</v>
+        <v>0.1921601661087716</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="261" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="258"/>
-      <c r="E51" s="258" t="s">
+      <c r="C51" s="261"/>
+      <c r="E51" s="261" t="s">
         <v>345</v>
       </c>
-      <c r="F51" s="258"/>
+      <c r="F51" s="261"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>13.515000000000001</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35942,7 +35942,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7088820.2250000006</v>
+        <v>7311739.0999999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35971,7 +35971,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5683795.2250000006</v>
+        <v>5906714.0999999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36000,7 +36000,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.171641791044774</v>
+        <v>20.805970149253724</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36029,7 +36029,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.1921417245060315</v>
+        <v>4.3239700806225727</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36058,7 +36058,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.6146979678745899</v>
+        <v>3.7283677152920296</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36087,7 +36087,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.3028845058685845</v>
+        <v>3.4324238838997752</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>37.161618491251936</v>
+        <v>38.619099955540442</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36889,7 +36889,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.9574546799852022E-2</v>
+        <v>4.8063127690100446E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.8109642496964295E-2</v>
+        <v>1.7557519250105628E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36976,7 +36976,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37005,7 +37005,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.7883313651108988E-2</v>
+        <v>3.6728334576380056E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.19820293862791533</v>
+        <v>0.1921601661087716</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37727,14 +37727,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="264" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="260"/>
-      <c r="F3" s="261" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="260"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38348,6 +38348,24 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38358,24 +38376,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98757CC1-2DD0-9C4D-90ED-AD9AFEF02D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184BAD75-C354-314F-A346-66FE2E4EDC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,28 +158,19 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="447">
   <si>
     <t>Ticker</t>
   </si>
@@ -1529,6 +1499,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2514,12 +2496,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2529,10 +2505,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2544,17 +2520,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12946,7 +12928,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12965,9 +12947,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>1.0609999999999999</v>
-    <v>0.23</v>
-    <v>1.6775999999999999E-2</v>
+    <v>1.0515000000000001</v>
+    <v>-0.23</v>
+    <v>-1.6084000000000001E-2</v>
+    <v>-4.8599999999999997E-2</v>
+    <v>-3.457E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12975,49 +12959,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>14.1</v>
+    <v>14.28</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46317.999605404686</v>
+    <v>46322.893121596877</v>
     <v>0</v>
-    <v>13.55</v>
-    <v>7264906276</v>
+    <v>13.87</v>
+    <v>7332656478</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>13.71</v>
-    <v>20.7883</v>
-    <v>13.71</v>
-    <v>13.94</v>
+    <v>14.19</v>
+    <v>20.981200000000001</v>
+    <v>14.3</v>
+    <v>14.07</v>
+    <v>14.0114</v>
     <v>521155400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>11796</v>
-    <v>34799606</v>
+    <v>20080659</v>
+    <v>32838704</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -13031,28 +13001,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
-    <v>6</v>
-    <v>49.39</v>
+    <v>3</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
-    <v>49.53</v>
+    <v>50.03</v>
+    <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13074,6 +13044,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13094,6 +13066,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13103,11 +13076,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13143,7 +13111,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13154,13 +13122,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13254,13 +13225,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13332,6 +13309,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13339,6 +13319,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13860,7 +13843,7 @@
       </c>
       <c r="F3" s="204">
         <f ca="1">Statement!AC153</f>
-        <v>7311739.0999999996</v>
+        <v>7379926.0499999998</v>
       </c>
       <c r="H3" s="202" t="str">
         <f>'AVG target price'!B5</f>
@@ -13868,7 +13851,7 @@
       </c>
       <c r="I3" s="228">
         <f ca="1">'AVG target price'!C5</f>
-        <v>6.2368901543502862</v>
+        <v>6.2424591183665044</v>
       </c>
       <c r="K3" s="253" t="s">
         <v>437</v>
@@ -13887,7 +13870,7 @@
       </c>
       <c r="F4" s="205">
         <f ca="1">Statement!AC154</f>
-        <v>5906714.0999999996</v>
+        <v>5974901.0499999998</v>
       </c>
       <c r="H4" s="202" t="str">
         <f>'AVG target price'!B6</f>
@@ -13895,7 +13878,7 @@
       </c>
       <c r="I4" s="228">
         <f ca="1">'AVG target price'!C6</f>
-        <v>15.659826435696912</v>
+        <v>15.665589079771257</v>
       </c>
       <c r="K4" s="253" t="s">
         <v>438</v>
@@ -13907,7 +13890,7 @@
       </c>
       <c r="C5" s="225" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
       <c r="E5" s="202" t="s">
         <v>285</v>
@@ -13922,7 +13905,7 @@
       </c>
       <c r="I5" s="228">
         <f ca="1">'AVG target price'!C7</f>
-        <v>12.891180252422014</v>
+        <v>12.896909104316912</v>
       </c>
       <c r="K5" s="253" t="s">
         <v>439</v>
@@ -13932,16 +13915,16 @@
       <c r="B6" s="202" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="225" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="225" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>14.0114</v>
       </c>
       <c r="E6" s="202" t="s">
         <v>279</v>
       </c>
       <c r="F6" s="207">
         <f ca="1">Statement!AC150</f>
-        <v>20.805970149253724</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="H6" s="202" t="str">
         <f>'AVG target price'!B8</f>
@@ -13949,7 +13932,7 @@
       </c>
       <c r="I6" s="228">
         <f ca="1">'AVG target price'!C8</f>
-        <v>10.019528926635143</v>
+        <v>10.02278501751266</v>
       </c>
       <c r="K6" s="254" t="s">
         <v>440</v>
@@ -13961,14 +13944,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" s="203" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="208">
         <f ca="1">Statement!AC151</f>
-        <v>4.3239700806225727</v>
+        <v>4.3642940483758688</v>
       </c>
       <c r="H7" s="202" t="str">
         <f>'AVG target price'!B9</f>
@@ -13976,23 +13959,23 @@
       </c>
       <c r="I7" s="228">
         <f ca="1">'AVG target price'!C9</f>
-        <v>11.731593098041735</v>
+        <v>11.735610031749815</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-4.8599999999999997E-2</v>
       </c>
       <c r="E8" s="202" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="209">
         <f ca="1">Statement!AC161</f>
-        <v>1.7557519250105628E-2</v>
+        <v>1.7395296257745021E-2</v>
       </c>
       <c r="H8" s="201" t="str">
         <f>'AVG target price'!B10</f>
@@ -14000,7 +13983,7 @@
       </c>
       <c r="I8" s="229">
         <f ca="1">'AVG target price'!C10</f>
-        <v>11.307803773429217</v>
+        <v>11.312670470343431</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -14009,14 +13992,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.6775999999999999E-2</v>
+        <v>-1.6084000000000001E-2</v>
       </c>
       <c r="E9" s="202" t="s">
         <v>330</v>
       </c>
       <c r="F9" s="209">
         <f ca="1">Statement!AC162</f>
-        <v>4.8063127690100446E-2</v>
+        <v>4.761904761904763E-2</v>
       </c>
       <c r="H9" s="201" t="str">
         <f>'AVG target price'!B12</f>
@@ -14024,23 +14007,23 @@
       </c>
       <c r="I9" s="230">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.18882325872100303</v>
+        <v>-0.19597224802107815</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-3.457E-3</v>
       </c>
       <c r="E10" s="202" t="s">
         <v>335</v>
       </c>
       <c r="F10" s="209">
         <f ca="1">Statement!AC164</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14088,7 +14071,7 @@
       </c>
       <c r="C13" s="226" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0609999999999999</v>
+        <v>1.0515000000000001</v>
       </c>
       <c r="E13" s="202" t="s">
         <v>121</v>
@@ -14111,7 +14094,7 @@
       </c>
       <c r="C14" s="227" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>34799606</v>
+        <v>32838704</v>
       </c>
       <c r="E14" s="203" t="s">
         <v>122</v>
@@ -14125,7 +14108,7 @@
       </c>
       <c r="I14" s="256">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>14.226260599451845</v>
+        <v>14.244112799800034</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14134,7 +14117,7 @@
       </c>
       <c r="F15" s="209">
         <f ca="1">Statement!AC176</f>
-        <v>0.1921601661087716</v>
+        <v>0.19038469904451144</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14167,7 +14150,7 @@
       </c>
       <c r="I17" s="251">
         <f ca="1">DCF!C15</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14189,7 +14172,7 @@
       </c>
       <c r="I18" s="252">
         <f ca="1">Multiples!C54</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14256,12 +14239,12 @@
       <c r="C26" s="187">
         <v>0.21</v>
       </c>
-      <c r="E26" s="202" t="e" vm="5">
+      <c r="E26" s="202" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="236" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14276,7 +14259,7 @@
       </c>
       <c r="F27" s="237">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14540,8 +14523,8 @@
       <c r="D2" s="261"/>
       <c r="E2" s="261"/>
       <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="261"/>
@@ -14574,32 +14557,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="267" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="270" t="s">
+      <c r="S4" s="268" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
-      <c r="AA4" s="271"/>
-      <c r="AB4" s="271"/>
-      <c r="AC4" s="271"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15095,33 +15078,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="269" t="s">
+      <c r="C11" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="269"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="269"/>
-      <c r="L11" s="269"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="270" t="s">
+      <c r="S11" s="268" t="s">
         <v>144</v>
       </c>
-      <c r="T11" s="271"/>
-      <c r="U11" s="271"/>
-      <c r="V11" s="271"/>
-      <c r="W11" s="271"/>
-      <c r="X11" s="271"/>
-      <c r="Y11" s="271"/>
-      <c r="Z11" s="271"/>
-      <c r="AA11" s="271"/>
-      <c r="AB11" s="271"/>
-      <c r="AC11" s="271"/>
+      <c r="T11" s="269"/>
+      <c r="U11" s="269"/>
+      <c r="V11" s="269"/>
+      <c r="W11" s="269"/>
+      <c r="X11" s="269"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="269"/>
+      <c r="AA11" s="269"/>
+      <c r="AB11" s="269"/>
+      <c r="AC11" s="269"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15562,33 +15545,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="269" t="s">
+      <c r="C19" s="267" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="269"/>
-      <c r="E19" s="269"/>
-      <c r="F19" s="269"/>
-      <c r="G19" s="269"/>
-      <c r="H19" s="269"/>
-      <c r="I19" s="269"/>
-      <c r="J19" s="269"/>
-      <c r="K19" s="269"/>
-      <c r="L19" s="269"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="267"/>
+      <c r="G19" s="267"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="267"/>
+      <c r="J19" s="267"/>
+      <c r="K19" s="267"/>
+      <c r="L19" s="267"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="270" t="s">
+      <c r="S19" s="268" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="271"/>
-      <c r="U19" s="271"/>
-      <c r="V19" s="271"/>
-      <c r="W19" s="271"/>
-      <c r="X19" s="271"/>
-      <c r="Y19" s="271"/>
-      <c r="Z19" s="271"/>
-      <c r="AA19" s="271"/>
-      <c r="AB19" s="271"/>
-      <c r="AC19" s="271"/>
+      <c r="T19" s="269"/>
+      <c r="U19" s="269"/>
+      <c r="V19" s="269"/>
+      <c r="W19" s="269"/>
+      <c r="X19" s="269"/>
+      <c r="Y19" s="269"/>
+      <c r="Z19" s="269"/>
+      <c r="AA19" s="269"/>
+      <c r="AB19" s="269"/>
+      <c r="AC19" s="269"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16406,32 +16389,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="269" t="s">
+      <c r="C32" s="267" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="269"/>
-      <c r="E32" s="269"/>
-      <c r="F32" s="269"/>
-      <c r="G32" s="269"/>
-      <c r="H32" s="269"/>
-      <c r="I32" s="269"/>
-      <c r="J32" s="269"/>
-      <c r="K32" s="269"/>
-      <c r="L32" s="269"/>
+      <c r="D32" s="267"/>
+      <c r="E32" s="267"/>
+      <c r="F32" s="267"/>
+      <c r="G32" s="267"/>
+      <c r="H32" s="267"/>
+      <c r="I32" s="267"/>
+      <c r="J32" s="267"/>
+      <c r="K32" s="267"/>
+      <c r="L32" s="267"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="270" t="s">
+      <c r="S32" s="268" t="s">
         <v>148</v>
       </c>
-      <c r="T32" s="271"/>
-      <c r="U32" s="271"/>
-      <c r="V32" s="271"/>
-      <c r="W32" s="271"/>
-      <c r="X32" s="271"/>
-      <c r="Y32" s="271"/>
-      <c r="Z32" s="271"/>
-      <c r="AA32" s="271"/>
-      <c r="AB32" s="271"/>
-      <c r="AC32" s="271"/>
+      <c r="T32" s="269"/>
+      <c r="U32" s="269"/>
+      <c r="V32" s="269"/>
+      <c r="W32" s="269"/>
+      <c r="X32" s="269"/>
+      <c r="Y32" s="269"/>
+      <c r="Z32" s="269"/>
+      <c r="AA32" s="269"/>
+      <c r="AB32" s="269"/>
+      <c r="AC32" s="269"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16688,18 +16671,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16742,8 +16725,8 @@
       <c r="D2" s="261"/>
       <c r="E2" s="261"/>
       <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="261"/>
@@ -16773,31 +16756,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="267" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
-      <c r="P4" s="271" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>138</v>
       </c>
-      <c r="Q4" s="271"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16992,32 +16975,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="269" t="s">
+      <c r="C9" s="267" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="269"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="269"/>
-      <c r="G9" s="269"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="269"/>
-      <c r="K9" s="269"/>
-      <c r="L9" s="269"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="271" t="s">
+      <c r="P9" s="269" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="271"/>
-      <c r="R9" s="271"/>
-      <c r="S9" s="271"/>
-      <c r="T9" s="271"/>
-      <c r="U9" s="271"/>
-      <c r="V9" s="271"/>
-      <c r="W9" s="271"/>
-      <c r="X9" s="271"/>
-      <c r="Y9" s="271"/>
-      <c r="Z9" s="271"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17866,31 +17849,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="269" t="s">
+      <c r="C21" s="267" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="269"/>
-      <c r="E21" s="269"/>
-      <c r="F21" s="269"/>
-      <c r="G21" s="269"/>
-      <c r="H21" s="269"/>
-      <c r="I21" s="269"/>
-      <c r="J21" s="269"/>
-      <c r="K21" s="269"/>
-      <c r="L21" s="269"/>
-      <c r="P21" s="271" t="s">
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="267"/>
+      <c r="J21" s="267"/>
+      <c r="K21" s="267"/>
+      <c r="L21" s="267"/>
+      <c r="P21" s="269" t="s">
         <v>167</v>
       </c>
-      <c r="Q21" s="271"/>
-      <c r="R21" s="271"/>
-      <c r="S21" s="271"/>
-      <c r="T21" s="271"/>
-      <c r="U21" s="271"/>
-      <c r="V21" s="271"/>
-      <c r="W21" s="271"/>
-      <c r="X21" s="271"/>
-      <c r="Y21" s="271"/>
-      <c r="Z21" s="271"/>
+      <c r="Q21" s="269"/>
+      <c r="R21" s="269"/>
+      <c r="S21" s="269"/>
+      <c r="T21" s="269"/>
+      <c r="U21" s="269"/>
+      <c r="V21" s="269"/>
+      <c r="W21" s="269"/>
+      <c r="X21" s="269"/>
+      <c r="Y21" s="269"/>
+      <c r="Z21" s="269"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18711,8 +18694,8 @@
       <c r="D3" s="261"/>
       <c r="E3" s="261"/>
       <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="261"/>
@@ -18736,18 +18719,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="267" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -18944,18 +18927,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="269" t="s">
+      <c r="C11" s="267" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="269"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="269"/>
-      <c r="L11" s="269"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="93"/>
       <c r="P11" s="272"/>
       <c r="Q11" s="272"/>
@@ -19209,18 +19192,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="269" t="s">
+      <c r="C18" s="267" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
-      <c r="F18" s="269"/>
-      <c r="G18" s="269"/>
-      <c r="H18" s="269"/>
-      <c r="I18" s="269"/>
-      <c r="J18" s="269"/>
-      <c r="K18" s="269"/>
-      <c r="L18" s="269"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19438,18 +19421,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="269" t="s">
+      <c r="C26" s="267" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="269"/>
-      <c r="E26" s="269"/>
-      <c r="F26" s="269"/>
-      <c r="G26" s="269"/>
-      <c r="H26" s="269"/>
-      <c r="I26" s="269"/>
-      <c r="J26" s="269"/>
-      <c r="K26" s="269"/>
-      <c r="L26" s="269"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19641,18 +19624,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="269" t="s">
+      <c r="C33" s="267" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="269"/>
-      <c r="E33" s="269"/>
-      <c r="F33" s="269"/>
-      <c r="G33" s="269"/>
-      <c r="H33" s="269"/>
-      <c r="I33" s="269"/>
-      <c r="J33" s="269"/>
-      <c r="K33" s="269"/>
-      <c r="L33" s="269"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19836,18 +19819,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="269" t="s">
+      <c r="C40" s="267" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="269"/>
-      <c r="E40" s="269"/>
-      <c r="F40" s="269"/>
-      <c r="G40" s="269"/>
-      <c r="H40" s="269"/>
-      <c r="I40" s="269"/>
-      <c r="J40" s="269"/>
-      <c r="K40" s="269"/>
-      <c r="L40" s="269"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20111,12 +20094,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20124,6 +20101,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20167,8 +20150,8 @@
       <c r="D2" s="261"/>
       <c r="E2" s="261"/>
       <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="261"/>
@@ -20192,18 +20175,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="S4" s="272"/>
       <c r="T4" s="272"/>
       <c r="U4" s="272"/>
@@ -20577,18 +20560,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="269" t="s">
+      <c r="C13" s="267" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="269"/>
-      <c r="E13" s="269"/>
-      <c r="F13" s="269"/>
-      <c r="G13" s="269"/>
-      <c r="H13" s="269"/>
-      <c r="I13" s="269"/>
-      <c r="J13" s="269"/>
-      <c r="K13" s="269"/>
-      <c r="L13" s="269"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20681,18 +20664,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="269" t="s">
+      <c r="C18" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
-      <c r="F18" s="269"/>
-      <c r="G18" s="269"/>
-      <c r="H18" s="269"/>
-      <c r="I18" s="269"/>
-      <c r="J18" s="269"/>
-      <c r="K18" s="269"/>
-      <c r="L18" s="269"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20884,18 +20867,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="269" t="s">
+      <c r="C25" s="267" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="269"/>
-      <c r="E25" s="269"/>
-      <c r="F25" s="269"/>
-      <c r="G25" s="269"/>
-      <c r="H25" s="269"/>
-      <c r="I25" s="269"/>
-      <c r="J25" s="269"/>
-      <c r="K25" s="269"/>
-      <c r="L25" s="269"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21033,18 +21016,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="269" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="269"/>
-      <c r="E31" s="269"/>
-      <c r="F31" s="269"/>
-      <c r="G31" s="269"/>
-      <c r="H31" s="269"/>
-      <c r="I31" s="269"/>
-      <c r="J31" s="269"/>
-      <c r="K31" s="269"/>
-      <c r="L31" s="269"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21183,16 +21166,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21314,7 +21297,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21323,7 +21306,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>7311739.0999999996</v>
+        <v>7379926.0499999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21341,7 +21324,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21350,7 +21333,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>1.0609999999999999</v>
+        <v>1.0515000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21420,7 +21403,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21429,7 +21412,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21480,8 +21463,8 @@
       <c r="D3" s="261"/>
       <c r="E3" s="261"/>
       <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="261"/>
@@ -21505,18 +21488,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="267" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -21680,7 +21663,7 @@
       </c>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2636474.6799858157</v>
+        <v>2639805.39530179</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -21734,23 +21717,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-20587.052381506786</v>
+        <v>-20588.881837184832</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-16630.631048867843</v>
+        <v>-16633.586921684164</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>48166.093805737451</v>
+        <v>48178.935697271365</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>72327.349254848305</v>
+        <v>72353.061982658881</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>125569.74851079404</v>
+        <v>125625.55181798639</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -21769,7 +21752,7 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1657471.9311680354</v>
+        <v>1660303.3637309594</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -21792,7 +21775,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -21807,7 +21790,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>208845.50814100518</v>
+        <v>208935.08073904764</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21816,7 +21799,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1657471.9311680354</v>
+        <v>1660303.3637309594</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21825,7 +21808,7 @@
       </c>
       <c r="C21" s="96">
         <f ca="1">C19+C20</f>
-        <v>1866317.4393090406</v>
+        <v>1869238.444470007</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21852,7 +21835,7 @@
       </c>
       <c r="C24" s="96">
         <f ca="1">C21+C22-C23</f>
-        <v>3271342.4393090406</v>
+        <v>3274263.444470007</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21870,7 +21853,7 @@
       </c>
       <c r="C26" s="250">
         <f ca="1">C24/C25</f>
-        <v>6.2368901543502862</v>
+        <v>6.2424591183665044</v>
       </c>
     </row>
   </sheetData>
@@ -21919,8 +21902,8 @@
       <c r="D2" s="261"/>
       <c r="E2" s="261"/>
       <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="261"/>
@@ -21932,18 +21915,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="267" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22139,23 +22122,23 @@
       <c r="G9" s="159"/>
       <c r="H9" s="94">
         <f ca="1">DCF!H10</f>
-        <v>-20587.052381506786</v>
+        <v>-20588.881837184832</v>
       </c>
       <c r="I9" s="94">
         <f ca="1">DCF!I10</f>
-        <v>-16630.631048867843</v>
+        <v>-16633.586921684164</v>
       </c>
       <c r="J9" s="94">
         <f ca="1">DCF!J10</f>
-        <v>48166.093805737451</v>
+        <v>48178.935697271365</v>
       </c>
       <c r="K9" s="94">
         <f ca="1">DCF!K10</f>
-        <v>72327.349254848305</v>
+        <v>72353.061982658881</v>
       </c>
       <c r="L9" s="94">
         <f ca="1">DCF!L10</f>
-        <v>125569.74851079404</v>
+        <v>125625.55181798639</v>
       </c>
       <c r="N9" s="93"/>
     </row>
@@ -22163,18 +22146,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="269" t="s">
+      <c r="C11" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="269"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="269"/>
-      <c r="L11" s="269"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="93"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22368,18 +22351,18 @@
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="269" t="s">
+      <c r="C17" s="267" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="269"/>
-      <c r="E17" s="269"/>
-      <c r="F17" s="269"/>
-      <c r="G17" s="269"/>
-      <c r="H17" s="269"/>
-      <c r="I17" s="269"/>
-      <c r="J17" s="269"/>
-      <c r="K17" s="269"/>
-      <c r="L17" s="269"/>
+      <c r="D17" s="267"/>
+      <c r="E17" s="267"/>
+      <c r="F17" s="267"/>
+      <c r="G17" s="267"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="267"/>
+      <c r="J17" s="267"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="267"/>
       <c r="N17" s="93"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -22513,18 +22496,18 @@
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="269" t="s">
+      <c r="C22" s="267" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="269"/>
-      <c r="E22" s="269"/>
-      <c r="F22" s="269"/>
-      <c r="G22" s="269"/>
-      <c r="H22" s="269"/>
-      <c r="I22" s="269"/>
-      <c r="J22" s="269"/>
-      <c r="K22" s="269"/>
-      <c r="L22" s="269"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="267"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="267"/>
+      <c r="J22" s="267"/>
+      <c r="K22" s="267"/>
+      <c r="L22" s="267"/>
       <c r="N22" s="93"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -22608,18 +22591,18 @@
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="269" t="s">
+      <c r="C27" s="267" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="269"/>
-      <c r="E27" s="269"/>
-      <c r="F27" s="269"/>
-      <c r="G27" s="269"/>
-      <c r="H27" s="269"/>
-      <c r="I27" s="269"/>
-      <c r="J27" s="269"/>
-      <c r="K27" s="269"/>
-      <c r="L27" s="269"/>
+      <c r="D27" s="267"/>
+      <c r="E27" s="267"/>
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="267"/>
+      <c r="K27" s="267"/>
+      <c r="L27" s="267"/>
       <c r="N27" s="93"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -22941,7 +22924,7 @@
       </c>
       <c r="C41" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -22967,7 +22950,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>6725513.1032893555</v>
+        <v>6728501.9272551592</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -22976,7 +22959,7 @@
       </c>
       <c r="C45" s="127">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>6808788.8629195662</v>
+        <v>6811811.4561762204</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23003,7 +22986,7 @@
       </c>
       <c r="C48" s="127">
         <f ca="1">C45+C46-C47</f>
-        <v>8213813.8629195662</v>
+        <v>8216836.4561762204</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -23021,7 +23004,7 @@
       </c>
       <c r="C50" s="250">
         <f ca="1">C48/C49</f>
-        <v>15.659826435696912</v>
+        <v>15.665589079771257</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -23045,7 +23028,7 @@
       </c>
       <c r="C54" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -23080,7 +23063,7 @@
       </c>
       <c r="C58" s="250">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>12.891180252422014</v>
+        <v>12.896909104316912</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23104,7 +23087,7 @@
       </c>
       <c r="C62" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23130,7 +23113,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>3767092.4553238209</v>
+        <v>3768766.5545395915</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23139,7 +23122,7 @@
       </c>
       <c r="C66" s="127">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>3850368.2149540321</v>
+        <v>3852076.0834606527</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -23166,7 +23149,7 @@
       </c>
       <c r="C69" s="127">
         <f ca="1">C66+C67-C68</f>
-        <v>5255393.2149540316</v>
+        <v>5257101.0834606532</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -23184,7 +23167,7 @@
       </c>
       <c r="C71" s="250">
         <f ca="1">C69/C70</f>
-        <v>10.019528926635143</v>
+        <v>10.02278501751266</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -23208,7 +23191,7 @@
       </c>
       <c r="C75" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -23234,7 +23217,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>4665095.7941891495</v>
+        <v>4667168.9668821925</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -23243,7 +23226,7 @@
       </c>
       <c r="C79" s="127">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>4748371.5538193602</v>
+        <v>4750478.4958032537</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -23270,7 +23253,7 @@
       </c>
       <c r="C82" s="127">
         <f ca="1">C79+C80-C81</f>
-        <v>6153396.5538193602</v>
+        <v>6155503.4958032537</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -23288,22 +23271,22 @@
       </c>
       <c r="C84" s="250">
         <f ca="1">C82/C83</f>
-        <v>11.731593098041735</v>
+        <v>11.735610031749815</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23353,7 +23336,7 @@
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
-        <v>6.2368901543502862</v>
+        <v>6.2424591183665044</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23362,7 +23345,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Multiples!C50</f>
-        <v>15.659826435696912</v>
+        <v>15.665589079771257</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23371,7 +23354,7 @@
       </c>
       <c r="C7" s="154">
         <f ca="1">Multiples!C58</f>
-        <v>12.891180252422014</v>
+        <v>12.896909104316912</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -23380,7 +23363,7 @@
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C71</f>
-        <v>10.019528926635143</v>
+        <v>10.02278501751266</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23389,7 +23372,7 @@
       </c>
       <c r="C9" s="154">
         <f ca="1">Multiples!C84</f>
-        <v>11.731593098041735</v>
+        <v>11.735610031749815</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23398,7 +23381,7 @@
       </c>
       <c r="C10" s="250">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>11.307803773429217</v>
+        <v>11.312670470343431</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23407,7 +23390,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">Overview!C5</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,7 +23399,7 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.18882325872100303</v>
+        <v>-0.19597224802107815</v>
       </c>
     </row>
   </sheetData>
@@ -23517,8 +23500,8 @@
       <c r="D2" s="261"/>
       <c r="E2" s="261"/>
       <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="261"/>
@@ -23530,18 +23513,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="267" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23654,18 +23637,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="269" t="s">
+      <c r="C9" s="267" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="269"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="269"/>
-      <c r="G9" s="269"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="269"/>
-      <c r="K9" s="269"/>
-      <c r="L9" s="269"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23786,18 +23769,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="269" t="s">
+      <c r="C14" s="267" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="269"/>
-      <c r="E14" s="269"/>
-      <c r="F14" s="269"/>
-      <c r="G14" s="269"/>
-      <c r="H14" s="269"/>
-      <c r="I14" s="269"/>
-      <c r="J14" s="269"/>
-      <c r="K14" s="269"/>
-      <c r="L14" s="269"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23925,7 +23908,7 @@
       </c>
       <c r="C24" s="156">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -23997,8 +23980,8 @@
       <c r="D3" s="261"/>
       <c r="E3" s="261"/>
       <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="261"/>
@@ -24022,18 +24005,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="267" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -24178,7 +24161,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>8408283.6415399536</v>
+        <v>8418906.0075799283</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -24232,23 +24215,23 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>17497.892506436398</v>
+        <v>17499.447445832604</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>38272.030270850388</v>
+        <v>38278.832613682156</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>83709.983960302503</v>
+        <v>83732.302451369251</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>183093.53763161102</v>
+        <v>183158.62828328708</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>400468.88001263718</v>
+        <v>400646.84873677138</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -24267,15 +24250,15 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>5286033.7445860878</v>
+        <v>5295063.790761644</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="274" t="s">
+      <c r="B14" s="273" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="275"/>
+      <c r="C14" s="274"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="174" t="s">
@@ -24283,7 +24266,7 @@
       </c>
       <c r="C15" s="175">
         <f ca="1">Overview!C5</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24292,7 +24275,7 @@
       </c>
       <c r="C16" s="175">
         <f ca="1">C36</f>
-        <v>14.226260599451845</v>
+        <v>14.244112799800034</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24302,20 +24285,20 @@
       <c r="C17" s="177">
         <v>1.4</v>
       </c>
-      <c r="E17" s="273" t="s">
+      <c r="E17" s="275" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="273"/>
-      <c r="G17" s="273"/>
-      <c r="H17" s="273"/>
-      <c r="I17" s="273"/>
+      <c r="F17" s="275"/>
+      <c r="G17" s="275"/>
+      <c r="H17" s="275"/>
+      <c r="I17" s="275"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="273" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="275"/>
+      <c r="C19" s="274"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="178" t="s">
@@ -24331,7 +24314,7 @@
       </c>
       <c r="C21" s="239">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.7275E-2</v>
+        <v>9.71775E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24349,7 +24332,7 @@
       </c>
       <c r="C23" s="180">
         <f ca="1">C15*C22</f>
-        <v>7264914.6399999997</v>
+        <v>7332664.9199999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24376,15 +24359,15 @@
       </c>
       <c r="C26" s="181">
         <f ca="1">C23+C25-C24</f>
-        <v>5859889.6399999997</v>
+        <v>5927639.9199999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="274" t="s">
+      <c r="B28" s="273" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="275"/>
+      <c r="C28" s="274"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="178" t="s">
@@ -24392,7 +24375,7 @@
       </c>
       <c r="C29" s="180">
         <f ca="1">SUM(H10:L10)</f>
-        <v>723042.32438183739</v>
+        <v>723316.05953094247</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24401,7 +24384,7 @@
       </c>
       <c r="C30" s="180">
         <f ca="1">L11</f>
-        <v>5286033.7445860878</v>
+        <v>5295063.790761644</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24410,7 +24393,7 @@
       </c>
       <c r="C31" s="183">
         <f ca="1">C29+C30</f>
-        <v>6009076.0689679254</v>
+        <v>6018379.8502925867</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24437,7 +24420,7 @@
       </c>
       <c r="C34" s="183">
         <f ca="1">C31+C32-C33</f>
-        <v>7414101.0689679254</v>
+        <v>7423404.8502925867</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -24455,21 +24438,21 @@
       </c>
       <c r="C36" s="186">
         <f ca="1">C34/C35</f>
-        <v>14.226260599451845</v>
+        <v>14.244112799800034</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31160,7 +31143,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31231,7 +31214,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -32537,7 +32520,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>20.805970149253724</v>
+        <v>20.999999999999996</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32574,7 +32557,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.3239700806225727</v>
+        <v>4.3642940483758688</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32635,7 +32618,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.7283677152920296</v>
+        <v>3.7631372850903055</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32696,7 +32679,7 @@
       </c>
       <c r="AC153" s="162">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>7311739.0999999996</v>
+        <v>7379926.0499999998</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32757,7 +32740,7 @@
       </c>
       <c r="AC154" s="162">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>5906714.0999999996</v>
+        <v>5974901.0499999998</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32794,7 +32777,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="200">
         <f ca="1">AC154/AC5</f>
-        <v>3.4324238838997752</v>
+        <v>3.4720476936504929</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32831,7 +32814,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="200">
         <f ca="1">AC154/AC12</f>
-        <v>38.619099955540442</v>
+        <v>39.064917815205163</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32966,7 +32949,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>56.955654483704116</v>
+        <v>57.486804776593758</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -33003,7 +32986,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="161"/>
-        <v>-130.89091009816738</v>
+        <v>-132.40191127263057</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -33040,7 +33023,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>1.7557519250105628E-2</v>
+        <v>1.7395296257745021E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33077,7 +33060,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>4.8063127690100446E-2</v>
+        <v>4.761904761904763E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33151,7 +33134,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="173">
         <f ca="1">-AC63/AC153</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -33188,7 +33171,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="173">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33691,7 +33674,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="173">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.1921601661087716</v>
+        <v>0.19038469904451144</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -35239,7 +35222,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -35272,7 +35255,7 @@
       </c>
       <c r="C5" s="189">
         <f ca="1">Overview!C5</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35288,7 +35271,7 @@
       </c>
       <c r="C6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7311739.0999999996</v>
+        <v>7379926.0499999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35308,7 +35291,7 @@
       </c>
       <c r="C7" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5906714.0999999996</v>
+        <v>5974901.0499999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35328,7 +35311,7 @@
       </c>
       <c r="C8" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.805970149253724</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>285</v>
@@ -35348,7 +35331,7 @@
       </c>
       <c r="C9" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.3239700806225727</v>
+        <v>4.3642940483758688</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>286</v>
@@ -35368,7 +35351,7 @@
       </c>
       <c r="C10" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.7283677152920296</v>
+        <v>3.7631372850903055</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35388,7 +35371,7 @@
       </c>
       <c r="C11" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.4324238838997752</v>
+        <v>3.4720476936504929</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35397,7 +35380,7 @@
       </c>
       <c r="C12" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>38.619099955540442</v>
+        <v>39.064917815205163</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -35633,7 +35616,7 @@
       </c>
       <c r="C38" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.8063127690100446E-2</v>
+        <v>4.761904761904763E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>312</v>
@@ -35649,7 +35632,7 @@
       </c>
       <c r="C39" s="232">
         <f ca="1">Statement!AC161</f>
-        <v>1.7557519250105628E-2</v>
+        <v>1.7395296257745021E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>314</v>
@@ -35681,7 +35664,7 @@
       </c>
       <c r="C41" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35690,7 +35673,7 @@
       </c>
       <c r="C42" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -35734,7 +35717,7 @@
       </c>
       <c r="F48" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>0.1921601661087716</v>
+        <v>0.19038469904451144</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -35788,8 +35771,51 @@
         <v>0.39573076923076922</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="261" t="s">
+        <v>443</v>
+      </c>
+      <c r="C57" s="261"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C58" s="191">
+        <f ca="1">Statement!AC159</f>
+        <v>57.486804776593758</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C59" s="191">
+        <f ca="1">Statement!AC160</f>
+        <v>-132.40191127263057</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="C60" s="192">
+        <f>Statement!AC166</f>
+        <v>-2.6223546626159742E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="C61" s="192">
+        <f>Statement!AC167</f>
+        <v>7.4599996048482789E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -35814,7 +35840,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I94"/>
+  <dimension ref="B1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -35913,7 +35939,7 @@
       </c>
       <c r="I6" s="189">
         <f ca="1">Statement!AC116</f>
-        <v>13.94</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35942,7 +35968,7 @@
       </c>
       <c r="I7" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>7311739.0999999996</v>
+        <v>7379926.0499999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35971,7 +35997,7 @@
       </c>
       <c r="I8" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>5906714.0999999996</v>
+        <v>5974901.0499999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36000,7 +36026,7 @@
       </c>
       <c r="I9" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>20.805970149253724</v>
+        <v>20.999999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36029,7 +36055,7 @@
       </c>
       <c r="I10" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>4.3239700806225727</v>
+        <v>4.3642940483758688</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36058,7 +36084,7 @@
       </c>
       <c r="I11" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>3.7283677152920296</v>
+        <v>3.7631372850903055</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36087,7 +36113,7 @@
       </c>
       <c r="I12" s="191">
         <f ca="1">Statement!AC155</f>
-        <v>3.4324238838997752</v>
+        <v>3.4720476936504929</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36116,7 +36142,7 @@
       </c>
       <c r="I13" s="191">
         <f ca="1">Statement!AC156</f>
-        <v>38.619099955540442</v>
+        <v>39.064917815205163</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36889,7 +36915,7 @@
       </c>
       <c r="I51" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>4.8063127690100446E-2</v>
+        <v>4.761904761904763E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36918,7 +36944,7 @@
       </c>
       <c r="I52" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>1.7557519250105628E-2</v>
+        <v>1.7395296257745021E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36976,7 +37002,7 @@
       </c>
       <c r="I54" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37005,7 +37031,7 @@
       </c>
       <c r="I55" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>3.6728334576380056E-2</v>
+        <v>3.6388982515617486E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37241,7 +37267,7 @@
       </c>
       <c r="I68" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.1921601661087716</v>
+        <v>0.19038469904451144</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37578,98 +37604,136 @@
       </c>
       <c r="I85" s="214"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C88" s="191">
+        <f>Statement!M159</f>
+        <v>-31.117410328396652</v>
+      </c>
+      <c r="D88" s="191">
+        <f>Statement!N159</f>
+        <v>-20.121230787144853</v>
+      </c>
+      <c r="E88" s="191">
+        <f>Statement!O159</f>
+        <v>-169.18232313158387</v>
+      </c>
+      <c r="F88" s="191">
+        <f>Statement!P159</f>
+        <v>-153.13123350282808</v>
+      </c>
+      <c r="G88" s="191">
+        <f>Statement!Q159</f>
+        <v>108.6619548175135</v>
+      </c>
+      <c r="I88" s="191">
+        <f ca="1">Statement!AC159</f>
+        <v>57.486804776593758</v>
+      </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C89" s="192">
-        <f>Statement!M197</f>
-        <v>1</v>
-      </c>
-      <c r="D89" s="192">
-        <f>Statement!N197</f>
-        <v>3.4084087514825716E-2</v>
-      </c>
-      <c r="E89" s="192">
-        <f>Statement!O197</f>
-        <v>0.24818614965570993</v>
-      </c>
-      <c r="F89" s="192">
-        <f>Statement!P197</f>
-        <v>-5.5102093364575021E-2</v>
-      </c>
-      <c r="G89" s="192">
-        <f>Statement!Q197</f>
-        <v>3.2771752459329104E-2</v>
-      </c>
-      <c r="I89" s="214"/>
+        <v>306</v>
+      </c>
+      <c r="C89" s="191">
+        <f>Statement!M160</f>
+        <v>-26.884257614591405</v>
+      </c>
+      <c r="D89" s="191">
+        <f>Statement!N160</f>
+        <v>-12.722058684723095</v>
+      </c>
+      <c r="E89" s="191">
+        <f>Statement!O160</f>
+        <v>-54.027334756669582</v>
+      </c>
+      <c r="F89" s="191">
+        <f>Statement!P160</f>
+        <v>-31.268001801694783</v>
+      </c>
+      <c r="G89" s="191">
+        <f>Statement!Q160</f>
+        <v>-52.805531070816492</v>
+      </c>
+      <c r="I89" s="191">
+        <f ca="1">Statement!AC160</f>
+        <v>-132.40191127263057</v>
+      </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>354</v>
+        <v>444</v>
       </c>
       <c r="C90" s="192">
-        <f>Statement!M198</f>
-        <v>1</v>
+        <f>Statement!M166</f>
+        <v>-0.67690742077350341</v>
       </c>
       <c r="D90" s="192">
-        <f>Statement!N198</f>
-        <v>0.37569180272908909</v>
+        <f>Statement!N166</f>
+        <v>-0.47238898109828159</v>
       </c>
       <c r="E90" s="192">
-        <f>Statement!O198</f>
-        <v>0.27729682030883041</v>
+        <f>Statement!O166</f>
+        <v>-0.16542896721281397</v>
       </c>
       <c r="F90" s="192">
-        <f>Statement!P198</f>
-        <v>0.23392027917368038</v>
+        <f>Statement!P166</f>
+        <v>-0.14131432280591805</v>
       </c>
       <c r="G90" s="192">
-        <f>Statement!Q198</f>
-        <v>0.19019336689332336</v>
-      </c>
-      <c r="I90" s="214"/>
+        <f>Statement!Q166</f>
+        <v>-5.8690949550842808E-2</v>
+      </c>
+      <c r="I90" s="192">
+        <f>Statement!AC166</f>
+        <v>-2.6223546626159742E-2</v>
+      </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>355</v>
+        <v>445</v>
       </c>
       <c r="C91" s="192">
-        <f>Statement!M199</f>
-        <v>1</v>
+        <f>Statement!M167</f>
+        <v>-0.6527023755620609</v>
       </c>
       <c r="D91" s="192">
-        <f>Statement!N199</f>
-        <v>0.26768885199472631</v>
+        <f>Statement!N167</f>
+        <v>-0.3812991164587311</v>
       </c>
       <c r="E91" s="192">
-        <f>Statement!O199</f>
-        <v>-0.29197642617772812</v>
+        <f>Statement!O167</f>
+        <v>-6.132307701716725E-2</v>
       </c>
       <c r="F91" s="192">
-        <f>Statement!P199</f>
-        <v>0.10317719384146673</v>
+        <f>Statement!P167</f>
+        <v>-3.6728210264789486E-2</v>
       </c>
       <c r="G91" s="192">
-        <f>Statement!Q199</f>
-        <v>0.22564418690666996</v>
-      </c>
-      <c r="I91" s="214"/>
+        <f>Statement!Q167</f>
+        <v>3.8175256989442262E-2</v>
+      </c>
+      <c r="I91" s="192">
+        <f>Statement!AC167</f>
+        <v>7.4599996048482789E-2</v>
+      </c>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -37703,6 +37767,95 @@
         <v>0</v>
       </c>
       <c r="I94" s="214"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C98" s="192">
+        <f>Statement!M197</f>
+        <v>1</v>
+      </c>
+      <c r="D98" s="192">
+        <f>Statement!N197</f>
+        <v>3.4084087514825716E-2</v>
+      </c>
+      <c r="E98" s="192">
+        <f>Statement!O197</f>
+        <v>0.24818614965570993</v>
+      </c>
+      <c r="F98" s="192">
+        <f>Statement!P197</f>
+        <v>-5.5102093364575021E-2</v>
+      </c>
+      <c r="G98" s="192">
+        <f>Statement!Q197</f>
+        <v>3.2771752459329104E-2</v>
+      </c>
+      <c r="I98" s="214"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="C99" s="192">
+        <f>Statement!M198</f>
+        <v>1</v>
+      </c>
+      <c r="D99" s="192">
+        <f>Statement!N198</f>
+        <v>0.37569180272908909</v>
+      </c>
+      <c r="E99" s="192">
+        <f>Statement!O198</f>
+        <v>0.27729682030883041</v>
+      </c>
+      <c r="F99" s="192">
+        <f>Statement!P198</f>
+        <v>0.23392027917368038</v>
+      </c>
+      <c r="G99" s="192">
+        <f>Statement!Q198</f>
+        <v>0.19019336689332336</v>
+      </c>
+      <c r="I99" s="214"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="C100" s="192">
+        <f>Statement!M199</f>
+        <v>1</v>
+      </c>
+      <c r="D100" s="192">
+        <f>Statement!N199</f>
+        <v>0.26768885199472631</v>
+      </c>
+      <c r="E100" s="192">
+        <f>Statement!O199</f>
+        <v>-0.29197642617772812</v>
+      </c>
+      <c r="F100" s="192">
+        <f>Statement!P199</f>
+        <v>0.10317719384146673</v>
+      </c>
+      <c r="G100" s="192">
+        <f>Statement!Q199</f>
+        <v>0.22564418690666996</v>
+      </c>
+      <c r="I100" s="214"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37727,14 +37880,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="262" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="263"/>
+      <c r="F3" s="264" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="263"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37801,19 +37954,19 @@
       <c r="B7" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="265">
         <f>Statement!AA89</f>
         <v>-1.94224416920422E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="266"/>
+      <c r="F7" s="265">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.13415605095541402</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="266"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="224" t="s">
@@ -37840,19 +37993,19 @@
       <c r="B9" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="265">
         <f>Statement!AA90</f>
         <v>4.7563955906821963E-2</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="266"/>
+      <c r="F9" s="265">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.25173967070518793</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="266"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="224" t="s">
@@ -37879,19 +38032,19 @@
       <c r="B11" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="265">
         <f>Statement!AA91</f>
         <v>-3.4514165890573843E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="266"/>
+      <c r="F11" s="265">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.10869755303550049</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="266"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="224" t="s">
@@ -37918,19 +38071,19 @@
       <c r="B13" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="265">
         <f>Statement!AA95</f>
         <v>-4.9134358640622461E-2</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="266"/>
+      <c r="F13" s="265">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-6.1310163038172411E-2</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="266"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="224" t="s">
@@ -37957,19 +38110,19 @@
       <c r="B15" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="265">
         <f>Statement!AA96</f>
         <v>0.12923857505270303</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="266"/>
+      <c r="F15" s="265">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.5657171166707951</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="266"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="224" t="s">
@@ -37996,19 +38149,19 @@
       <c r="B17" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="265">
         <f>Statement!AA98</f>
         <v>0.60217536071032185</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="266"/>
+      <c r="F17" s="265">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>21.783459595959595</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="266"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="224" t="s">
@@ -38035,22 +38188,22 @@
       <c r="B19" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="265">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-9.1035167425135184E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="266"/>
+      <c r="F19" s="265">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.6568944396857414E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="266"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="224" t="s">
@@ -38077,22 +38230,22 @@
       <c r="B21" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="265">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="266"/>
+      <c r="F21" s="265">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="266"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38140,22 +38293,22 @@
       <c r="B25" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="265">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.17055904198675231</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="266"/>
+      <c r="F25" s="265">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.10415385026881001</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="266"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38182,22 +38335,22 @@
       <c r="B27" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="265">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>5.20515770868673E-2</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="266"/>
+      <c r="F27" s="265">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.11622609213678298</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="266"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38224,22 +38377,22 @@
       <c r="B29" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="265">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.2582560296846011</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="266"/>
+      <c r="F29" s="265">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.81595858621920747</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="266"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38287,22 +38440,22 @@
       <c r="B33" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="265">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.9204075718055491E-2</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="266"/>
+      <c r="F33" s="265">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12435933366639569</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="266"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38329,43 +38482,25 @@
       <c r="B35" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="265">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>1.600609756097561E-2</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="266"/>
+      <c r="F35" s="265">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>9.6217105263157895E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -38376,6 +38511,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
